--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT PROJECTS\ABCDautomationforUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD5F093-C7FB-4077-9FBF-20D6CCCC7834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,28 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD5F093-C7FB-4077-9FBF-20D6CCCC7834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7DC816F-5F18-4F9B-889E-B836CCE9D622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="13" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>
-    <sheet name="AddCustomer" sheetId="13" r:id="rId2"/>
-    <sheet name="AddCityArea" sheetId="1" r:id="rId3"/>
-    <sheet name="AddCityAdmin" sheetId="2" r:id="rId4"/>
-    <sheet name="AddAutoDriver" sheetId="3" r:id="rId5"/>
-    <sheet name="AddBikeDriver" sheetId="4" r:id="rId6"/>
-    <sheet name="AddTaxiDriver" sheetId="5" r:id="rId7"/>
-    <sheet name="TransportServiceCompleteTest" sheetId="15" r:id="rId8"/>
-    <sheet name="AddStore" sheetId="7" r:id="rId9"/>
-    <sheet name="StoreOperations" sheetId="8" r:id="rId10"/>
-    <sheet name="StoreStatusManagement" sheetId="10" r:id="rId11"/>
-    <sheet name="DeliveryServiceCompleteTest" sheetId="14" r:id="rId12"/>
-    <sheet name="AddProvider" sheetId="11" r:id="rId13"/>
-    <sheet name="ProviderServiceCompleteTest" sheetId="12" r:id="rId14"/>
-    <sheet name="SubscriptionPlanTest" sheetId="29" r:id="rId15"/>
-    <sheet name="AddTransportCityAdmin" sheetId="30" r:id="rId16"/>
-    <sheet name="DataCleanUpSheet" sheetId="28" r:id="rId17"/>
+    <sheet name="UniversalFlow" sheetId="31" r:id="rId2"/>
+    <sheet name="AddCustomer" sheetId="13" r:id="rId3"/>
+    <sheet name="AddCityArea" sheetId="1" r:id="rId4"/>
+    <sheet name="AddCityAdmin" sheetId="2" r:id="rId5"/>
+    <sheet name="AddAutoDriver" sheetId="3" r:id="rId6"/>
+    <sheet name="AddBikeDriver" sheetId="4" r:id="rId7"/>
+    <sheet name="AddTaxiDriver" sheetId="5" r:id="rId8"/>
+    <sheet name="TransportServiceCompleteTest" sheetId="15" r:id="rId9"/>
+    <sheet name="AddStore" sheetId="7" r:id="rId10"/>
+    <sheet name="StoreOperations" sheetId="8" r:id="rId11"/>
+    <sheet name="StoreStatusManagement" sheetId="10" r:id="rId12"/>
+    <sheet name="DeliveryServiceCompleteTest" sheetId="14" r:id="rId13"/>
+    <sheet name="AddProvider" sheetId="11" r:id="rId14"/>
+    <sheet name="ProviderServiceCompleteTest" sheetId="12" r:id="rId15"/>
+    <sheet name="SubscriptionPlanTest" sheetId="29" r:id="rId16"/>
+    <sheet name="AddTransportCityAdmin" sheetId="30" r:id="rId17"/>
+    <sheet name="DataCleanUpSheet" sheetId="28" r:id="rId18"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="113">
   <si>
     <t>City Area</t>
   </si>
@@ -3095,6 +3096,28 @@
 176.Click  Submit,click,,"//button[normalize-space()='Submit']"
 177.Verify Sucess, verify, , "//div[@aria-label='Info']"
 178.wait,2000,,</t>
+  </si>
+  <si>
+    <t>SA_TS_33</t>
+  </si>
+  <si>
+    <t>UniversalFlow</t>
+  </si>
+  <si>
+    <t>TC_CA_00_Universal_Flow</t>
+  </si>
+  <si>
+    <t>UniversalFlow is verified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Load Site,navigate,https://dev.we1.co/#/login,
+2.Enter  Email , type , super_admin@gmail.com, "//input[@placeholder='Enter your email']"
+3.Enter Password,type,R1mep@321, "//input[@placeholder='Enter your password']"
+4.Click Login,click,,"//button[@type='submit']"
+5.Verify Dashboard,verify,,"//div[contains(text(),'Date Wise Statistics')]"
+6.Load User App,switch_to,user,
+7.wait,5000,,
+</t>
   </si>
 </sst>
 </file>
@@ -3542,6 +3565,78 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C456A73-57BC-411E-B40E-DADED30882CB}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="69.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A4538F-421E-4B0B-A965-0382A5BEF523}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3613,7 +3708,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57207608-1AD9-408F-B018-55A141C9A651}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3685,7 +3780,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73960651-1493-478A-BEDA-A31CF297E315}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3757,7 +3852,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F63FB6C5-854C-4D7D-9CEB-846B4D7D2F52}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3829,7 +3924,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{319ADEF0-2336-4246-BBC3-461C4994D500}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3901,7 +3996,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0F6277B-DBCF-4BFF-819C-1E90748D3258}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3973,7 +4068,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F6B7FC7-76CD-491F-AC51-1837B3B068AC}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4038,7 +4133,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2F621F-9A1F-4BCF-BC43-4FD25385804C}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4113,6 +4208,82 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1717BC20-9348-4B52-9588-34F52BC8B75D}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.33203125" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.77734375" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" customWidth="1"/>
+    <col min="5" max="5" width="53.21875" customWidth="1"/>
+    <col min="6" max="6" width="36.88671875" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" customWidth="1"/>
+    <col min="8" max="8" width="15.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="1" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46ECEE02-404F-4AF1-8311-95653C3B218B}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4188,7 +4359,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4264,7 +4435,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9466ABF-463D-46B5-A321-4AC4765F1CE7}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4329,7 +4500,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7A75689-8D07-4A99-AA90-48806EECB90F}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4401,7 +4572,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4197A722-266E-4219-9B46-8F4D56D7D7A1}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4473,7 +4644,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{790BFFF3-3BE5-4068-A6FF-6214BEDD72BA}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4545,7 +4716,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4DB4E5D-EBF5-4B6A-BF83-7934D70C5535}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4616,76 +4787,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C456A73-57BC-411E-B40E-DADED30882CB}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7DC816F-5F18-4F9B-889E-B836CCE9D622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECD6CB3B-5825-4CF5-A965-E0EFF5DB6800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3110,14 +3110,15 @@
     <t>UniversalFlow is verified</t>
   </si>
   <si>
-    <t xml:space="preserve">1.Load Site,navigate,https://dev.we1.co/#/login,
+    <t>1.Load Site,navigate,https://dev.we1.co/#/login,
 2.Enter  Email , type , super_admin@gmail.com, "//input[@placeholder='Enter your email']"
 3.Enter Password,type,R1mep@321, "//input[@placeholder='Enter your password']"
 4.Click Login,click,,"//button[@type='submit']"
 5.Verify Dashboard,verify,,"//div[contains(text(),'Date Wise Statistics')]"
 6.Load User App,switch_to,user,
 7.wait,5000,,
-</t>
+8.Load Driver App,switch_to,driver,
+9.wait,5000,,</t>
   </si>
 </sst>
 </file>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECD6CB3B-5825-4CF5-A965-E0EFF5DB6800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76EC1EA8-2C6E-4EC3-94A5-E0208F982DA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3110,15 +3110,19 @@
     <t>UniversalFlow is verified</t>
   </si>
   <si>
-    <t>1.Load Site,navigate,https://dev.we1.co/#/login,
+    <t xml:space="preserve">1.Load Site,navigate,https://dev.we1.co/#/login,
 2.Enter  Email , type , super_admin@gmail.com, "//input[@placeholder='Enter your email']"
 3.Enter Password,type,R1mep@321, "//input[@placeholder='Enter your password']"
 4.Click Login,click,,"//button[@type='submit']"
 5.Verify Dashboard,verify,,"//div[contains(text(),'Date Wise Statistics')]"
 6.Load User App,switch_to,user,
 7.wait,5000,,
-8.Load Driver App,switch_to,driver,
-9.wait,5000,,</t>
+8.Click English  Icon,tap,,"//android.widget.Button[@content-desc="English"]"
+9.Click Next,tap,,"//android.widget.Button[@content-desc="Next"]"
+9.wait,3000,,
+10.Load Driver App,switch_to,driver,
+11.wait,5000,,
+</t>
   </si>
 </sst>
 </file>
@@ -4249,7 +4253,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" s="1" customFormat="1" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>108</v>
       </c>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F870781B-A199-4D5B-A1F8-5168EBE3C61C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E21B82-E5FC-4236-BA48-8107482CD04D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>
@@ -1860,52 +1860,6 @@
 27. Open Select City Dropdown,click,,"//select[@id='cityId']"
 28. Select {areaName},click,,"//option[contains(text(),'{areaName}')][last()]"
 29. Verify Selection,verify,,"//select[@id='cityId'][contains(.,'{areaName}')]"
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click Setting menu,click,,"//i[contains(@class,'fa-cog')]"
-2. Click Setting menu,click,,"//i[contains(@class,'fa-cog')]"
-3. Click City admin menu,click,,"//span[normalize-space()='City Admin']"
-4. Verify City Admin List,verify,,"//div[normalize-space()='City Admin List']"
-5. Click Add City Admin button,click,,"//button[contains(@class, 'buttonWidget') and normalize-space()='Add City Admin']"
-6. Verify City Admin heading,verify,,"//h2[@class='text-base font-semibold text-gray-800']"
-7.Select Name field,click ,, "//input[@id='name']"
-8. Enter Admin Name, type, faizal{randomAlpha} &gt;&gt; adminName, "//input[@id='name']"
-9.Select Email field,click,, "//input[@id='email']"
-10. Enter Email, type, faizal_{timestamp}@gmail.com, "//input[@id='email']"
-11.select the password field,click,, "//input[@id='password']"
-12.Enter the Password as "faizal@123". "//input[@id='password']"
-13.Open Select City Dropdown,click,,"//select[@id='cityId']"
-14.Select {areaName},click,,"//option[contains(text(),'{areaName}')][last()]"
-15. Click on the "Transport Service" → "Auto Ride" checkbox. "//label[normalize-space()='Auto Ride']"
-16.Click on the "Customers" → "Add Customers" checkbox. "//label[normalize-space()='Add Customers']"
-17.Click on the "Customers" → "Verified Customers"checkbox. "//label[normalize-space()='Verified Customers']"
-18.Click on the "Customers" → "Non Verified Customers" checkbox. "//label[normalize-space()='Non Verified Customers']"
-19.Click on the "Customers" → "Blocked Customers" checkbox. "//label[normalize-space()='Blocked Customers']"
-20.Click on the "Customers" → "Deleted Customers" checkbox. "//label[normalize-space()='Deleted Customers']"
-21.Click on the "Customers" → "Pending Customers" checkbox. "//label[normalize-space()='Pending Customers']"
-22.Click on the "Providers" → "Transport Providers List" checkbox. "//label[normalize-space()='Transport Providers List']"
-23.Click on the "Drivers" → "Add Driver" checkbox."//label[normalize-space()='Add Driver']"
-24.Click on the "Drivers" → "Approved Drivers" checkbox. "//label[normalize-space()='Approved Drivers']"
-25.Click on the "Drivers" → "Un-Approved Drivers" checkbox. "//label[normalize-space()='Un-Approved Drivers']"
-26.Click on the "Drivers" → "Blocked Drivers" checkbox. "//label[normalize-space()='Blocked Drivers']"
-27.Click on the "Drivers" → "Reject Drivers" checkbox. "//label[normalize-space()='Reject Drivers']"
-28.Click on the "Drivers" → "Deleted Drivers" checkbox. "//label[normalize-space()='Deleted Drivers']"
-29.Click on the "Subscription Plan" → "Driver Subscription Plan" checkbox. "//label[normalize-space()='Driver Subscription Plan']"
-30.Click on the "Cash Out" → "Driver Cash Out" checkbox. "//label[normalize-space()='Driver Cash Out']"
-31.Click on the "Report Issue" → "Customer Report Issues" checkbox. "//label[normalize-space()='Customer Report Issues']"
-32.Click on the "Report Issue" → "Driver Report Issues" checkbox. "//label[normalize-space()='Driver Report Issues']"
-33.Click on the "Report Issue" → "Provider Report Issues" checkbox,click,,"//label[normalize-space()='Provider Report Issues']"
-34.Click on the "Report Issue" → "Report issue settings" checkbox. "//label[normalize-space()='Report issue settings']"
-35.Click on the "Report Issue" → "FAQs" checkbox. "(//h3[contains(.,'Report Issue')]/following-sibling::div//label[contains(.,'FAQs')])[1]"
-36.Click on the "Website Settings" → "Header &amp; Footer Settings" checkbox. "//label[normalize-space()='Header &amp; Footer']"
-37.Click on the "Website Settings" → "Home Page Settings" checkbox. "//label[normalize-space()='Home Page']"
-38.Click on the "Website Settings" → "Delivery Settings" checkbox. "//div[h3[contains(.,'Website Settings')]]//label[contains(.,'Delivery')]"
-39.Click on the "Website Settings" → "Transport Settings" checkbox. "//div[.//h3[contains(text(),'Website Settings')]]//label[contains(.,'Transport')]"
-40.Click on the "Website Settings" → "FAQs" checkbox. "(//h3[contains(.,'Website Settings')]/following-sibling::div//label[contains(.,'FAQs')])[1]"
-41.Click on the "Add City Admin" button. "//button[@type='submit']"
-42. Verify Success Message,verify,,"//div[@aria-label='Info']"
-43.Filter admin name,type,{adminName},"//input[@aria-label='Name Filter Input']"
 </t>
   </si>
   <si>
@@ -3095,6 +3049,52 @@
 176.Click  Submit,click,,"//button[normalize-space()='Submit']"
 177.Verify Sucess, verify, , "//div[@aria-label='Info']"
 178.wait,2000,,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click Setting menu,click,,"//i[contains(@class,'fa-cog')]"
+2. Click Setting menu,click,,"//i[contains(@class,'fa-cog')]"
+3. Click City admin menu,click,,"//span[normalize-space()='City Admin']"
+4. Verify City Admin List,verify,,"//div[normalize-space()='City Admin List']"
+5. Click Add City Admin button,click,,"//button[contains(@class, 'buttonWidget') and normalize-space()='Add City Admin']"
+6. Verify City Admin heading,verify,,"//h2[@class='text-base font-semibold text-gray-800']"
+7.Select Name field,click ,, "//input[@id='name']"
+8. Enter Admin Name, type, faizal{randomAlpha} &gt;&gt; adminName, "//input[@id='name']"
+9.Select Email field,click,, "//input[@id='email']"
+10. Enter Email, type, faizal_{timestamp}@gmail.com, "//input[@id='email']"
+11.select the password field,click,, "//input[@id='password']"
+12.Enter the Password as "faizal@123". "//input[@id='password']"
+13.Open Select City Dropdown,click,,"//select[@id='cityId']"
+14.Select {areaName},click,,"//option[contains(text(),'{areaName}')][last()]"
+15. Click on the "Transport Service" → "Auto Ride" checkbox. "//label[normalize-space()='Auto Ride']"
+16.Click on the "Customers" → "Add Customers" checkbox. "//label[normalize-space()='Add Customers']"
+17.Click on the "Customers" → "Verified Customers"checkbox. "//label[normalize-space()='Verified Customers']"
+18.Click on the "Customers" → "Non Verified Customers" checkbox. "//label[normalize-space()='Non Verified Customers']"
+19.Click on the "Customers" → "Blocked Customers" checkbox. "//label[normalize-space()='Blocked Customers']"
+20.Click on the "Customers" → "Deleted Customers" checkbox. "//label[normalize-space()='Deleted Customers']"
+21.Click on the "Customers" → "Pending Customers" checkbox. "//label[normalize-space()='Pending Customers']"
+22.Click on the "Providers" → "Transport Providers List" checkbox. "//label[normalize-space()='Transport Providers List']"
+23.Click on the "Drivers" → "Add Driver" checkbox."//label[normalize-space()='Add Driver']"
+24.Click on the "Drivers" → "Approved Drivers" checkbox. "//label[normalize-space()='Approved Drivers']"
+25.Click on the "Drivers" → "Un-Approved Drivers" checkbox. "//label[normalize-space()='Un-Approved Drivers']"
+26.Click on the "Drivers" → "Blocked Drivers" checkbox. "//label[normalize-space()='Blocked Drivers']"
+27.Click on the "Drivers" → "Reject Drivers" checkbox. "//label[normalize-space()='Reject Drivers']"
+28.Click on the "Drivers" → "Deleted Drivers" checkbox. "//label[normalize-space()='Deleted Drivers']"
+29.Click on the "Subscription Plan" → "Driver Subscription Plan" checkbox. "//label[normalize-space()='Driver Subscription Plan']"
+30.Click on the "Cash Out" → "Driver Cash Out" checkbox. "//label[normalize-space()='Driver Cash Out']"
+31.Click on the "Report Issue" → "Customer Report Issues" checkbox. "//label[normalize-space()='Customer Report Issues']"
+32.Click on the "Report Issue" → "Driver Report Issues" checkbox. "//label[normalize-space()='Driver Report Issues']"
+33.Click on the "Report Issue" → "Provider Report Issues" checkbox,click,,"//label[normalize-space()='Provider Report Issues']"
+34.Click on the "Report Issue" → "Report issue settings" checkbox. "//label[normalize-space()='Report issue settings']"
+35.Click on the "Report Issue" → "FAQs" checkbox. "(//h3[contains(.,'Report Issue')]/following-sibling::div//label[contains(.,'FAQs')])[1]"
+36.Click on the "Website Settings" → "Header &amp; Footer Settings" checkbox. "//label[normalize-space()='Header &amp; Footer']"
+37.Click on the "Website Settings" → "Home Page Settings" checkbox. "//label[normalize-space()='Home Page']"
+38.Click on the "Website Settings" → "Delivery Settings" checkbox. "//div[h3[contains(.,'Website Settings')]]//label[contains(.,'Delivery')]"
+39.Click on the "Website Settings" → "Transport Settings" checkbox. "//div[.//h3[contains(text(),'Website Settings')]]//label[contains(.,'Transport')]"
+40.Click on the "Website Settings" → "FAQs" checkbox. "(//h3[contains(.,'Website Settings')]/following-sibling::div//label[contains(.,'FAQs')])[1]"
+41.Click Submit,click,,"//button[@type='submit']"
+42. Verify Success Message,verify,,"//div[@aria-label='Info']"
+43.Filter admin name,type,{adminName},"//input[@aria-label='Name Filter Input']"
+</t>
   </si>
 </sst>
 </file>
@@ -3511,7 +3511,7 @@
         <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>22</v>
@@ -3589,7 +3589,7 @@
         <v>31</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>32</v>
@@ -3661,13 +3661,13 @@
         <v>34</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>48</v>
@@ -3733,13 +3733,13 @@
         <v>57</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>60</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>61</v>
@@ -3805,7 +3805,7 @@
         <v>37</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>38</v>
@@ -3877,7 +3877,7 @@
         <v>43</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>59</v>
@@ -3949,13 +3949,13 @@
         <v>73</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>75</v>
@@ -4018,19 +4018,19 @@
         <v>74</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -4080,19 +4080,19 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>70</v>
@@ -4318,7 +4318,7 @@
         <v>26</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>40</v>
@@ -4377,13 +4377,13 @@
         <v>14</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>45</v>
@@ -4449,13 +4449,13 @@
         <v>15</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>46</v>
@@ -4521,13 +4521,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>47</v>
@@ -4593,13 +4593,13 @@
         <v>63</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>66</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>65</v>
@@ -4666,13 +4666,13 @@
         <v>28</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>48</v>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E21B82-E5FC-4236-BA48-8107482CD04D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3ACB132-3CED-47AB-9032-CAFCB3B4D90A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>
-    <sheet name="AddCustomer" sheetId="13" r:id="rId2"/>
+    <sheet name="AddCustomer" sheetId="31" r:id="rId2"/>
     <sheet name="AddCityArea" sheetId="1" r:id="rId3"/>
     <sheet name="AddCityAdmin" sheetId="2" r:id="rId4"/>
     <sheet name="AddAutoDriver" sheetId="3" r:id="rId5"/>
@@ -110,12 +110,6 @@
   </si>
   <si>
     <t>TC_CA_00_super_admin_login</t>
-  </si>
-  <si>
-    <t>1. Enter  Email , type , super_admin@gmail.com, "//input[@placeholder='Enter your email']"
-2. Enter Password,type,R1mep@321, "//input[@placeholder='Enter your password']"
-3. Click Login,click,,"//button[@type='submit']"
-4. Verify Dashboard,verify,,"//div[contains(text(),'Date Wise Statistics')]"</t>
   </si>
   <si>
     <t>Verify successful authentication of the Super Admin role using valid credentials and Dashboard access validation.</t>
@@ -1746,88 +1740,6 @@
   </si>
   <si>
     <t>This test case validates the end-to-end management of subscription plan architectures across four distinct user entities: Store, Driver, Provider, and Customer. The workflow systematically executes the creation of localized "Premium" plans for various service categories—such as Food Delivery and Pest Control—featuring integrated multi-language support in Arabic, Tamil, and Hindi. The validation cycle spans from defining plan durations, pricing, and free-ride quotas to conducting administrative audits including localized description verification, active/inactive state toggling, and data filtering. The process concludes by confirming the operational lifecycle through record modification and final deletion, ensuring the functional stability and localized integrity of the platform’s commercial monetization modules.</t>
-  </si>
-  <si>
-    <t>1. Click Customer  Icon,click,,"//i[@class='fa-solid fa-users fas iconstyle']"
-2.Click  Add Customers,click,,"//span[normalize-space()='Add Customers']"
-3. Verify Add Customer Heading,verify,,"//div[normalize-space()='Add Customer']"
-4.Enter Customer Name, type, customer{randomAlpha} &gt;&gt; customerName, "//label[contains(., 'Customer Full Name')]/following::input[1]"
-5.Enter Email, type, customer_{timestamp}@gmail.com&gt;&gt;customerEmail, "//input[@type='email']"
-6.Enter Contact Number, type, {randomPhone}, "//input[@type='tel']"
-7.Enter Video Call Limit, type, 60, "//label[contains(., 'User Used Video Call Limit in Minutes')]/following::input[1]"
-8.Open Gender,click,,"//span[@aria-label='select gender']"
-9.Select Male,click,,"//li[@aria-label='Male']"
-10.Upload Profile Image, uploadfile, "src/main/resources/test-data/customer.jpg", "//input[@type='file' and @accept='image/*']"
-11.Click Submit, click, , "//button[normalize-space()='Submit']"
-12.Verify Added Succesfully, verify, , "//div[@aria-label='Info']"
-13. Click Customer  Icon,click,,"//i[@class='fa-solid fa-users fas iconstyle']"
-14. Click Customer  Icon,click,,"//i[@class='fa-solid fa-users fas iconstyle']"
-15.Click  Verified Customers,click,,"//span[normalize-space()='Verified Customers']"
-16. Verify Verified Customer List Heading,verify,,"//div[normalize-space()='Verified Customer List']"
-17.Filter Customer Name List,type,{customerName},"//input[@aria-label='Customer Name Filter Input']"
-18.Scroll Grid, tab, 7, "//input[@aria-label='Customer Name Filter Input']"
-19.Click Edit Icon ,click,,"//i[@class='bi bi-pencil-square cursor-pointer gridIcon Edit']"
-20.Click Close, click, , "//button[normalize-space()='Close']"
-21.Click Wallet Icon ,click,,"//i[@title='Wallet']"
-22.Click Add Money ,click,,"//button[normalize-space()='Add Money']"
-23.Enter Wallet Amount, type, 1000, "//input[@placeholder='Enter Wallet Amount']"
-24.Open Choose Option Dropdown,click,,"//label[contains(.,'Choose Option')]/following-sibling::p-dropdown/div"
-25.Select Add Money,click,,"//li[@role='option' and @aria-label='Add Money']"
-26.Click Submit, click, , "//button[normalize-space()='Submit']"
-27.Verify Saved Succesfully, verify, , "//div[@aria-label='Added Successfully']"
-28.Click Add Money ,click,,"//button[normalize-space()='Add Money']"
-29.Enter Wallet Amount, type, 200, "//input[@placeholder='Enter Wallet Amount']"
-30.Open Choose Option Dropdown,click,,"//label[contains(.,'Choose Option')]/following-sibling::p-dropdown/div"
-31.Select Deduct Money,click,,"//li[@role='option'][contains(.,'Deduct Money')]"
-32.Click Submit, click, , "//button[normalize-space()='Submit']"
-33.Verify Saved Succesfully, verify, , "//div[@aria-label='Added Successfully']"
-34. Click Customer  Icon,click,,"//i[@class='fa-solid fa-users fas iconstyle']"
-35. Click Customer  Icon,click,,"//i[@class='fa-solid fa-users fas iconstyle']"
-36.Click  Verified Customers,click,,"//span[normalize-space()='Verified Customers']"
-37. Verify Verified Customer List Heading,verify,,"//div[normalize-space()='Verified Customer List']"
-38.Filter Customer Name List,type,{customerName},"//input[@aria-label='Customer Name Filter Input']"
-39.Scroll Grid, tab, 7, "//input[@aria-label='Customer Name Filter Input']"
-40.Click Loyalty Points Icon,click,,"//i[@title='Loyalty Points']"
-41.Click Manage Loyality Points, click, , "//button[normalize-space()='Manage Loyalty Points']"
-42.Open Service Dropdown,click,,"//label[contains(.,'Service')]/following-sibling::p-dropdown/div"
-43.Select Bike Ride,click,,"//li[@role='option'][contains(.,'Bike Ride')]"
-44.Open Choose Option Dropdown,click,,"//label[contains(.,'Choose Option')]/following-sibling::p-dropdown/div"
-45.Select Add Points,click,,"//li[@role='option'][contains(.,'Add Points')]"
-46.Enter Points, type, 30, "//input[@placeholder='Enter Points']"
-47.Click Submit, click, , "//button[normalize-space()='Submit']"
-48.Verify Added Succesfully, verify, , "//div[@aria-label='Info']"
-49.Click Manage Loyality Points, click, , "//button[normalize-space()='Manage Loyalty Points']"
-50.Open Service Dropdown,click,,"//label[contains(.,'Service')]/following-sibling::p-dropdown/div"
-51.Select Bike Ride,click,,"//li[@role='option'][contains(.,'Bike Ride')]"
-52.Open Choose Option Dropdown,click,,"//label[contains(.,'Choose Option')]/following-sibling::p-dropdown/div"
-53.Select Deduct Points,click,,"//li[@role='option'][contains(.,'Deduct Points')]"
-54.Enter Points, type, 10, "//input[@placeholder='Enter Points']"
-55.Click Submit, click, , "//button[normalize-space()='Submit']"
-56.Verify Added Succesfully, verify, , "//div[@aria-label='Info']"
-57. Click Customer  Icon,click,,"//i[@class='fa-solid fa-users fas iconstyle']"
-58. Click Customer  Icon,click,,"//i[@class='fa-solid fa-users fas iconstyle']"
-59.Click  Verified Customers,click,,"//span[normalize-space()='Verified Customers']"
-60. Verify Verified Customer List Heading,verify,,"//div[normalize-space()='Verified Customer List']"
-61.Filter Customer Name List,type,{customerName},"//input[@aria-label='Customer Name Filter Input']"
-62.Scroll Grid, tab, 7, "//input[@aria-label='Customer Name Filter Input']"
-63.Click Disable  Icon,click,,"//i[@title='Block']"
-64.Click Disable  User  Yes,click,,"//button[normalize-space()='Yes']"
-65.Disable Reason,type,Client Complaints,"//textarea[@id='swal2-textarea']"
-66.Click Reject  Yes,click,,"//button[normalize-space()='Yes']"
-67.Verify Added Succesfully, verify, , "//div[@aria-label='Info']"
-68. Click Customer  Icon,click,,"//i[@class='fa-solid fa-users fas iconstyle']"
-69. Click Customer  Icon,click,,"//i[@class='fa-solid fa-users fas iconstyle']"
-70.Click  Blocked Customers,click,,"//span[normalize-space()='Blocked Customers']"
-71.Filter Customer Name List,type,{customerName},"//input[@aria-label='Customer Name Filter Input']"
-72.Scroll Grid, tab, 10, "//input[@aria-label='Customer Name Filter Input']"
-73.Click Enable  Icon,click,,"//i[@title='Status']"
-74.Click Enable  Yes,click,,"//button[normalize-space()='Yes']"
-75. Click Customer  Icon,click,,"//i[@class='fa-solid fa-users fas iconstyle']"
-76. Click Customer  Icon,click,,"//i[@class='fa-solid fa-users fas iconstyle']"
-77.Click  Verified Customers,click,,"//span[normalize-space()='Verified Customers']"
-78. Verify Verified Customer List Heading,verify,,"//div[normalize-space()='Verified Customer List']"
-79.Filter Customer Name List,type,{customerName},"//input[@aria-label='Customer Name Filter Input']"
-80.wait,1000,,</t>
   </si>
   <si>
     <t xml:space="preserve">1. Click Setting menu,click,,"//i[contains(@class,'fa-cog')]"
@@ -3095,6 +3007,93 @@
 42. Verify Success Message,verify,,"//div[@aria-label='Info']"
 43.Filter admin name,type,{adminName},"//input[@aria-label='Name Filter Input']"
 </t>
+  </si>
+  <si>
+    <t>1. Enter  Email , type , super_admin@gmail.com, "admin.login.email"
+2. Enter Password,type,R1mep@321, "admin.login.password"
+3. Click Login,click,,"admin.login.submit_btn"
+4. Verify Dashboard,verify,,"admin.dashboard.statistics_header"</t>
+  </si>
+  <si>
+    <t>1. Click Customer Icon,click,,"admin.menu.customer_icon"
+2.Click Add Customers,click,,"admin.menu.add_customers"
+3. Verify Add Customer Heading,verify,,"admin.customer.add_heading"
+4.Enter Customer Name, type, customer{randomAlpha} &gt;&gt; customerName, "admin.customer.input_name"
+5.Enter Email, type, customer_{timestamp}@gmail.com&gt;&gt;customerEmail, "admin.customer.input_email"
+6.Enter Contact Number, type, {randomPhone}, "admin.customer.input_phone"
+7.Enter Video Call Limit, type, 60, "admin.customer.input_video_limit"
+8.Open Gender,click,,"admin.customer.dropdown_gender"
+9.Select Male,click,,"admin.customer.select_gender_male"
+10.Upload Profile Image, uploadfile, "src/main/resources/test-data/customer.jpg", "admin.customer.upload_profile_img"
+11.Click Submit, click, , "admin.customer.submit_btn"
+12.Verify Added Succesfully, verify, , "admin.customer.toast_info"
+13. Click Customer Icon,click,,"admin.menu.customer_icon"
+14. Click Customer Icon,click,,"admin.menu.customer_icon"
+15.Click Verified Customers,click,,"admin.menu.verified_customers"
+16. Verify Verified Customer List Heading,verify,,"admin.customer.verified_list_heading"
+17.Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+18.Scroll Grid, tab, 7, "admin.customer.filter_name"
+19.Click Edit Icon ,click,,"admin.customer.grid.btn_edit"
+20.Click Close, click, , "admin.customer.grid.btn_close"
+21.Click Wallet Icon ,click,,"admin.customer.grid.btn_wallet"
+22.Click Add Money ,click,,"admin.customer.wallet.btn_add_money"
+23.Enter Wallet Amount, type, 1000, "admin.customer.wallet.input_amount"
+24.Open Choose Option Dropdown,click,,"admin.customer.wallet.dropdown_option"
+25.Select Add Money,click,,"admin.customer.wallet.select_add_money"
+26.Click Submit, click, , "admin.customer.submit_btn"
+27.Verify Saved Succesfully, verify, , "admin.customer.toast_added_success"
+28.Click Add Money ,click,,"admin.customer.wallet.btn_add_money"
+29.Enter Wallet Amount, type, 200, "admin.customer.wallet.input_amount"
+30.Open Choose Option Dropdown,click,,"admin.customer.wallet.dropdown_option"
+31.Select Deduct Money,click,,"admin.customer.wallet.select_deduct_money"
+32.Click Submit, click, , "admin.customer.submit_btn"
+33.Verify Saved Succesfully, verify, , "admin.customer.toast_added_success"
+34. Click Customer Icon,click,,"admin.menu.customer_icon"
+35. Click Customer Icon,click,,"admin.menu.customer_icon"
+36.Click Verified Customers,click,,"admin.menu.verified_customers"
+37. Verify Verified Customer List Heading,verify,,"admin.customer.verified_list_heading"
+38.Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+39.Scroll Grid, tab, 7, "admin.customer.filter_name"
+40.Click Loyalty Points Icon,click,,"admin.customer.grid.btn_loyalty_points"
+41.Click Manage Loyality Points, click, , "admin.customer.loyalty.btn_manage"
+42.Open Service Dropdown,click,,"admin.customer.loyalty.dropdown_service"
+43.Select Bike Ride,click,,"admin.customer.loyalty.select_bike_ride"
+44.Open Choose Option Dropdown,click,,"admin.customer.loyalty.dropdown_option"
+45.Select Add Points,click,,"admin.customer.loyalty.select_add_points"
+46.Enter Points, type, 30, "admin.customer.loyalty.input_points"
+47.Click Submit, click, , "admin.customer.submit_btn"
+48.Verify Added Succesfully, verify, , "admin.customer.toast_info"
+49.Click Manage Loyality Points, click, , "admin.customer.loyalty.btn_manage"
+50.Open Service Dropdown,click,,"admin.customer.loyalty.dropdown_service"
+51.Select Bike Ride,click,,"admin.customer.loyalty.select_bike_ride"
+52.Open Choose Option Dropdown,click,,"admin.customer.loyalty.dropdown_option"
+53.Select Deduct Points,click,,"admin.customer.loyalty.select_deduct_points"
+54.Enter Points, type, 10, "admin.customer.loyalty.input_points"
+55.Click Submit, click, , "admin.customer.submit_btn"
+56.Verify Added Succesfully, verify, , "admin.customer.toast_info"
+57. Click Customer Icon,click,,"admin.menu.customer_icon"
+58. Click Customer Icon,click,,"admin.menu.customer_icon"
+59.Click Verified Customers,click,,"admin.menu.verified_customers"
+60. Verify Verified Customer List Heading,verify,,"admin.customer.verified_list_heading"
+61.Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+62.Scroll Grid, tab, 7, "admin.customer.filter_name"
+63.Click Disable Icon,click,,"admin.customer.grid.btn_block"
+64.Click Disable User Yes,click,,"admin.customer.dialog.btn_confirm_yes"
+65.Disable Reason,type,Client Complaints,"admin.customer.dialog.textarea_reason"
+66.Click Reject Yes,click,,"admin.customer.dialog.btn_confirm_yes"
+67.Verify Added Succesfully, verify, , "admin.customer.toast_info"
+68. Click Customer Icon,click,,"admin.menu.customer_icon"
+69. Click Customer Icon,click,,"admin.menu.customer_icon"
+70.Click Blocked Customers,click,,"admin.menu.blocked_customers"
+71.Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+72.Scroll Grid, tab, 10, "admin.customer.filter_name"
+73.Click Enable Icon,click,,"admin.customer.grid.btn_status_enable"
+74.Click Enable Yes,click,,"admin.customer.dialog.btn_confirm_yes"
+75. Click Customer Icon,click,,"admin.menu.customer_icon"
+76. Click Customer Icon,click,,"admin.menu.customer_icon"
+77.Click Verified Customers,click,,"admin.menu.verified_customers"
+78. Verify Verified Customer List Heading,verify,,"admin.customer.verified_list_heading"
+79.Filter Customer Name List,type,{customerName},"admin.customer.filter_name"</t>
   </si>
 </sst>
 </file>
@@ -3511,19 +3510,19 @@
         <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>23</v>
+        <v>106</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -3583,22 +3582,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -3655,22 +3654,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -3727,22 +3726,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -3799,22 +3798,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -3871,22 +3870,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -3943,22 +3942,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4015,22 +4014,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -4080,22 +4079,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4113,7 +4112,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46ECEE02-404F-4AF1-8311-95653C3B218B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4396F6CA-D57B-49F5-A8ED-CEBB93A6ED43}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4158,19 +4157,19 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4237,16 +4236,16 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4312,16 +4311,16 @@
         <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -4377,16 +4376,16 @@
         <v>14</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4449,16 +4448,16 @@
         <v>15</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4515,22 +4514,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4587,22 +4586,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4660,22 +4659,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43B0356B-E3FD-4B43-95F8-B87BD805C748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96B60783-E1EF-4901-A479-BBF4161F3A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3063,36 +3063,37 @@
 79. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click Setting menu,click,,"web.global.menu.settings"
-2. Click City area menu,click,,"admin.menu.city_area"
-3. Verify City Area List,verify,,"admin.city_area.list_heading"
-4. Click Add City Area button,click,,"admin.city_area.btn_add"
-5. Verify City Area heading,verify,,"admin.city_area.add_heading"
-6. Enter Area Name,type,triplicane_{timestamp} &gt;&gt; areaName,"admin.city_area.input_name"
-7. Open Status Dropdown,click,,"admin.city_area.dropdown_status"
-8. Select Active,click,,"admin.city_area.select_status_active"
-9. Enter City Area,type,triplicane,"admin.city_area.input_search_location"
-10. wait,1000,,
-11. Select First Option,arrow_down,,"admin.city_area.input_search_location"
-12. Confirm Option,press_enter,,"admin.city_area.input_search_location"
-13. wait,1000,,
-14. Map Polygon,draw polygon,"-120;-120 : 120;-120 : 120;120 : -120;120 : -120;-120","//div[@class='ol-layer']//canvas"
-15. Click Submit,click,,"web.global.action.submit"
-16. Verify Success Message,verify,,"web.global.toast.success"
-17. Click Transport Services,click,,"admin.transport.card_link"
-18. Verify Transport Page,verify,,"admin.transport.page_heading"
-19. Click Add Category,click,,"admin.transport.btn_add_category"
-20. Open Select City Dropdown,click,,"admin.transport.dropdown_city_multiselect"
-21. Search City Area,type,{areaName},"admin.transport.input_filter_city"
-22. Verify Area in Dropdown,verify,,"admin.transport.select_filtered_option"
-23. Click close,click,,"web.global.action.close"
-24. Click Setting menu,click,,"web.global.menu.settings"
-25. Click City admin menu,click,,"admin.menu.city_admin"
-26. Verify City Admin List,verify,,"admin.city_admin.list_heading"
-27. Click Add City Admin button,click,,"admin.city_admin.btn_add"
-28. Open Select City Dropdown,click,,"admin.city_admin.select_city_dropdown"
-29. Select {areaName},click,,"admin.city_admin.select_dynamic_option"
-30. Verify Selection,verify,,"admin.city_admin.verify_dropdown_value"
+    <t xml:space="preserve">1. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+2. Click Setting menu,click,,"web.global.menu.settings"
+3. Click City area menu,click,,"admin.menu.city_area"
+4. Verify City Area List,verify,,"admin.city_area.list_heading"
+5. Click Add City Area button,click,,"admin.city_area.btn_add"
+6. Verify City Area heading,verify,,"admin.city_area.add_heading"
+7. Enter Area Name,type,triplicane_{timestamp} &gt;&gt; areaName,"admin.city_area.input_name"
+8. Open Status Dropdown,click,,"admin.city_area.dropdown_status"
+9. Select Active,click,,"admin.city_area.select_status_active"
+10. Enter City Area,type,triplicane,"admin.city_area.input_search_location"
+11. wait,1000,,
+12. Select First Option,arrow_down,,"admin.city_area.input_search_location"
+13. Confirm Option,press_enter,,"admin.city_area.input_search_location"
+14. wait,1000,,
+15. Map Polygon,draw polygon,"-120;-120 : 120;-120 : 120;120 : -120;120 : -120;-120","//div[@class='ol-layer']//canvas"
+16. Click Submit,click,,"web.global.action.submit"
+17. Verify Success Message,verify,,"web.global.toast.success"
+18. Click Transport Services,click,,"admin.transport.card_link"
+19. Verify Transport Page,verify,,"admin.transport.page_heading"
+20. Click Add Category,click,,"admin.transport.btn_add_category"
+21. Open Select City Dropdown,click,,"admin.transport.dropdown_city_multiselect"
+22. Search City Area,type,{areaName},"admin.transport.input_filter_city"
+23. Verify Area in Dropdown,verify,,"admin.transport.select_filtered_option"
+24. Click close,click,,"web.global.action.close"
+25. Click Setting menu,click,,"web.global.menu.settings"
+26. Click City admin menu,click,,"admin.menu.city_admin"
+27. Verify City Admin List,verify,,"admin.city_admin.list_heading"
+28. Click Add City Admin button,click,,"admin.city_admin.btn_add"
+29. Open Select City Dropdown,click,,"admin.city_admin.select_city_dropdown"
+30. Select {areaName},click,,"admin.city_admin.select_dynamic_option"
+31. Verify Selection,verify,,"admin.city_admin.verify_dropdown_value"
 </t>
   </si>
 </sst>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34816D78-B912-4358-B4A5-4C37AB9A8B62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{106C96A7-C8B0-4924-B6A1-AEF71A3DCFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="AddAutoDriver" sheetId="33" r:id="rId5"/>
     <sheet name="AddBikeDriver" sheetId="34" r:id="rId6"/>
     <sheet name="AddTaxiDriver" sheetId="35" r:id="rId7"/>
-    <sheet name="TransportServiceCompleteTest" sheetId="15" r:id="rId8"/>
+    <sheet name="TransportServiceCompleteTest" sheetId="37" r:id="rId8"/>
     <sheet name="AddTransportCityAdmin" sheetId="30" r:id="rId9"/>
     <sheet name="AddStore" sheetId="7" r:id="rId10"/>
     <sheet name="StoreOperations" sheetId="8" r:id="rId11"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="114">
   <si>
     <t>City Area</t>
   </si>
@@ -1740,186 +1740,6 @@
   </si>
   <si>
     <t>Super Admin Login</t>
-  </si>
-  <si>
-    <t>1.Click Transports Services Icon,click,,"//i[@class='fa-motorcycle fa-solid iconstyle']"
-2. Click Transports Services Menu,click,,"//h2[normalize-space()='Transport Services']"
-3.Verify Transport Services,verify,,"//div[normalize-space()='TRANSPORT SERVICES']"
-4.Click  Add Category,click,,"//button[normalize-space()='Add Category']"
-5.Enter Service Name, type, Bus Ride{randomAlpha}&gt;&gt;transportName, "//input[@placeholder='Service Name']"
-6.Enter Service Name Arabic, type, رحلة بالحافلة, "//input[@placeholder='Service Name (in Arabic)']"
-7.Enter Slug, type, Bus Ride, "//input[@placeholder='Slug']"
-8.Upload Transport Service Image, uploadfile, "src/main/resources/test-data/bus.jpg", "//input[@type='file' and @accept='image/*']"
-9.wait,2000,,
-10.Open status Dropdown,click,,"//label[contains(., 'Status')]/following-sibling::p-dropdown"
-11.Select Activate,click,,"//li[@aria-label='Activate']"
-12.Open Select City Dropdown,click,,"//span[text()='Select City']/ancestor::app-drop-down//div[contains(@class, 'p-multiselect-label-container')]"
-13.Select {areaName},click,,"//li[@aria-label='{areaName}']"
-14.Click  Submit,click,,"//button[normalize-space()='Submit']"
-15.Verify Sucess, verify, , "//div[@aria-label='Info']"
-16.wait,2000,,
-17.Click  back,click,,"//button[normalize-space()='Back']"
-18.Click Transports Services Icon,click,,"//i[@class='fa-motorcycle fa-solid iconstyle']"
-19.Click Transports Services Menu,click,,"//h2[normalize-space()='Transport Services']"
-20.Filter Services List,type,{transportName},"//input[@aria-label='Services Filter Input']"
-21.Click Home Icon ,click,,"//i[@title='Home']"
-22.Click Settings ,click,,"//button[contains(., 'Settings')]"
-23.Click Vehicle Type,click,,"//div[normalize-space()='Vehicle Type']"
-24.Click Add Vehicle Type,click,,"//button[normalize-space()='Add Vehicle Type']"
-25.Enter Vehicle Type Name, type, volvo{randomAlpha}&gt;&gt;busTypeName, "//input[@placeholder='Enter Vehicle Type']"
-26.Enter Base Fare, type, 150, "//input[@placeholder='Enter base fare']"
-27.Enter Base Fare Max Kilometer, type, 10, "//input[@placeholder='Enter Base Fare KM Limit']"
-28.Open Extra Distance Fare Dropdown,click,"//label[contains(., 'Extra Distance Fare Type')]/following-sibling::p-dropdown"
-29.Select Amount,click,,"//li[@aria-label='Amount']"
-30.Enter Extra Distance Fare , type, 10, "//input[@placeholder='Extra Distance Fare (Per Km)']"
-31.Enter Free Waiting Time , type, 10, "//label[contains(., 'Free Waiting Time')]/following::input[1]"
-32.Open Waiting Charge Dropdown,click,"((//label[contains(., 'Waiting Charge Type')]/following::p-dropdown)[1])"
-33.Select Amount,click,,"//li[@aria-label='Amount']"
-34.Enter Waiting Rate , type, 10, "//input[@placeholder='Waiting Rate (per min)']"
-35.Enter Included Trip Waiting , type, 10, "//input[@placeholder='Included Trip Waiting']"
-36.Open Trip Waiting Charge Dropdown,click,"((//label[contains(., 'Waiting Charge Type')]/following::p-dropdown)[2])"
-37.Select Amount,click,,"//li[@aria-label='Amount']"
-38.Enter Trip Waiting Rate , type,50, "//input[@placeholder='Trip Waiting Rate (per min)']"
-39.Enter Free Pickup Distance , type,5, "//input[@placeholder='Free Pickup Distance (In kms)']"
-40.Open Pickup Charge Dropdown,click,"//label[contains(., 'Pickup Charge Type')]/following-sibling::p-dropdown"
-41.Select Amount,click,,"//li[@aria-label='Amount']"
-42.Enter Pickup Fee, type,50, "//input[@placeholder='Pickup Fee (Per Km)']"
-43.Open Customer Fee  Dropdown,click,"//span[@aria-label='Customer Fee Type']"
-44.Select Amount,click,,"//li[@aria-label='Amount']"
-45.Enter Customer Fee, type,50, "//input[@placeholder='Customer Fee']"
-46.Open Customer GST  Dropdown,click,"//label[contains(., 'Customer GST type')]/following-sibling::p-dropdown"
-47.Select Amount,click,,"//li[@aria-label='Amount']"
-48.Enter  GST amount, type,50, "//input[contains(@placeholder,'Enter GST amount or percentage')]"
-49.Open Driver Fee  Dropdown,click,"//span[@aria-label='Driver Fee Type']"
-50.Select Amount,click,,"//li[@aria-label='Amount']"
-51.Enter  Driver Fee, type,50, "//input[@placeholder='Driver Fee']"
-52.Open Driver GST  Dropdown,click,"//label[contains(., 'Driver GST type')]/following-sibling::p-dropdown"
-53.Select Amount,click,,"//li[@aria-label='Amount']"
-54.Enter Driver Gst,type,50," //input[@placeholder='Driver GST in amount or percentage']"
-55.Open Status Dropdown,click,"//label[contains(., 'Status')]/following-sibling::p-dropdown"
-56.Select Active,click,,"//li[@aria-label='Active']"
-57.Upload Vehicle Image, uploadfile, "src/main/resources/test-data/volvo.jpg", "//app-image-upload//input[@type='file' and @accept='image/*']"
-58.Enter Notifiacation,type,50,"//input[@placeholder='User will be notified when pickup km exceeds this']"
-59.Enter Driver Request ETA,type,50,"//input[@placeholder='Enter Driver ETA Limit']"
-60.Enter Driver Request KM,type,50,"//input[@placeholder='Driver Request KM Limit']"
-61.Click Surcharge Time Checkbox, click, , "//div[text()='EveryDay']/preceding-sibling::mat-checkbox"
-62.Enter From Time, type, 100000AM, "((//input[@placeholder='--:--:-- --'])[1])"
-63.Enter To Time, type, 220000PM, "((//input[@placeholder='--:--:-- --'])[2])"
-64.Open  Dropdown,click,"((//span[@aria-label='select type'])[1])"
-65.Select Amount,click,,"//li[@aria-label='Amount']"
-66.Enter  Price, type,50, "//input[@placeholder='Enter Price']"
-67.Click  Submit,click,,"//button[normalize-space()='Submit']"
-68.Verify Sucess, verify, , "//div[@aria-label='Info']"
-69.Click Settings ,click,,"//button[contains(., 'Settings')]"
-70.Click Promocode,click,,"//div[normalize-space()='Promocode']"
-71.Click Add Promo Code ,click,,"//button[normalize-space()='Add Promo Code']"
-72.Open User List Dropdown,click,,"//label[contains(., 'User List')]/following-sibling::p-multiselect//div[contains(@class, 'p-multiselect-label-container')]"
-73.Select User,click,,"//li[@aria-label='{customerName}']"
-74.Click Code Name Box,click,,"//input[@placeholder='Code Name']"
-75.Enter Code Name, type, promoCode{randomAlpha}&gt;&gt; promoCodeName, "//input[@placeholder='Code Name']"
-76.Open Discout Type Dropdown,click,,"//span[@aria-label='Select Discount Type']"
-77.Select Discout Type,click,,"//li[@aria-label='Discount in Amount ']"
-78.Enter Expiry Date,type,12122026,"//div[label[contains(., 'Expiry Date')]]//input"
-79.Enter Discount Amount, type, 100, "//input[@placeholder='Discount Amount']"
-80.Enter Minimum Order Amount, type, 1000, "//input[@placeholder='Min Order Amount']"
-81.Enter Maximum Discount Amount, type, 100, "//input[@placeholder='Max DiscountAmount']"
-82.Enter Coupon Limit, type, 5,"//div[label[contains(., 'Coupon Limit')]]//input"
-83.Enter Usage Limit for One User, type, 2,"//div[label[contains(., 'Usage Limit For One User')]]//input"
-84.Enter Promo Code Description, type, Promo Dode For Gold Member,"//textarea[@placeholder='PromoCode Description']"
-85.Click Submit ,click,,"//button[normalize-space()='Submit']"
-86.Verify Sucess, verify, , "//div[@aria-label='Info']"
-87.wait,2000,,
-88.Click Settings ,click,,"//button[contains(., 'Settings')]"
-89.Click Service Settings ,click,,"//div[normalize-space()='Service Setting']"
-90.Enter Driver Accept Timeout, type, 60, "//label[contains(., "Driver Accept Timeout")]/following::input[1]"
-91.Enter Driver Serach Radius, type, 50, "//label[contains(., "Driver Search Radius")]/following::input[1]"
-92.Click Submit ,click,,"//button[normalize-space()='Submit']"
-93.Verify Sucess, verify, , "//div[@aria-label='Info']"
-94.wait,1000,,
-95.Click Settings ,click,,"//button[contains(., 'Settings')]"
-96.Click Requirment Document ,click,,"//div[contains(text(), 'Required Documents')]"
-97.Click Add Document ,click,,"//button[normalize-space()='Add Document']"
-98.Enter Name, type, documet{randomAlpha}&gt;&gt; documentName, "//label[contains(., 'Name')]/following::input[1]"
-99.Open status Dropdown,click,,"//label[contains(., 'Status')]/following::div[contains(@class, 'p-dropdown')]"
-100.Select Active,click,,"//li[@aria-label='Active']"
-101.Click Document Expiry ,click,,"//div[./div[contains(text(), 'Document Expiry')]]//input"
-102.Click Mandatory Document ,click,,"//div[./div[contains(text(), 'Mandatory Document')]]//input"
-103.Click  Require Proof Number,click,,"//div[./div[contains(text(), 'Require Proof Number')]]//input"
-104.Enter Display Order, type, 10,"//input[@placeholder='Display Order']"
-105.Click Submit ,click,,"//button[normalize-space()='Submit']"
-106.Verify Sucess, verify, , "//div[@aria-label='Info']"
-107.Filter Document List,type,{documentName},"//input[@aria-label='Name Filter Input']"
-108.wait,1000,,
-109.Click Settings ,click,,"//button[contains(., 'Settings')]"
-110.Click Customer Loyalty Settings,click,,"//div[text()=' Customer Loyalty Settings ']"
-111.Open status Allow Customer loyalty points,click,,"//label[contains(., 'Allow Customer loyalty points')]/following::div[contains(@class, 'p-dropdown')]"
-112.Select ON,click,,"//li[@role='option']//span[text()='ON']"
-113.Enter Minimum order amount for eligibility to redeem loyalty points, type, 100,"//label[contains(., 'Minimum order amount for eligibility to redeem loyalty points')]/following::input[1]"
-114.Enter Loyalty points redeem per order (in %) (% of order amount), type, 10,"//label[contains(., 'Loyalty points redeem per order (in %) (% of order amount)')]/following::input[1]"
-115.Enter Loyalty points per default currency (for ex. $1 = 10 points), type, 5,"//label[contains(., 'Loyalty points per default currency (for ex. $1 = 10 points)')]/following::input[1]"
-116.Click Submit ,click,,"//button[normalize-space()='Submit']"
-117.Verify Sucess, verify, , "//div[@aria-label='Info']"
-118.Click drivers menu,click,,"//i[contains(@class,'fa-motorcycle fa-solid iconstyle')]"
-119.Click Add Driver menu,click,,"//span[normalize-space()='Add Driver']"
-120.Verify Add Driver,verify,,"//div[contains(text(),'Add Driver')]"
-121.Click Service Category Dropdown,click,,"//span[@aria-label='Select Service category']"
-122.Select Bus Ride Option,click,,"//span[normalize-space()='{transportName}']"
-123.Click Checkbox, click, , "//div[contains(@class, 'mdc-checkbox')][1]"
-124.Enter Driver Name, type, busdriver_{timestamp} &gt;&gt; busDriverName, "//label[contains(.,'Full Name')]/following::input[1]"
-125.Enter Email, type, busdriver_{timestamp}@gmail.com&gt;&gt;busEmail, "//label[contains(.,'Email')]/following::input[1]"
-126.Enter Contact Number, type, {randomPhone}, "//input[@type='tel']"
-127.Upload Profile Image, uploadfile, "src/main/resources/test-data/busdriver.jpg", "//input[@type='file']"
-128.Select Male Gender, click, , "//div[contains(@class, 'genlabel') and text()='Male']"
-129.Click Vehicle Type Dropdown,click,,"//span[contains(@aria-label,'vehicle type')]"
-130.Select  volvo Option,click,,"//li[@role='option']//span[text()='{busTypeName}']"
-131.Enter Model Year, type, 2013, "//label[contains(.,'Model Year')]/following::input[1]"
-132.Enter Vehicle Company, type, busCompany{randomAlpha}&gt;&gt; busCompanyName, "//label[contains(.,'Vehicle Company')]/following::input[1]"
-133.Enter Plate No, type, KL-01-AB-1634, "//label[contains(.,'Plate No')]/following::input[1]"
-134. Enter Model Name, type, deisel, "//label[contains(.,'Model Name')]/following::input[1]"
-135.Upload Vehicle Image, uploadfile, "src/main/resources/test-data/busvolvo.jpeg", "(//input[@type='file'])[2]"
-136. Enter Vehicle Color, type, white, "//label[contains(.,'Vehicle Color')]/following::input[1]"
-137.Enter Bank Name, type, HDFC Bank, "//label[contains(.,'Bank Name')]/following::input[1]"
-138.Enter Bank Location, type, Chennai, "//label[contains(.,'Bank Location')]/following::input[1]"
-139.Enter Account Number, type, 50100123456789, "//label[contains(.,'Account Number')]/following::input[1]"
-140.Enter Account Holder Name, type, {busDriverName}, "//label[contains(.,'Account Holder Name')]/following::input[1]"
-141.Enter Payment Email Address, type, {busEmail}, "//label[contains(.,'Payment Email Address')]/following::input[1]"
-142.Enter IFSC Code, type, HDFC0001234, "//label[contains(.,'IFSC Code')]/following::input[1]"
-143.Click Submit, click, , "//button[contains(.,'Submit')]"
-144.Verify Driver Added, verify, , "//div[@aria-label='Added Successfully']"
-145.Wait for Toast to hide, wait, 1000,
-146.Click drivers menu,click,,"//i[contains(@class,'fa-motorcycle fa-solid iconstyle')]"
-147.Click drivers menu,click,,"//i[contains(@class,'fa-motorcycle fa-solid iconstyle')]"
-148.Click Pending Documents,click,," //span[normalize-space()='Pending Documents']"
-149.Filter by Name,type,{busDriverName},"//input[@aria-label='Driver Name Filter Input']"
-150.Scroll Grid, tab, 7, "//input[@aria-label='Driver Name Filter Input']"
-151.Click Doc Icon,click,,"//i[@class='bi bi-file-earmark-text cursor-pointer gridIcon Navigate']"
-152.Driver Required Documents,verify,,"//div[contains(text(),'Driver Required Documents')]"
-153.FilterDocumet List,type,{documentName},"//input[@aria-label='Document Name Filter Input']"
-154.Add Driving License,click,,"//i[@title='Edit']"
-155.Upload Driving Iicense, uploadfile, "src/main/resources/test-data/license.jpg", "//input[@type='file']"
-156.Enter Expiry Date,type,12-12-2026,"//input[@placeholder='DD/MM/YYYY']"
-157.Click Submit, click, , "//button[normalize-space()='Submit']"
-158.Verify Updated Succesfully, verify, , "//div[@aria-label='Updated Successfully']"
-159.Click Approve Driver,click,,"//i[@title='Approve']"
-160.Verify Updated Succesfully, verify, , "//div[@aria-label='Updated Successfully']"
-161.Click drivers menu,click,,"//i[contains(@class,'fa-motorcycle fa-solid iconstyle')]"
-162.Click drivers menu,click,,"//i[contains(@class,'fa-motorcycle fa-solid iconstyle')]"
-163.Click Approved Drivers,click,,"//span[normalize-space()='Approved Drivers']"
-164.Approved Drivers List,verify,,"//div[contains(text(),'Approved Drivers List')]"
-165.Filter Approved Driver,type,{busDriverName},"//input[@aria-label='Driver Name Filter Input']"
-166.Click Transports Services Icon,click,,"//i[@class='fa-motorcycle fa-solid iconstyle']"
-167.Click Transports Services Menu,click,,"//h2[normalize-space()='Transport Services']"
-168.Verify Transport Services,verify,,"//div[normalize-space()='TRANSPORT SERVICES']"
-169.Filter Services List,type,{transportName},"//input[@aria-label='Services Filter Input']"
-170.Click Edit Icon ,click,,"//i[@title='Edit']"
-171.wait,2000,,
-172.Scroll Grid, tab, 5, "//input[@placeholder='Service Name']"
-173.wait,2000,,
-174.Open status Dropdown,click,,"//label[contains(., 'Status')]/following-sibling::p-dropdown"
-175.Select Deactivate,click,,"//li[@aria-label='Deactivate']"
-176.Click  Submit,click,,"//button[normalize-space()='Submit']"
-177.Verify Sucess, verify, , "//div[@aria-label='Info']"
-178.wait,2000,,</t>
   </si>
   <si>
     <t>1.Click badge,click,,"//i[contains(@class, 'fa-user-shield')]"
@@ -2745,86 +2565,6 @@
 4.Load Dashboard,wait_until_visible,,"web.global.dashboard.statistics_header"</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click Dashboard Icon,click,,"web.global.menu.dashboard"
-2. Click Setting menu,click,,"web.global.menu.settings"
-3. Click City area menu,click,,"admin.menu.city_area"
-4. Wait For Area List,wait_until_visible,,"admin.city_area.list_heading"
-5. Click Add City Area button,click,,"admin.city_area.btn_add"
-6. Wait For City Area heading,wait_until_visible,,"admin.city_area.add_heading"
-7. Enter Area Name,type,triplicane_{timestamp} &gt;&gt; areaName,"admin.city_area.input_name"
-8. Open Status Dropdown,click,,"admin.city_area.dropdown_status"
-9. Select Active,click,,"admin.city_area.select_status_active"
-10. Enter City Area,type,triplicane,"admin.city_area.input_search_location"
-11. wait,1000,,
-12. Select First Option,arrow_down,,"admin.city_area.input_search_location"
-13. Confirm Option,press_enter,,"admin.city_area.input_search_location"
-14. wait,1000,,
-15. Map Polygon,draw polygon,"-120;-120 : 120;-120 : 120;120 : -120;120 : -120;-120","//div[@class='ol-layer']//canvas"
-16. Click Submit,click,,"web.global.action.submit"
-17. Wait For Success Message,wait_until_visible,,"web.global.toast.success"
-18. Click Transport Services,click,,"admin.transport.card_link"
-19. Wait For Transport Page,wait_until_visible,,"admin.transport.page_heading"
-20. Click Add Category,click,,"admin.transport.btn_add_category"
-21. Open Select City Dropdown,click,,"admin.transport.dropdown_city_multiselect"
-22. Search City Area,type,{areaName},"admin.transport.input_filter_city"
-23. Verify Area in Dropdown,verify,,"admin.transport.select_filtered_option"
-24. Click close,click,,"web.global.action.close"
-25.Click Dashboard Icon,click,,"web.global.menu.dashboard"
-26. Click Setting menu,click,,"web.global.menu.settings"
-27. Click City admin menu,click,,"admin.menu.city_admin"
-28. Wait For City Admin List,wait_until_visible,,"admin.city_admin.list_heading"
-29. Click Add City Admin button,click,,"admin.city_admin.btn_add"
-30. Open Select City Dropdown,click,,"admin.city_admin.select_city_dropdown"
-31. Select {areaName},click,,"admin.city_admin.select_dynamic_option"
-32. Verify Selection,verify,,"admin.city_admin.verify_dropdown_value"
-</t>
-  </si>
-  <si>
-    <t>1. Click Dashboard Icon,click,,"web.global.menu.dashboard"
-2. Click Setting menu,click,,web.global.menu.settings
-3. Click City admin menu,click,,admin.menu.city_admin
-4. Wait For City Admin List,wait_until_visible,,admin.city_admin.list_heading
-5. Click Add City Admin button,click,,admin.city_admin.btn_add
-6. Wait For Admin heading,wait_until_visible,,admin.city_admin.add_heading
-7.Select Name field,click,,admin.city_admin.input_name
-8. Enter Admin Name,type,faizal{randomAlpha} &gt;&gt; adminName,admin.city_admin.input_name
-9.Select Email field,click,,admin.city_admin.input_email
-10. Enter Email,type,faizal_{timestamp}@gmail.com,admin.city_admin.input_email
-11.select the password field,click,,admin.city_admin.input_password
-12.Enter the Password as "faizal@123",type,faizal@123,admin.city_admin.input_password
-13.Open Select City Dropdown,click,,admin.city_admin.select_city_dropdown
-14.Select {areaName},click,,admin.city_admin.select_dynamic_option
-15. Click on the "Transport Service" → "Auto Ride" checkbox,click,,admin.city_admin.chk_transport_autoride
-16.Click on the "Customers" → "Add Customers" checkbox,click,,admin.city_admin.chk_customer_add
-17.Click on the "Customers" → "Verified Customers"checkbox,click,,admin.city_admin.chk_customer_verified
-18.Click on the "Customers" → "Non Verified Customers" checkbox,click,,admin.city_admin.chk_customer_unverified
-19.Click on the "Customers" → "Blocked Customers" checkbox,click,,admin.city_admin.chk_customer_blocked
-20.Click on the "Customers" → "Deleted Customers" checkbox,click,,admin.city_admin.chk_customer_deleted
-21.Click on the "Customers" → "Pending Customers" checkbox,click,,admin.city_admin.chk_customer_pending
-22.Click on the "Providers" → "Transport Providers List" checkbox,click,,admin.city_admin.chk_provider_list
-23.Click on the "Drivers" → "Add Driver" checkbox,click,,admin.city_admin.chk_driver_add
-24.Click on the "Drivers" → "Approved Drivers" checkbox,click,,admin.city_admin.chk_driver_approved
-25.Click on the "Drivers" → "Un-Approved Drivers" checkbox,click,,admin.city_admin.chk_driver_unapproved
-26.Click on the "Drivers" → "Blocked Drivers" checkbox,click,,admin.city_admin.chk_driver_blocked
-27.Click on the "Drivers" → "Reject Drivers" checkbox,click,,admin.city_admin.chk_driver_rejected
-28.Click on the "Drivers" → "Deleted Drivers" checkbox,click,,admin.city_admin.chk_driver_deleted
-29.Click on the "Subscription Plan" → "Driver Subscription Plan" checkbox,click,,admin.city_admin.chk_subscription_plan
-30.Click on the "Cash Out" → "Driver Cash Out" checkbox,click,,admin.city_admin.chk_cashout
-31.Click on the "Report Issue" → "Customer Report Issues" checkbox,click,,admin.city_admin.chk_report_customer
-32.Click on the "Report Issue" → "Driver Report Issues" checkbox,click,,admin.city_admin.chk_report_driver
-33.Click on the "Report Issue" → "Provider Report Issues" checkbox,click,,admin.city_admin.chk_report_provider
-34.Click on the "Report Issue" → "Report issue settings" checkbox,click,,admin.city_admin.chk_report_settings
-35.Click on the "Report Issue" → "FAQs" checkbox,click,,admin.city_admin.chk_report_faqs
-36.Click on the "Website Settings" → "Header &amp; Footer Settings" checkbox,click,,admin.city_admin.chk_web_header_footer
-37.Click on the "Website Settings" → "Home Page Settings" checkbox,click,,admin.city_admin.chk_web_homepage
-38.Click on the "Website Settings" → "Delivery Settings" checkbox,click,,admin.city_admin.chk_web_delivery
-39.Click on the "Website Settings" → "Transport Settings" checkbox,click,,admin.city_admin.chk_web_transport
-40.Click on the "Website Settings" → "FAQs" checkbox,click,,admin.city_admin.chk_web_faqs
-41.Click Submit,click,,web.global.login.submit_btn
-42. Wait For Success Message,wait_until_visible,,web.global.toast.info
-43.Filter admin name,type,{adminName},admin.city_admin.input_name_filter</t>
-  </si>
-  <si>
     <t>1. Click Dashboard Icon,click,,"web.global.menu.dashboard"
 2. Click Customer Icon,click,,"admin.menu.customer_icon"
 3. Click Add Customers,click,,"admin.menu.add_customers"
@@ -3109,6 +2849,282 @@
     <t>7.Select Auto Ride Option,click,,"//span[normalize-space()='Auto Ride']"
 8.Wait for Auto Ride,wait_until_visible,,"//label[contains(.,'Driver Services')]/following-sibling::mat-checkbox"
 9.Click Auto Ride, click, , "//label[contains(.,'Driver Services')]/following-sibling::mat-checkbox"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+2. Click Setting menu,click,,"web.global.menu.settings"
+3. Click City area menu,click,,"admin.menu.city_area"
+4. Wait For Area List,wait_until_visible,,"admin.city_area.list_heading"
+5. Click Add City Area button,click,,"admin.city_area.btn_add"
+6. Wait For City Area heading,wait_until_visible,,"admin.city_area.add_heading"
+7. Enter Area Name,type,triplicane_{timestamp} &gt;&gt; areaName,"admin.city_area.input_name"
+8. Open Status Dropdown,click,,"admin.city_area.dropdown_status"
+9. Select Active,click,,"admin.city_area.select_status_active"
+10. Enter City Area,type,triplicane,"admin.city_area.input_search_location"
+11. wait,1000,,
+12. Select First Option,arrow_down,,"admin.city_area.input_search_location"
+13. Confirm Option,press_enter,,"admin.city_area.input_search_location"
+14. wait,1000,,
+15. Map Polygon,draw polygon,"-120;-120 : 120;-120 : 120;120 : -120;120 : -120;-120","//div[@class='ol-layer']//canvas"
+16. Click Submit,click,,"web.global.action.submit"
+17. Wait For Success Message,wait_until_visible,,"web.global.toast.success"
+18. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+19. Click Transport Services,click,,"admin.transport.menu.card"
+20. Wait For Transport Page,wait_until_visible,,"admin.transport.page.header"
+21. Click Add Category,click,,"admin.transport.add_category.btn"
+22. Open Select City Dropdown,click,,"admin.transport.city.dropdown"
+23. Search City Area,type,{areaName},"admin.transport.input_filter_city"
+24. Verify Area in Dropdown,verify,,"admin.transport.city.dynamic_option"
+25. Click close,click,,"web.global.action.close"
+26.Click Dashboard Icon,click,,"web.global.menu.dashboard"
+27. Click Setting menu,click,,"web.global.menu.settings"
+28. Click City admin menu,click,,"admin.menu.city_admin"
+29. Wait For City Admin List,wait_until_visible,,"admin.city_admin.list_heading"
+30. Click Add City Admin button,click,,"admin.city_admin.btn_add"
+31. Open Select City Dropdown,click,,"admin.city_admin.select_city_dropdown"
+32. Select {areaName},click,,"admin.city_admin.select_dynamic_option"
+33. Verify Selection,verify,,"admin.city_admin.verify_dropdown_value"
+</t>
+  </si>
+  <si>
+    <t>Removed Test Cases</t>
+  </si>
+  <si>
+    <t>21.Click on the "Customers" → "Pending Customers" checkbox,click,,admin.city_admin.chk_customer_pending
+35.Click on the "Website Settings" → "Header &amp; Footer Settings" checkbox,click,,admin.city_admin.chk_web_header_footer
+36.Click on the "Website Settings" → "Home Page Settings" checkbox,click,,admin.city_admin.chk_web_homepage
+37.Click on the "Website Settings" → "Delivery Settings" checkbox,click,,admin.city_admin.chk_web_delivery
+38.Click on the "Website Settings" → "Transport Settings" checkbox,click,,admin.city_admin.chk_web_transport
+39.Click on the "Website Settings" → "FAQs" checkbox,click,,admin.city_admin.chk_web_faqs</t>
+  </si>
+  <si>
+    <t>1. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+2. Click Setting menu,click,,"web.global.menu.settings"
+3. Click City admin menu,click,,"admin.menu.city_admin"
+4. Wait For City Admin List,wait_until_visible,,"admin.city_admin.list_heading"
+5. Click Add City Admin button,click,,"admin.city_admin.btn_add"
+6. Wait For Admin heading,wait_until_visible,,"admin.city_admin.add_heading"
+7.Select Name field,click,,"admin.city_admin.input_name"
+8. Enter Admin Name,type,faizal{randomAlpha} &gt;&gt; adminName,"admin.city_admin.input_name"
+9.Select Email field,click,,"admin.city_admin.input_email"
+10. Enter Email,type,faizal_{timestamp}@gmail.com,"admin.city_admin.input_email"
+11.select the password field,click,,"admin.city_admin.input_password"
+12.Enter the Password as "faizal@123",type,faizal@123,"admin.city_admin.input_password"
+13.Open Select City Dropdown,click,,"admin.city_admin.select_city_dropdown"
+14.Select {areaName},click,,"admin.city_admin.select_dynamic_option"
+15. Click on the "Transport Service" → "Auto Ride" checkbox,click,,"admin.city_admin.chk_transport_autoride"
+16.Click on the "Customers" → "Add Customers" checkbox,click,,"admin.city_admin.chk_customer_add"
+17.Click on the "Customers" → "Verified Customers"checkbox,click,,"admin.city_admin.chk_customer_verified"
+18.Click on the "Customers" → "Non Verified Customers" checkbox,click,,"admin.city_admin.chk_customer_unverified"
+19.Click on the "Customers" → "Blocked Customers" checkbox,click,,"admin.city_admin.chk_customer_blocked"
+20.Click on the "Customers" → "Deleted Customers" checkbox,click,,"admin.city_admin.chk_customer_deleted"
+21.Click on the "Providers" → "Transport Providers List" checkbox,click,,"admin.city_admin.chk_provider_list"
+22.Click on the "Drivers" → "Add Driver" checkbox,click,,"admin.city_admin.chk_driver_add"
+23.Click on the "Drivers" → "Approved Drivers" checkbox,click,,"admin.city_admin.chk_driver_approved"
+24.Click on the "Drivers" → "Un-Approved Drivers" checkbox,click,,"admin.city_admin.chk_driver_unapproved"
+25.Click on the "Drivers" → "Blocked Drivers" checkbox,click,,"admin.city_admin.chk_driver_blocked"
+26.Click on the "Drivers" → "Reject Drivers" checkbox,click,,"admin.city_admin.chk_driver_rejected"
+27.Click on the "Drivers" → "Deleted Drivers" checkbox,click,,"admin.city_admin.chk_driver_deleted"
+28.Click on the "Subscription Plan" → "Driver Subscription Plan" checkbox,click,,"admin.city_admin.chk_subscription_plan"
+29.Click on the "Cash Out" → "Driver Cash Out" checkbox,click,,"admin.city_admin.chk_cashout"
+30.Click on the "Report Issue" → "Customer Report Issues" checkbox,click,,"admin.city_admin.chk_report_customer"
+31.Click on the "Report Issue" → "Driver Report Issues" checkbox,click,,"admin.city_admin.chk_report_driver"
+32.Click on the "Report Issue" → "Provider Report Issues" checkbox,click,,"admin.city_admin.chk_report_provider"
+33.Click on the "Report Issue" → "Report issue settings" checkbox,click,,"admin.city_admin.chk_report_settings"
+34.Click on the "Report Issue" → "FAQs" checkbox,click,,"admin.city_admin.chk_report_faqs"
+35.Click Submit,click,,"web.global.login.submit_btn"
+36. Wait For Success Message,wait_until_visible,,"web.global.toast.info"
+37.Filter admin name,type,{adminName},"admin.city_admin.input_name_filter"</t>
+  </si>
+  <si>
+    <t>Test Steps Deleted</t>
+  </si>
+  <si>
+    <t>111.Click Settings ,click,, "admin.transport.menu.settings"
+112.Click Customer Loyalty Settings,click,, "admin.transport.loyalty.menu_item"
+113.Open status Allow Customer loyalty points,click,, "admin.transport.loyalty.status.dropdown"
+114.Open status Allow Customer loyalty points,click,, "admin.transport.loyalty.status.dropdown"
+115.Select ON,click,, "admin.transport.loyalty.status.on_option"
+116.Enter Minimum order amount for eligibility to redeem loyalty points, type, 100, "admin.transport.loyalty.min_redeem.input"
+117.Enter Loyalty points redeem per order (in %) (% of order amount), type, 10, "admin.transport.loyalty.pct_cap.input"
+118.Enter Loyalty points per default currency (for ex. $1 = 10 points), type, 5, "admin.transport.loyalty.ratio.input"
+119.Click Submit ,click,, "web.global.action.submit"
+120.Wait For Sucess, wait_until_visible, , "web.global.toast.info"</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2. Click Transports Services Menu,click,, "admin.transport.menu.card"
+3.Wait For Transport Services, wait_until_visible,, "admin.transport.page.header"
+4.Click  Add Category,click,, "admin.transport.add_category.btn"
+5.Enter Service Name, type, Bus Ride{randomAlpha}&gt;&gt;transportName, "admin.transport.name.input"
+6.Enter Service Name Arabic, type, رحلة بالحافلة, "admin.transport.name_ar.input"
+7.Enter Slug, type, Bus Ride, "admin.transport.slug.input"
+8.Upload Transport Service Image, uploadfile, "src/main/resources/test-data/bus.jpg", "admin.transport.image.file"
+9.wait,2000,,
+10.Open status Dropdown,click,, "admin.transport.status.dropdown"
+11.Select Activate,click,, "admin.transport.status.activate_option"
+12.Open Select City Dropdown,click,, "admin.transport.city.dropdown"
+13.Select {areaName},click,, "admin.transport.city.dynamic_option"
+14.Click  Submit,click,, "web.global.action.submit"
+15.Wait Till Sucess, wait_until_visible, , "web.global.toast.info"
+16.wait,2000,,
+17.Click  back,click,, "admin.transport.back.btn"
+18. Click Dashboard Icon,click,, "web.global.menu.dashboard"
+19.Click Transports Services Menu,click,, "admin.transport.menu.card"
+20.Filter Services List,type,{transportName}, "admin.transport.grid.name_filter"
+21.Click Home Icon ,click,, "admin.transport.home.icon"
+22.Click Settings ,click,, "admin.transport.menu.settings"
+23.Click Vehicle Type,click,, "admin.transport.settings.vehicle_type"
+24.Click Add Vehicle Type,click,, "admin.transport.vehicle.add_type.btn"
+25.Enter Vehicle Type Name, type, volvo{randomAlpha}&gt;&gt;busTypeName, "admin.transport.vehicle.name.input"
+26.Enter Base Fare, type, 150, "admin.transport.vehicle.base_fare.input"
+27.Enter Base Fare Max Kilometer, type, 10, "admin.transport.vehicle.base_km.input"
+28.Open Extra Distance Fare Dropdown,click,, "admin.transport.vehicle.extra_fare_type.dropdown"
+29.Select Amount,click,, "admin.transport.status.amount_option"
+30.Enter Extra Distance Fare , type, 10, "admin.transport.vehicle.extra_fare.input"
+31.Enter Free Waiting Time , type, 10, "admin.transport.vehicle.waiting_free.input"
+32.Open Waiting Charge Dropdown,click,, "admin.transport.vehicle.waiting_type.dropdown"
+33.Select Amount,click,, "admin.transport.status.amount_option"
+34.Enter Waiting Rate , type, 10, "admin.transport.vehicle.waiting_rate.input"
+35.Enter Included Trip Waiting , type, 10, "admin.transport.vehicle.trip_waiting_free.input"
+36.Open Trip Waiting Charge Dropdown,click,, "admin.transport.vehicle.trip_waiting_type.dropdown"
+37.Select Amount,click,, "admin.transport.status.amount_option"
+38.Enter Trip Waiting Rate , type,50, "admin.transport.vehicle.trip_waiting_rate.input"
+39.Enter Free Pickup Distance , type,5, "admin.transport.vehicle.pickup_free.input"
+40.Open Pickup Charge Dropdown,click,, "admin.transport.vehicle.pickup_type.dropdown"
+41.Select Amount,click,, "admin.transport.status.amount_option"
+42.Enter Pickup Fee, type,50, "admin.transport.vehicle.pickup_fee.input"
+43.Open Customer Fee  Dropdown,click,, "admin.transport.vehicle.customer_type.dropdown"
+44.Select Amount,click,, "admin.transport.status.amount_option"
+45.Enter Customer Fee, type,50, "admin.transport.vehicle.customer_fee.input"
+46.Open Customer GST  Dropdown,click,, "admin.transport.vehicle.customer_gst_type.dropdown"
+47.Select Amount,click,, "admin.transport.status.amount_option"
+48.Enter  GST amount, type,50, "admin.transport.vehicle.customer_gst.input"
+49.Open Driver Fee  Dropdown,click,, "admin.transport.vehicle.driver_type.dropdown"
+50.Select Amount,click,, "admin.transport.status.amount_option"
+51.Enter  Driver Fee, type,50, "admin.transport.vehicle.driver_fee.input"
+52.Open Driver GST  Dropdown,click,, "admin.transport.vehicle.driver_gst_type.dropdown"
+53.Select Amount,click,, "admin.transport.status.amount_option"
+54.Enter Driver Gst,type,50, "admin.transport.vehicle.driver_gst.input"
+55.Open Status Dropdown,click,, "admin.transport.vehicle.status.dropdown"
+56.Select Active,click,, "admin.transport.status.active_option"
+57.Upload Vehicle Image, uploadfile, "src/main/resources/test-data/volvo.jpg", "admin.transport.vehicle.image.file"
+58.Enter Notifiacation,type,50, "admin.transport.vehicle.notify_km.input"
+59.Enter Driver Request ETA,type,50, "admin.transport.vehicle.eta_limit.input"
+60.Enter Driver Request KM,type,50, "admin.transport.vehicle.km_limit.input"
+61.Open Night Charge Timing Status Dropdown,click,, "admin.transport.night.status.dropdown"
+62.Select Active,click,, "admin.transport.status.active_option"
+63.Click Surcharge Time Checkbox, click, , "admin.transport.night.everyday.checkbox"
+64.Enter From Time, type, 100000AM, "admin.transport.night.from_time.input"
+65.Enter To Time, type, 220000PM, "admin.transport.night.to_time.input"
+66.Open  Dropdown,click,, "admin.transport.night.type.dropdown"
+67.Select Amount,click,, "admin.transport.status.amount_option"
+68.Enter  Price, type,50, "admin.transport.night.price.input"
+69.Click  Submit,click,, "web.global.action.submit"
+70.Wait For Sucess,wait_until_visible, , "web.global.toast.info"
+71.Click Settings ,click,, "admin.transport.menu.settings"
+72.Click Promocode,click,, "admin.transport.promo.menu_item"
+73.Click Add Promo Code ,click,, "admin.transport.promo.add.btn"
+74.Open User List Dropdown,click,, "admin.transport.promo.user_list.dropdown"
+75.Select User,click,, "admin.transport.promo.user_option"
+76.Click Code Name Box,click,, "admin.transport.promo.codename.input"
+77.Enter Code Name, type, promoCode{randomAlpha}&gt;&gt; promoCodeName, "admin.transport.promo.codename.input"
+78.Open Discout Type Dropdown,click,, "admin.transport.promo.discount_type.dropdown"
+79.Select Discout Type,click,, "admin.transport.promo.discount_type.amount_option"
+80.Enter Expiry Date,type,12122026, "admin.transport.promo.expiry.input"
+81.Enter Discount Amount, type, 100, "admin.transport.promo.amount.input"
+82.Enter Minimum Order Amount, type, 1000, "admin.transport.promo.min_order.input"
+83.Enter Maximum Discount Amount, type, 100, "admin.transport.promo.max_discount.input"
+84.Enter Coupon Limit, type, 5, "admin.transport.promo.coupon_limit.input"
+85.Enter Usage Limit for One User, type, 2, "admin.transport.promo.user_limit.input"
+86.Enter Promo Code Description, type, Promo Dode For Gold Member, "admin.transport.promo.desc.textarea"
+87.Click Submit ,click,, "web.global.action.submit"
+88.Wait For Sucess, wait_until_visible, , "web.global.toast.info"
+89.wait,2000,,
+90.Click Settings ,click,, "admin.transport.menu.settings"
+91.Click Service Settings ,click,, "admin.transport.rules.menu_item"
+92.Enter Driver Accept Timeout, type, 60, "admin.transport.rules.timeout.input"
+93.Enter Driver Serach Radius, type, 50, "admin.transport.rules.radius.input"
+94.Click Submit ,click,, "web.global.action.submit"
+95.Wait For Sucess, wait_until_visible, , "web.global.toast.info"
+96.wait,1000,,
+97.Click Settings ,click,, "admin.transport.menu.settings"
+98.Click Requirment Document ,click,, "admin.transport.docs.menu_item"
+99.Click Add Document ,click,, "admin.transport.docs.add.btn"
+100.Enter Name, type, documet{randomAlpha}&gt;&gt; documentName, "admin.transport.docs.name.input"
+101.Open status Dropdown,click,, "admin.transport.docs.status.dropdown"
+102.Select Active,click,, "admin.transport.status.active_option"
+103.Click Document Expiry ,click,, "admin.transport.docs.expiry.checkbox"
+104.Click Mandatory Document ,click,, "admin.transport.docs.mandatory.checkbox"
+105.Click  Require Proof Number,click,, "admin.transport.docs.proof_no.checkbox"
+106.Enter Display Order, type, 10, "admin.transport.docs.order.input"
+107.Click Submit ,click,, "web.global.action.submit"
+108.Wait For Sucess, wait_until_visible, , "web.global.toast.info"
+109.Filter Document List,type,{documentName}, "admin.transport.docs.grid.name_filter"
+110.wait,1000,,
+111. Click Dashboard Icon,click,, "web.global.menu.dashboard"
+112.Click drivers menu,click,, "admin.drivers.menu.icon"
+113.Click Add Driver menu,click,, "admin.drivers.add_menu.link"
+114.Wait For Add Driver, wait_until_visible,, "admin.drivers.add_page.header"
+115.Click Service Category Dropdown,click,, "admin.drivers.service_dropdown.select"
+116.Select Bus Ride Option,click,, "admin.transport.dropdown.dynamic_service"
+117.Enter Driver Name, type, busdriver_{timestamp} &gt;&gt; busDriverName, "admin.drivers.fullname.input"
+118.Enter Email, type, busdriver_{timestamp}@gmail.com&gt;&gt;busEmail, "admin.drivers.email.input"
+119.Enter Contact Number, type, {randomPhone}&gt;&gt;busPhone, "admin.drivers.phone.input"
+120.Click Whatspp,click,, "admin.drivers.whatsapp.checkbox"
+121.Enter Whatspp Number,type,{busPhone}, "admin.drivers.whatsapp_phone.input"
+122.Upload Profile Image, uploadfile, "src/main/resources/test-data/busdriver.jpg", "admin.drivers.profile_image.file"
+123.Select Source,click,, "admin.drivers.source_dropdown.select"
+124.Select Instagram,click,, "admin.drivers.instagram_option.span"
+125.Select Male Gender, click, , "admin.drivers.male_gender.div"
+126.Click Vehicle Type Dropdown,click,, "admin.drivers.vehicle_dropdown.select"
+127.Select  volvo Option,click,, "admin.transport.dropdown.dynamic_vehicle"
+128.Enter Model Year, type, 2013, "admin.drivers.modelyear.input"
+129.Enter Plate No, type, KL-01-AB-1634, "admin.drivers.plateno.input"
+130. Enter Model Name, type, deisel, "admin.drivers.modelname.input"
+131.Upload Vehicle Image, uploadfile, "src/main/resources/test-data/busvolvo.jpeg", "admin.drivers.vehicle_image.file"
+132.Enter Bank Name, type, HDFC Bank, "admin.drivers.bankname.input"
+133.Enter Bank Location, type, Chennai, "admin.drivers.banklocation.input"
+134.Enter Account Number, type, 50100123456789, "admin.drivers.accountno.input"
+135.Enter Account Holder Name, type, {busDriverName}, "admin.drivers.accountholder.input"
+136.Enter Payment Email Address, type, {busEmail}, "admin.drivers.paymentemail.input"
+137.Enter IFSC Code, type, HDFC0001234, "admin.drivers.ifsc.input"
+138.Click Submit, click, , "web.global.action.submit"
+139.Wait For Driver Added,wait_until_visible, , "web.global.toast.success"
+140.Wait for Toast to hide, wait, 1000,
+141. Click Dashboard Icon,click,, "web.global.menu.dashboard"
+142.Click drivers menu,click,, "admin.drivers.menu.icon"
+143.Click Pending Documents,click,, "admin.drivers.pending_docs.link"
+144.Filter by Name,type,{busDriverName}, "admin.drivers.name_filter.input"
+145.Scroll Grid, tab, 7, "admin.drivers.name_filter.input"
+146.Click Doc Icon,click,, "admin.drivers.docs.icon"
+147.Driver Required Documents,verify,, "admin.drivers.required_docs.header"
+148.FilterDocumet List,type,{documentName}, "admin.drivers.docs_filter.input"
+149.Add Driving License,click,, "admin.drivers.docs.edit_icon"
+150.Upload Driving Iicense, uploadfile, "src/main/resources/test-data/license.jpg", "admin.drivers.profile_image.file"
+151.Enter Expiry Date,type,12-12-2026, "admin.drivers.doc_expiry.input"
+152.Click Submit, click, , "web.global.action.submit"
+153.Wait For Updated Succesfully, wait_until_visible, , "web.global.toast.updated"
+154.Click Approve Driver,click,, "admin.drivers.docs.approval"
+155.Verify Updated Succesfully, verify, , "web.global.toast.updated"
+156. Click Dashboard Icon,click,, "web.global.menu.dashboard"
+157.Click drivers menu,click,, "admin.drivers.menu.icon"
+158.Click Approved Drivers,click,, "admin.drivers.approved_docs.link"
+159.Wait For Approved Drivers List, wait_until_visible,, "admin.drivers.approved_page.header"
+160.Filter Approved Driver,type,{busDriverName}, "admin.drivers.name_filter.input"
+161.Click Transports Services Icon,click,, "admin.drivers.menu.icon"
+162.Click Transports Services Menu,click,, "admin.transport.menu.card"
+163.Wait For Transport Services, wait_until_visible,, "admin.transport.page.header"
+164.Filter Services List,type,{transportName}, "admin.transport.grid.name_filter"
+165.Click Edit Icon ,click,, "admin.drivers.docs.edit_icon"
+166.wait,2000,,
+167.Scroll Grid, tab, 5, "admin.transport.name.input"
+168.wait,2000,,
+169.Open status Dropdown,click,, "admin.transport.status.dropdown"
+170.Select Deactivate,click,, "admin.transport.status.deactivate_option"
+171.Click  Submit,click,, "web.global.action.submit"
+172.Wait For Sucess, wait_until_visible, , "web.global.toast.info"
+173.wait,2000,,</t>
   </si>
 </sst>
 </file>
@@ -3534,7 +3550,7 @@
         <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>37</v>
@@ -3603,13 +3619,13 @@
         <v>27</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>46</v>
@@ -3675,7 +3691,7 @@
         <v>30</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>31</v>
@@ -3747,13 +3763,13 @@
         <v>32</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>46</v>
@@ -3819,13 +3835,13 @@
         <v>55</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>58</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>59</v>
@@ -3891,7 +3907,7 @@
         <v>35</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>36</v>
@@ -3963,7 +3979,7 @@
         <v>41</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>57</v>
@@ -4035,13 +4051,13 @@
         <v>71</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>73</v>
@@ -4101,19 +4117,19 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>67</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>68</v>
@@ -4188,7 +4204,7 @@
         <v>53</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>42</v>
@@ -4264,7 +4280,7 @@
         <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>42</v>
@@ -4296,7 +4312,7 @@
     <col min="4" max="4" width="34.77734375" customWidth="1"/>
     <col min="5" max="5" width="64" customWidth="1"/>
     <col min="6" max="6" width="32.6640625" customWidth="1"/>
-    <col min="7" max="7" width="17.5546875" customWidth="1"/>
+    <col min="7" max="7" width="44.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -4319,7 +4335,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4339,10 +4355,13 @@
         <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>38</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -4384,7 +4403,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4398,19 +4417,19 @@
         <v>14</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4459,7 +4478,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4473,19 +4492,19 @@
         <v>15</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>44</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4534,7 +4553,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4548,19 +4567,19 @@
         <v>17</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>45</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4576,7 +4595,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4DB4E5D-EBF5-4B6A-BF83-7934D70C5535}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C5E7D15-8F85-42A0-A3E4-72E2C74068F3}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4586,7 +4605,7 @@
     <col min="4" max="4" width="34.109375" customWidth="1"/>
     <col min="5" max="5" width="69.33203125" customWidth="1"/>
     <col min="6" max="6" width="38" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="7" max="7" width="61.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -4609,7 +4628,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>6</v>
+        <v>111</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4623,16 +4642,19 @@
         <v>61</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>64</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>63</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4690,22 +4712,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC13A97E-358D-43E7-AB26-196297D4DAE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A2782A3-6539-4CC8-BB61-AFA4B194CB16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>
@@ -26,9 +26,9 @@
     <sheet name="StoreOperations" sheetId="42" r:id="rId11"/>
     <sheet name="StoreStatusManagement" sheetId="43" r:id="rId12"/>
     <sheet name="DeliveryServiceCompleteTest" sheetId="44" r:id="rId13"/>
-    <sheet name="AddProvider" sheetId="11" r:id="rId14"/>
-    <sheet name="ProviderServiceCompleteTest" sheetId="12" r:id="rId15"/>
-    <sheet name="SubscriptionPlanTest" sheetId="29" r:id="rId16"/>
+    <sheet name="AddProvider" sheetId="45" r:id="rId14"/>
+    <sheet name="ProviderServiceCompleteTest" sheetId="46" r:id="rId15"/>
+    <sheet name="SubscriptionPlanTest" sheetId="47" r:id="rId16"/>
     <sheet name="DataCleanUpSheet" sheetId="28" r:id="rId17"/>
   </sheets>
   <calcPr calcId="162913"/>
@@ -898,111 +898,6 @@
     <t>Validate the end-to-end creation of a Customer.</t>
   </si>
   <si>
-    <t xml:space="preserve">1.Click badge,click,,"//i[contains(@class, 'fa-user-secret')]"
-2.Click Delivery Services,click,,"//h2[contains(text(), 'Provider Services')]"
-3.Verify Delivery Services,verify,,"//div[contains(text(),'ON-DEMAND SERVICES')]"
-4.Filter service List,type,Plumbers,"//input[@aria-label='Services Filter Input']"
-5.Click Home Icon Plumbers,click,,"//div[@role='row'][.//span[text()='Plumbers']]//i[@title='Home']"
-6.Verify Plumbers Summary,verify,,"//div[contains(text(),'Plumbers Summary')]"
-7.Click  Providers,click,,"//button[contains(., 'Providers')]"
-8.Select Add Providers,click,,"//div[contains(text(), 'Add Providers')]"
-9.Verify Add Provider,verify,,"//h1[text()=' Add Provider ']"
-10.Enter Provider Full Name, type, Plumber{randomAlpha}&gt;&gt; plumberName, "//input[@placeholder='Provider Full Name']"
-11.Upload Plumber Image, uploadfile, "src/main/resources/test-data/plumber.jpg", "//input[@type='file']"
-12.Enter Email, type, Plumber_{timestamp}@gmail.com&gt;&gt;plumberEmail, "//input[@placeholder='Unique Email']"
-13.Enter Contact Number, type, {randomPhone}, "//input[@placeholder='Unique Contact Number']"
-14.Enter Landmark, type, Near LIC Building, "//input[@placeholder='Provider Landmark']"
-15.Open Delivery Radius Dropdown,click,,"//select[@formcontrolname='serviceRadius']"
-16.Select Twenty Five Kilometer,click,,"//option[text()='25 KM']"
-17.Enter Minimum Order, type, 10, "//input[@placeholder='Minimum Order']"
-18.Enter Provider Address, type, plumber chennai, "//input[@placeholder='Enter provider Address']"
-19.wait,1000,,
-20.Select First Option,arrow_down,,"//input[@placeholder='Enter provider Address']"
-21.Confirm Option,press_enter,,"//input[@placeholder='Enter provider Address']"
-22.wait,1000,,
-23.Click Everyday Checkbox, click, , "//span[text()='EveryDay']/preceding-sibling::input"
-24.Click 09:00 AM-10:00 AM, click, , "//button[normalize-space()='09:00 AM-10:00 AM']"
-25.Click 10:00 AM-11:00 AM, click, , "//button[normalize-space()='10:00 AM-11:00 AM']"
-26.Click 11:00 AM-12:00 PM, click, , "//button[normalize-space()='11:00 AM-12:00 PM']"
-27.Click 12:00 PM-01:00 PM, click, , "//button[normalize-space()='12:00 PM-01:00 PM']"
-28.Click 02:00 PM-03:00 PM, click, , "//button[normalize-space()='02:00 PM-03:00 PM']"
-29.Click 03:00 PM-04:00 PM, click, , "//button[normalize-space()='03:00 PM-04:00 PM']"
-30.Enter Bank Name, type, federal, "//input[@placeholder='Bank Name']"
-31.Enter Bank Location,type, chennai, "//input[@placeholder='Bank Location(City Name)']"
-32.Scroll Grid, tab, 1, "//input[@placeholder='Bank Location(City Name)']"
-33.Enter Account Number, type, 123456789012, "//input[@placeholder='Account Number']"
-34.Enter Accont Holder Name, type, {plumberName}, "//input[@placeholder='Account Holder Name']"
-35.Enter Payment Email Address, type, {plumberEmail}, "//input[@placeholder='Email Address for Payment Notification']"
-36.Enter BIC Code, type, 1234, "//input[@placeholder='BIC Code']"
-37.Click Save, click, , "//button[@type='submit']"
-38.Verify Sucess, verify, , "//div[@aria-label='Info']"
-39.Filter Plumber List,type,{plumberName},"//input[@aria-label='Provider Name Filter Input']"
-40.Click  Providers,click,,"//button[contains(., 'Providers')]"
-41.Select Pending Document Providers,click,,"//div[normalize-space()='Pending Document Providers']"
-42.Filter Plumber List,type,{plumberName},"//input[@aria-label='Provider Name Filter Input']"
-43.Click Document Icon,click,,"//i[@class='bi bi-file-earmark-text cursor-pointer gridIcon Navigate']"
-44. Provider Required Documents,verify,,"//div[contains(text(),'Documents')]"
-45.FilterDocumet List,type,Store Address,"//input[@aria-label='Document Name Filter Input']"
-46.Add Address Proof,click,,"(//i[contains(@class, 'Edit')])[1]"
-47.Upload Address Proof, uploadfile, "src/main/resources/test-data/addressproof.png", "//input[@type='file']"
-48.Enter Expiry Date,type,2026-12-12,"//input[@placeholder='YYYY/MM/DD']"
-49.Click Submit, click, , "//button[normalize-space()='Submit']"
-50.Verify Updated Succesfully, verify, , "//div[@aria-label='Updated Successfully']"
-51.FilterDocumet List,type,Store Address,"//input[@aria-label='Document Name Filter Input']"
-52.Click Approve Store,click,,"//div[@row-index='0']//i[contains(@class, 'bi-hand-thumbs-up-fill')]"
-53.Verify Updated Succesfully, verify, , "//div[@aria-label='Updated Successfully']"
-54.Click Back, click, , "//button[@class='buttonWidget']"
-55.Click  Providers,click,,"//button[contains(., 'Providers')]"
-56.Select Provider List,click,,"//div[normalize-space()='Provider List']"
-57.Verify Approved Provider,verify,,"//div[normalize-space()='Approved Plumbers Service Providers']"
-58.Filter Plumber List,type,{plumberName},"//input[@aria-label='Provider Name Filter Input']"
-59.Click Doc Icon,click,,"//i[@class='bi bi-file-earmark-text cursor-pointer gridIcon Navigate']"
-60.Click Eye Icon,click,,"//i[@class='bi bi-eye cursor-pointer gridIcon View']"
-61.Click Back, click, , "//button[@class='buttonWidget']"
-62.Verify Approved Provider,verify,,"//div[normalize-space()='Approved Plumbers Service Providers']"
-63.Filter Plumber List,type,{plumberName},"//input[@aria-label='Provider Name Filter Input']"
-64.Scroll Grid, tab, 11, "//input[@aria-label='Provider Name Filter Input']"
-65.Click Wallet Icon,click,,"//i[@class='bi bi-cash-stack cursor-pointer gridIcon Navigate']"
-66.Click Manage Transaction, click, , "//button[normalize-space()='Manage Transaction']"
-67.Enter Wallet Amount, type, 1000, "//input[@placeholder='Enter Wallet Amount']"
-68.Open Choose Option Dropdown,click,,"//label[contains(.,'Choose Option')]/following-sibling::p-dropdown/div"
-69.Select Add Money,click,,"//li[@role='option' and @aria-label='Add Money']"
-70.Click Submit, click, , "//button[normalize-space()='Submit']"
-71.Verify Saved Succesfully, verify, , "//div[@aria-label='Added Successfully']"
-72.Click Manage Transaction, click, , "//button[normalize-space()='Manage Transaction']"
-73.Enter Wallet Amount, type, 200, "//input[@placeholder='Enter Wallet Amount']"
-74.Open Choose Option Dropdown,click,,"//label[contains(.,'Choose Option')]/following-sibling::p-dropdown/div"
-75.Select Deduct Money,click,,"//li[@role='option'][contains(.,'Deduct Money')]"
-76.Click Submit, click, , "//button[normalize-space()='Submit']"
-77.Verify Saved Succesfully, verify, , "//div[@aria-label='Added Successfully']"
-78.Click Back, click, , "//button[normalize-space()='Back']"
-79.Filter Plumber List,type,{plumberName},"//input[@aria-label='Provider Name Filter Input']"
-80.Click Doc Icon,click,,"//i[@class='bi bi-file-earmark-text cursor-pointer gridIcon Navigate']"
-81.FilterDocumet List,type,Store Address,"//input[@aria-label='Document Name Filter Input']"
-82.Click Reject Document,click,,"//i[@class='bi bi-hand-thumbs-down-fill cursor-pointer gridIcon Modify']"
-83.Click Reject  Yes,click,,"//button[normalize-space()='Yes']"
-84.Rejection Reason,type,document insufficent,"//textarea[@id='swal2-textarea']"
-85..Click Reject  Yes,click,,"//button[normalize-space()='Yes']"
-86.Click Back, click, , "//button[@class='buttonWidget']"
-87.Filter Plumber List,type,{plumberName},"//input[@aria-label='Provider Name Filter Input']"
-88.Scroll Grid, tab, 13, "//input[@aria-label='Provider Name Filter Input']"
-89.Click Block Provider,click,,"//i[@title='Block Provider']"
-90.Click Block  Yes,click,,"//button[normalize-space()='Yes']"
-91. Blocking Reason,type,customer complaints,"//textarea[@id='swal2-textarea']"
-92.Click block  Yes,click,,"//button[normalize-space()='Yes']"
-93.Click  Providers,click,,"//button[contains(., 'Providers')]"
-94.Select Blocked Providers,click,,"//div[contains(text(), 'Blocked Providers')]"
-95.Verify Blocked Provider,verify,,"//div[normalize-space()='Blocked Plumbers Service Providers']"
-96.Filter Plumber List,type,{plumberName},"//input[@aria-label='Provider Name Filter Input']"
-97.Scroll Grid, tab, 12, "//input[@aria-label='Provider Name Filter Input']"
-98.Click Unblock Provider,click,,"//i[@class='bi bi-hand-thumbs-up-fill cursor-pointer gridIcon Modify']"
-99.Click  Providers,click,,"//button[contains(., 'Providers')]"
-100.Select Provider List,click,,"//div[contains(text(), 'Provider List')]"
-101.Filter Plumber List,type,{plumberName},"//input[@aria-label='Provider Name Filter Input']"
-102.wait,1000,,
-</t>
-  </si>
-  <si>
     <t>Add New Delivery Service &amp;  Category</t>
   </si>
   <si>
@@ -1381,150 +1276,6 @@
     </r>
   </si>
   <si>
-    <t>1.Click badge,click,,"//i[contains(@class, 'fa-user-secret')]"
-2.Click Provider Services,click,,"//h2[contains(text(), 'Provider Services')]"
-3.Verify Provider Services,verify,,"//div[normalize-space()='ON-DEMAND SERVICES']"
-4.Click  Add New Services,click,,"//button[normalize-space()='Add New Services']"
-5.Enter Service Name, type, Painter{randomAlpha}&gt;&gt; serviceName, "//input[@placeholder='Service Name']"
-6.Enter Service Name Tamil, type, பெயிண்டர், "//input[@placeholder='Service Name (in Tamil)']"
-7.Enter Service Name Arabic, type, دهان, "//input[@placeholder='Service Name (in Arabic)']"
-8.Enter Service Name Hindi, type, पेंटर, "//input[@placeholder='Service Name (in Hindi)']"
-9.Enter Slug, type, painter, "//input[@placeholder='Slug']"
-10.Upload Service Image, uploadfile, "src/main/resources/test-data/painter.jpg", "//input[@type='file' and @accept='image/*']"
-11.wait,2000,,
-12.Open status Dropdown,click,,"//label[contains(., 'Status')]/following-sibling::p-dropdown"
-13.Select Activate,click,,"//li[@aria-label='Activate']"
-14.Open Select City Dropdown,click,,"//div[contains(@class, 'p-multiselect-label-container')]"
-15.Select {areaName},click,,"//li[contains(@aria-label, '{areaName}')]"
-16.Click  Submit,click,,"//button[normalize-space()='Submit']"
-17.Filter Services List,type,{serviceName},"//input[@aria-label='Services Filter Input']"
-18.Click Home Icon ,click,,"//i[@title='Home']"
-19.Click Settings ,click,,"//button[contains(., 'Settings')]"
-20.Click Requirment Document ,click,,"//div[normalize-space()='Required Document']"
-21.Click Add Document ,click,,"//button[normalize-space()='Add Document']"
-22.Enter Name, type, documet{randomAlpha}&gt;&gt; providerDocumentName, "//input[@placeholder='Type here']"
-23.Open status Dropdown,click,,"//span[@aria-label='Status']"
-24.Select Active,click,,"//li[@aria-label='Active']"
-25.Click Document Expiry ,click,,"//div[./div[contains(text(), 'Document Expiry')]]//input"
-26.Click Mandatory Document ,click,,"//div[./div[contains(text(), 'Mandatory Document')]]//input"
-27.Click Submit ,click,,"//button[normalize-space()='Submit']"
-28.Verify Sucess, verify, , "//div[@aria-label='Info']"
-29.Filter Document List,type,{providerDocumentName},"//input[@aria-label='Name Filter Input']"
-30.Click Settings ,click,,"//button[contains(., 'Settings')]"
-31.Click Promocode ,click,,"//div[normalize-space()='Promocode']"
-32.Click Add Promo Code ,click,,"//button[normalize-space()='Add Promo Code']"
-33.Open User List Dropdown,click,,"//label[contains(., 'User List')]/following-sibling::p-multiselect//div[contains(@class, 'p-multiselect-label-container')]"
-34.Select User,click,,"//li[@aria-label='{customerName}']"
-35.Click Code Name Box,click,,"//input[@placeholder='Code Name']"
-35.Enter Code Name, type, promoCode{randomAlpha}&gt;&gt; providerPromoCodeName, "//input[@placeholder='Code Name']"
-36.Open Discout Type Dropdown,click,,"//span[@aria-label='Select Discount Type']"
-37.Select Discout Type,click,,"//li[@aria-label='Discount in Amount ']"
-38.Enter Expiry Date,type,12122026,"//div[label[contains(., 'Expiry Date')]]//input"
-39.Enter Discount Amount, type, 100, "//input[@placeholder='Discount Amount']"
-40.Enter Minimum Order Amount, type, 1000, "//input[@placeholder='Min Order Amount']"
-41.Enter Maximum Discount Amount, type, 100, "//input[@placeholder='Max DiscountAmount']"
-42.Enter Coupon Limit, type, 5,"//div[label[contains(., 'Coupon Limit')]]//input"
-43.Enter Usage Limit for One User, type, 2,"//div[label[contains(., 'Usage Limit For One User')]]//input"
-44.Enter Promo Code Description, type, Promo Dode For Gold Member,"//textarea[@placeholder='PromoCode Description']"
-45.Click Submit ,click,,"//button[normalize-space()='Submit']"
-46.Verify Sucess, verify, , "//div[@aria-label='Info']"
-47.Filter PromoCode List,type,{providerPromoCodeName},"//input[@aria-label='Promocode Filter Input']"
-48.Click  Providers,click,,"//button[contains(., 'Providers')]"
-49.Select Add Providers,click,,"//div[contains(text(), 'Add Providers')]"
-50.Verify Add Provider,verify,,"//h1[text()=' Add Provider ']"
-51.Enter Provider Full Name, type, Painter{randomAlpha}&gt;&gt; painterName, "//input[@placeholder='Provider Full Name']"
-52.Upload Painter Image, uploadfile, "src/main/resources/test-data/painter.jpg", "//input[@type='file']"
-53.Enter Email, type, Painter_{timestamp}@gmail.com&gt;&gt;painterEmail, "//input[@placeholder='Unique Email']"
-54.Enter Contact Number, type, {randomPhone}, "//input[@placeholder='Unique Contact Number']"
-55.Enter Landmark, type, Near LIC Building, "//input[@placeholder='Provider Landmark']"
-56.Open Delivery Radius Dropdown,click,,"//select[@formcontrolname='serviceRadius']"
-57.Select Twenty Five Kilometer,click,,"//option[text()='25 KM']"
-58.Enter Minimum Order, type, 10, "//input[@placeholder='Minimum Order']"
-59.Enter Provider Address, type, painter chennai, "//input[@placeholder='Enter provider Address']"
-60.wait,1000,,
-61.Select First Option,arrow_down,,"//input[@placeholder='Enter provider Address']"
-62.Confirm Option,press_enter,,"//input[@placeholder='Enter provider Address']"
-63.wait,1000,,
-64.Click Everyday Checkbox, click, , "//span[text()='EveryDay']/preceding-sibling::input"
-65.Click 09:00 AM-10:00 AM, click, , "//button[normalize-space()='09:00 AM-10:00 AM']"
-66.Click 10:00 AM-11:00 AM, click, , "//button[normalize-space()='10:00 AM-11:00 AM']"
-67.Click 11:00 AM-12:00 PM, click, , "//button[normalize-space()='11:00 AM-12:00 PM']"
-68.Click 12:00 PM-01:00 PM, click, , "//button[normalize-space()='12:00 PM-01:00 PM']"
-69.Click 02:00 PM-03:00 PM, click, , "//button[normalize-space()='02:00 PM-03:00 PM']"
-70.Click 03:00 PM-04:00 PM, click, , "//button[normalize-space()='03:00 PM-04:00 PM']"
-71.Enter Bank Name, type, federal, "//input[@placeholder='Bank Name']"
-72.Enter Bank Location,type, chennai, "//input[@placeholder='Bank Location(City Name)']"
-73.Scroll Grid, tab, 1, "//input[@placeholder='Bank Location(City Name)']"
-74.Enter Account Number, type, 123456789012, "//input[@placeholder='Account Number']"
-75.Enter Accont Holder Name, type, {painterName}, "//input[@placeholder='Account Holder Name']"
-76.Enter Payment Email Address, type, {painterEmail}, "//input[@placeholder='Email Address for Payment Notification']"
-77.Enter BIC Code, type, 1234, "//input[@placeholder='BIC Code']"
-78.Click Save, click, , "//button[@type='submit']"
-79.Verify Sucess, verify, , "//div[@aria-label='Info']"
-80.Filter Painter List,type,{painterName},"//input[@aria-label='Provider Name Filter Input']"
-81.Click  Providers,click,,"//button[contains(., 'Providers')]"
-82.Select Pending Document Providers,click,,"//div[normalize-space()='Pending Document Providers']"
-83.Filter Plumber List,type,{painterName},"//input[@aria-label='Provider Name Filter Input']"
-84.Click Document Icon,click,,"//i[@class='bi bi-file-earmark-text cursor-pointer gridIcon Navigate']"
-85. Provider Required Documents,verify,,"//div[contains(text(),'Documents')]"
-86.FilterDocumet List,type,{providerDocumentName},"//input[@aria-label='Document Name Filter Input']"
-87.Add Address Proof,click,,"(//i[contains(@class, 'Edit')])[1]"
-88.Upload Address Proof, uploadfile, "src/main/resources/test-data/addressproof.png", "//input[@type='file']"
-89.Enter Expiry Date,type,2026-12-12,"//input[@placeholder='YYYY/MM/DD']"
-90.Click Submit, click, , "//button[normalize-space()='Submit']"
-91.Verify Updated Succesfully, verify, , "//div[@aria-label='Updated Successfully']"
-92.FilterDocumet List,type,{providerDocumentName},"//input[@aria-label='Document Name Filter Input']"
-93.Click Approve Store,click,,"//div[@row-index='0']//i[contains(@class, 'bi-hand-thumbs-up-fill')]"
-94.Verify Updated Succesfully, verify, , "//div[@aria-label='Updated Successfully']"
-95.Click Back, click, , "//button[@class='buttonWidget']"
-96.Click  Providers,click,,"//button[normalize-space()='Category']"
-97.Click  Add New Category,click,,"//button[normalize-space()='ADD CATEGORY']"
-98.Enter Category Name, type,residentialPainter{randomAlpha}&gt;&gt; painterCategoryName, "//input[@placeholder='Enter the category name']"
-99.Enter Category Name Tamil, type, குடியிருப்பு பெயிண்டர், "//input[@placeholder='Category Name (in Tamil)']"
-100.Enter Category Name Arabic, type, دهان سكني, "//input[@placeholder='Category Name (in Arabic)']"
-101.Enter Category Name Hindi, type, आवासीय पेंटर, "//input[@placeholder='Category Name (in Hindi)']"
-102.Open Category status Dropdown,click,,"//span[@aria-label='Select a category status']"
-103.Select Activate,click,,"//li[@aria-label='Active']"
-104.Upload Category Image, uploadfile, "src/main/resources/test-data/painter.jpg", "//input[@type='file' and @accept='image/*']"
-105.wait,2000,,
-106.Click  Submit,click,,"//button[normalize-space()='Submit']"
-107.Filter Category Name,type,{painterCategoryName},"//input[@aria-label='Category Name Filter Input']"
-108.Click  Providers,click,,"//button[contains(., 'Providers')]"
-109.Select Provider List,click,,"//div[normalize-space()='Provider List']"
-110.Filter Painter List,type,{painterName},"//input[@aria-label='Provider Name Filter Input']"
-111.Scroll Grid, tab, 7, "//input[@aria-label='Provider Name Filter Input']"
-112.Click Package Icon,click,,"//i[@class='bi bi-box-seam cursor-pointer gridIcon Navigate']"
-113.Click  Add Package,click,,"//button[normalize-space()='Add Package']"
-114.Open Category  Dropdown,click,,"//span[@aria-label='Package Category']"
-115.Select Activate,click,,"//li[@aria-label='{painterCategoryName}']"
-116.Enter Package Name, type, package{randomAlpha}&gt;&gt; packageName, "//input[@placeholder='Package Name']"
-117.Enter Amount, type, 1000, "//input[@placeholder='Amount Value']"
-118.Open Max Book Quantity  Dropdown,click,,"//span[@aria-label='Package Max Book Quantity']"
-119.Select 4,click,,"//li[@aria-label='4']"
-120.Open Status Dropdown,click,,"//span[@aria-label='select Status']"
-121.Select Activate,click,,"//li[@aria-label='Activate']"
-122.Enter Description, type, Premium residential painting package, "//textarea[@placeholder='Description']"
-123.Click  Submit,click,,"//button[normalize-space()='Submit']"
-124.wait,1000,,
-125.Click  back,click,,"//button[normalize-space()='Back']"
-126.Click badge,click,,"//i[contains(@class, 'fa-user-secret')]"
-127.Click Delivery Services,click,,"//h2[contains(text(), 'Provider Services')]"
-128.Filter Services List,type,{serviceName},"//input[@aria-label='Services Filter Input']"
-129.Click Edit Icon ,click,,"//i[@title='Edit']"
-130.Enter Service Name Tamil, type, பெயிண்டர், "//input[@placeholder='Service Name (in Tamil)']"
-131.Enter Service Name Arabic, type, دهان, "//input[@placeholder='Service Name (in Arabic)']"
-132.Enter Service Name Hindi, type, पेंटर, "//input[@placeholder='Service Name (in Hindi)']"
-133.Scroll Grid, tab, 4, "//input[@placeholder='Service Name (in Hindi)']"
-134.Open status Dropdown,click,,"//label[contains(., 'Status')]/following-sibling::p-dropdown"
-135.Select Deactivate,click,,"//li[@aria-label='Deactivate']"
-136.Click  Submit,click,,"//button[normalize-space()='Submit']"
-137.Click  back,click,,"//button[normalize-space()='Back']"
-138.Click badge,click,,"//i[contains(@class, 'fa-user-secret')]"
-139.Click Delivery Services,click,,"//h2[contains(text(), 'Provider Services')]"
-140.Filter Services List,type,{serviceName},"//input[@aria-label='Services Filter Input']"
-141.wait,1000,,</t>
-  </si>
-  <si>
     <t>Add New  Store, Provider , Driver &amp;  Customer Subscription Plan</t>
   </si>
   <si>
@@ -1603,131 +1354,6 @@
   </si>
   <si>
     <t>Super Admin Login</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.Click badge,click,,"//i[contains(@class, 'fa-hand-holding-usd fa-solid iconstyle')]"
-2.Click Subscription Plan,click,,"//h2[normalize-space()='Subscription Plan']"
-3.Click Store subscription plan,click,,"//span[normalize-space()='Store Subscription Plan']"
-4.Verify Store Subscription Plan Lists ,verify,,"//div[normalize-space()='Subscription Plan Lists - Store']"
-5.Click  Add New Subscription,click,,"//button[@class='buttonWidget']"
-6.Open Service Category Dropdown,click,,"//span[@aria-label='Select Service Category']"
-7.Select Food Delivery,click,,"//li[@aria-label='Food Delivery']"
-8.Enter Store Plan Name, type, StorePlan{randomAlpha}&gt;&gt; storeSubscriptionName, "//input[@placeholder='Plan Name']"
-9.Enter Store Plan Name Arabic, type,عضو ذهبي, "//input[@placeholder='Plan Name (in Arabic)']"
-10.Enter Store Plan Name Tamil, type,தங்க உறுப்பினர், "//input[@placeholder='Plan Name (in Tamil):']"
-11.Enter Store Plan Name Hindi, type,गोल्ड मेंबर, "//input[@placeholder='Plan Name (in Hindi):']"
-12.Enter Number Of Days, type,100, "//input[@placeholder='Enter No. of Days ']"
-13.Enter Price, type,5000, "//input[@placeholder='Enter Plan Price']"
-14.Enter Plan Description English, type,A premium tier status offering exclusive benefits and high-level rewards to loyal users, "//textarea[@placeholder='Page Description English']"
-15.Enter Plan Description Arabic, type,فئة عضوية مميزة تمنح المستخدمين المخلصين مزايا حصرية ومكافآت رفيعة المستوى, "//textarea[@placeholder='Page Description(in Arabic)']"
-16.Enter Plan Description Tamil, type,இது விசுவாசமான பயனர்களுக்கு பிரத்யேக நன்மைகள் மற்றும் சலுகைகளை வழங்கும் ஒரு பிரீமியம் உறுப்பினர் நிலையாகும், "//textarea[@placeholder='Page Description(in Tamil)']"
-17.Enter Plan Description Hindi, type,यह एक प्रीमियम सदस्यता स्तर है जो वफादार उपयोगकर्ताओं को विशेष लाभ और पुरस्कार प्रदान करता है, "//textarea[@placeholder='Page Description(in Hindi)']"
-18.Open status Dropdown,click,,"//span[@aria-label='select Status']"
-19.Select On,click,,"//li[@aria-label='on']"
-20.Click Submit ,click,,"//button[normalize-space()='Submit']"
-21.Filter Services List,type,{storeSubscriptionName},"//input[@aria-label='Plan Name Filter Input']"
-22.Click Edit ,click,,"//i[@class='bi bi-pencil-square cursor-pointer gridIcon Edit']"
-23.Click Close ,click,,"//button[normalize-space()='Close']"
-24.Click Active ,click,,"//i[@title='Active']"
-25.wait,2000,,
-26.Click Deactive,click,,"//i[@title='Inactive']"
-27.wait,2000,,
-28.Click Delete Plan,click,,"//i[@class='bi bi-trash cursor-pointer gridIcon Delete']"
-29.Click Confirm Delete,click,,"//button[normalize-space()='Yes, delete it!']"
-30.wait,3000,,
-31.Click badge,click,,"//i[contains(@class, 'fa-hand-holding-usd fa-solid iconstyle')]"
-32.Click Subscription Plan,click,,"//h2[normalize-space()='Subscription Plan']"
-33.Click Driver subscription plan,click,,"//span[normalize-space()='Driver Subscription Plan']"
-34.Verify Driver Subscription Plan Lists ,verify,,"//div[normalize-space()='Subscription Plan Lists - Driver']"
-35.Click  Add New Subscription,click,,"//button[normalize-space()='ADD']"
-36.Open Service Category Dropdown,click,,"//span[@aria-label='Select Service Category']"
-37.Select Auto Ride,click,,"//li[@aria-label='Auto Ride']"
-38.Enter Driver Plan Name, type, DriverPlan{randomAlpha}&gt;&gt; driverSubscriptionName, "//input[@placeholder='Plan Name']"
-39.Enter Driver Plan Name Arabic, type,عضو ذهبي, "//input[@placeholder='Plan Name (in Arabic)']"
-40.Enter Driver Plan Name Tamil, type,தங்க உறுப்பினர், "//input[@placeholder='Plan Name (in Tamil)']"
-41.Enter Driver Plan Name Hindi, type,गोल्ड मेंबर, "//input[@placeholder='Plan Name (in Hindi)']"
-42.Enter Number Of Days, type,100, "//input[@placeholder='No. of Days ']"
-43.Enter Number Of Free Rides, type,2, "//input[@placeholder='Enter No of Rides with Zero admin commission']"
-44.Enter Price, type,5000, "//input[@placeholder='Enter Plan Price']"
-45.Enter Plan Description English, type,A premium tier status offering exclusive benefits and high-level rewards to loyal users, "//textarea[@placeholder='Page Description English']"
-46.Enter Plan Description Arabic, type,فئة عضوية مميزة تمنح المستخدمين المخلصين مزايا حصرية ومكافآت رفيعة المستوى, "//textarea[@placeholder='Page Description Arabic']"
-47.Enter Plan Description Tamil, type,இது விசுவாசமான பயனர்களுக்கு பிரத்யேக நன்மைகள் மற்றும் சலுகைகளை வழங்கும் ஒரு பிரீமியம் உறுப்பினர் நிலையாகும், "//textarea[@placeholder='Page Description Tamil']"
-48.Enter Plan Description Hindi, type,यह एक प्रीमियम सदस्यता स्तर है जो वफादार उपयोगकर्ताओं को विशेष लाभ और पुरस्कार प्रदान करता है, "//textarea[@placeholder='Page Description Hindi']"
-49.Open status Dropdown,click,,"//span[@aria-label='select Status']"
-50.Select On,click,,"//li[@aria-label='on']"
-51.Click Submit ,click,,"//button[normalize-space()='Submit']"
-52.Filter Services List,type,{driverSubscriptionName},"//input[@aria-label='Plan Name Filter Input']"
-53.Click Edit ,click,,"//i[@class='bi bi-pencil-square cursor-pointer gridIcon Edit']"
-54.Click Close ,click,,"//button[normalize-space()='Close']"
-55.Click Active ,click,,"//i[@class='bi bi-hand-thumbs-up-fill cursor-pointer gridIcon Modify']"
-56.wait,2000,,
-57.Click Deactive,click,,"//i[@class='bi bi-hand-thumbs-down-fill cursor-pointer gridIcon Modify']"
-58.wait,2000,,
-59.Click Delete Plan,click,,"//i[@class='bi bi-trash cursor-pointer gridIcon Delete']"
-60.Click Confirm Delete,click,,"//button[normalize-space()='Yes, delete it!']"
-61.wait,3000,,
-62.Click badge,click,,"//i[contains(@class, 'fa-hand-holding-usd fa-solid iconstyle')]"
-63.Click Subscription Plan,click,,"//h2[normalize-space()='Subscription Plan']"
-64.Click Provider subscription plan,click,,"//span[normalize-space()='Provider Subscription Plan']"
-65.Verify Provider Subscription Plan Lists ,verify,,"//div[normalize-space()='Subscription Plan Lists - Provider']"
-66.Click  Add New Subscription,click,,"//button[@class='buttonWidget']"
-67.Open Service Category Dropdown,click,,"//span[@aria-label='Select Service Category']"
-68.Select Pest Control,click,,"//li[@aria-label='Pest Control']"
-69.Enter Provider Plan Name, type, ProviderPlan{randomAlpha}&gt;&gt; providerSubscriptionName, "//input[@placeholder='Plan Name']"
-70.Enter Provider Plan Name Arabic, type,عضو ذهبي, "//input[@placeholder='Plan Name (in Arabic):']"
-71.Enter Provider Plan Name Tamil, type,தங்க உறுப்பினர், "//input[@placeholder='Plan Name (in Tamil):']"
-72.Enter Provider Plan Name Hindi, type,गोल्ड मेंबर, "//input[@placeholder='Plan Name (in Hindi):']"
-73.Enter Number Of Days, type,100, "//input[@placeholder='Enter No. of Days ']"
-74.Enter Price, type,5000, "//input[@placeholder='Enter Plan Price ']"
-75.Enter Plan Description English, type,A premium tier status offering exclusive benefits and high-level rewards to loyal users, "//textarea[@placeholder='Enter Description(in English):']"
-76.Enter Plan Description Arabic, type,فئة عضوية مميزة تمنح المستخدمين المخلصين مزايا حصرية ومكافآت رفيعة المستوى, "//textarea[@placeholder='Enter Description(in Arabic):']"
-77.Enter Plan Description Tamil, type,இது விசுவாசமான பயனர்களுக்கு பிரத்யேக நன்மைகள் மற்றும் சலுகைகளை வழங்கும் ஒரு பிரீமியம் உறுப்பினர் நிலையாகும், "//textarea[@placeholder='Enter Description(in Tamil)']"
-78.Enter Plan Description Hindi, type,यह एक प्रीमियम सदस्यता स्तर है जो वफादार उपयोगकर्ताओं को विशेष लाभ और पुरस्कार प्रदान करता है, "//textarea[@placeholder='Enter Description(in Hindi']"
-79.Open status Dropdown,click,,"//span[@aria-label='select Status']"
-80.Select On,click,,"//li[@aria-label='on']"
-81.Click Submit ,click,,"//button[normalize-space()='Submit']"
-82.Filter Services List,type,{providerSubscriptionName},"//input[@aria-label='Plan Name Filter Input']"
-83.Click Edit ,click,,"//i[@class='bi bi-pencil-square cursor-pointer gridIcon Edit']"
-84.Click Close ,click,,"//button[normalize-space()='Close']"
-85.Click Active ,click,,"//i[@class='bi bi-hand-thumbs-up-fill cursor-pointer gridIcon Modify']"
-86.wait,2000,,
-87.Click Deactive,click,,"//i[@class='bi bi-hand-thumbs-down-fill cursor-pointer gridIcon Modify']"
-88.wait,2000,,
-89.Click Delete Plan,click,,"//i[@class='bi bi-trash cursor-pointer gridIcon Delete']"
-90.Click Confirm Delete,click,,"//button[normalize-space()='Yes, delete it!']"
-91.wait,3000,,
-92.Click badge,click,,"//i[contains(@class, 'fa-hand-holding-usd fa-solid iconstyle')]"
-93.Click Subscription Plan,click,,"//h2[normalize-space()='Subscription Plan']"
-94.Click Customer subscription plan,click,,"//span[normalize-space()='Customer Subscription Plan']"
-95.Verify Customer Subscription Plan Lists ,verify,,"//div[normalize-space()='Customer Subscription Plans']"
-96.Click  Add New Subscription,click,,"//button[@class='buttonWidget']"
-97.Open Service Category Dropdown,click,,"//span[@aria-label='Select Service Category']"
-98.Select Pest Control,click,,"//li[@aria-label='Pest Control']"
-99.Enter Customer Plan Name, type,CustomerPlan{randomAlpha}&gt;&gt; custometSubscriptionName, "//input[@placeholder='Plan Name']"
-100.Enter Driver Plan Name Arabic, type,عضو ذهبي, "//input[@placeholder='Plan Name (in Arabic)']"
-101.Enter Driver Plan Name Tamil, type,தங்க உறுப்பினர், "//input[@placeholder='Plan Name (in Tamil):']"
-102.Enter Driver Plan Name Hindi, type,गोल्ड मेंबर, "//input[@placeholder='Plan Name (in Hindi):']"
-103.Enter Number Of Days, type,100, "//input[@placeholder='Enter No. of Days ']"
-104.Enter Number Of Free Rides, type,2, "//input[@placeholder='Enter No Of Free Rides']"
-105.Enter Price, type,5000, "//input[@placeholder='Enter Plan Price']"
-106.Enter Plan Description English, type,A premium tier status offering exclusive benefits and high-level rewards to loyal users, "//textarea[@placeholder='Page Description English']"
-107.Enter Plan Description Arabic, type,فئة عضوية مميزة تمنح المستخدمين المخلصين مزايا حصرية ومكافآت رفيعة المستوى, "//textarea[@placeholder='Page Description(in Arabic)']"
-108.Enter Plan Description Tamil, type,இது விசுவாசமான பயனர்களுக்கு பிரத்யேக நன்மைகள் மற்றும் சலுகைகளை வழங்கும் ஒரு பிரீமியம் உறுப்பினர் நிலையாகும், "//textarea[@placeholder='Page Description(in Tamil)']"
-109.Enter Plan Description Hindi, type,यह एक प्रीमियम सदस्यता स्तर है जो वफादार उपयोगकर्ताओं को विशेष लाभ और पुरस्कार प्रदान करता है, "//textarea[@placeholder='Page Description(in Hindi)']"
-110.Open status Dropdown,click,,"//span[@aria-label='select Status']"
-111.Select On,click,,"//li[@aria-label='on']"
-112.Click Submit ,click,,"//button[normalize-space()='Submit']"
-113.Filter Services List,type,{custometSubscriptionName},"//input[@aria-label='Plan Name Filter Input']"
-114.Click Edit ,click,,"//i[@title='Edit Plan']"
-115.Click Close ,click,,"//button[normalize-space()='Close']"
-116.Click Active ,click,,"//i[@title='Activate Plan']"
-117.wait,2000,,
-118.Click Deactive,click,,"//i[@title='Deactivate Plan']"
-119.wait,2000,,
-120.Click Delete Plan,click,,"//i[@title='Delete Plan']"
-121.Click Confirm Delete,click,,"//button[normalize-space()='Yes, delete it!']"
-122.wait,3000,,
-</t>
   </si>
   <si>
     <t>SA_TS_16</t>
@@ -1998,181 +1624,6 @@
 118.Enter Loyalty points per default currency (for ex. $1 = 10 points), type, 5, "admin.transport.loyalty.ratio.input"
 119.Click Submit ,click,, "web.global.action.submit"
 120.Wait For Sucess, wait_until_visible, , "web.global.toast.info"</t>
-  </si>
-  <si>
-    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-2. Click Transports Services Menu,click,, "admin.transport.menu.card"
-3.Wait For Transport Services, wait_until_visible,, "admin.transport.page.header"
-4.Click  Add Category,click,, "admin.transport.add_category.btn"
-5.Enter Service Name, type, Bus Ride{randomAlpha}&gt;&gt;transportName, "admin.transport.name.input"
-6.Enter Service Name Arabic, type, رحلة بالحافلة, "admin.transport.name_ar.input"
-7.Enter Slug, type, Bus Ride, "admin.transport.slug.input"
-8.Upload Transport Service Image, uploadfile, "src/main/resources/test-data/bus.jpg", "admin.transport.image.file"
-9.wait,2000,,
-10.Open status Dropdown,click,, "admin.transport.status.dropdown"
-11.Select Activate,click,, "admin.transport.status.activate_option"
-12.Open Select City Dropdown,click,, "admin.transport.city.dropdown"
-13.Select {areaName},click,, "admin.transport.city.dynamic_option"
-14.Click  Submit,click,, "web.global.action.submit"
-15.Wait Till Sucess, wait_until_visible, , "web.global.toast.info"
-16.wait,2000,,
-17.Click  back,click,, "admin.transport.back.btn"
-18. Click Dashboard Icon,click,, "web.global.menu.dashboard"
-19.Click Transports Services Menu,click,, "admin.transport.menu.card"
-20.Filter Services List,type,{transportName}, "admin.transport.grid.name_filter"
-21.Click Home Icon ,click,, "admin.transport.home.icon"
-22.Click Settings ,click,, "admin.transport.menu.settings"
-23.Click Vehicle Type,click,, "admin.transport.settings.vehicle_type"
-24.Click Add Vehicle Type,click,, "admin.transport.vehicle.add_type.btn"
-25.Enter Vehicle Type Name, type, volvo{randomAlpha}&gt;&gt;busTypeName, "admin.transport.vehicle.name.input"
-26.Enter Base Fare, type, 150, "admin.transport.vehicle.base_fare.input"
-27.Enter Base Fare Max Kilometer, type, 10, "admin.transport.vehicle.base_km.input"
-28.Open Extra Distance Fare Dropdown,click,, "admin.transport.vehicle.extra_fare_type.dropdown"
-29.Select Amount,click,, "admin.transport.status.amount_option"
-30.Enter Extra Distance Fare , type, 10, "admin.transport.vehicle.extra_fare.input"
-31.Enter Free Waiting Time , type, 10, "admin.transport.vehicle.waiting_free.input"
-32.Open Waiting Charge Dropdown,click,, "admin.transport.vehicle.waiting_type.dropdown"
-33.Select Amount,click,, "admin.transport.status.amount_option"
-34.Enter Waiting Rate , type, 10, "admin.transport.vehicle.waiting_rate.input"
-35.Enter Included Trip Waiting , type, 10, "admin.transport.vehicle.trip_waiting_free.input"
-36.Open Trip Waiting Charge Dropdown,click,, "admin.transport.vehicle.trip_waiting_type.dropdown"
-37.Select Amount,click,, "admin.transport.status.amount_option"
-38.Enter Trip Waiting Rate , type,50, "admin.transport.vehicle.trip_waiting_rate.input"
-39.Enter Free Pickup Distance , type,5, "admin.transport.vehicle.pickup_free.input"
-40.Open Pickup Charge Dropdown,click,, "admin.transport.vehicle.pickup_type.dropdown"
-41.Select Amount,click,, "admin.transport.status.amount_option"
-42.Enter Pickup Fee, type,50, "admin.transport.vehicle.pickup_fee.input"
-43.Open Customer Fee  Dropdown,click,, "admin.transport.vehicle.customer_type.dropdown"
-44.Select Amount,click,, "admin.transport.status.amount_option"
-45.Enter Customer Fee, type,50, "admin.transport.vehicle.customer_fee.input"
-46.Open Customer GST  Dropdown,click,, "admin.transport.vehicle.customer_gst_type.dropdown"
-47.Select Amount,click,, "admin.transport.status.amount_option"
-48.Enter  GST amount, type,50, "admin.transport.vehicle.customer_gst.input"
-49.Open Driver Fee  Dropdown,click,, "admin.transport.vehicle.driver_type.dropdown"
-50.Select Amount,click,, "admin.transport.status.amount_option"
-51.Enter  Driver Fee, type,50, "admin.transport.vehicle.driver_fee.input"
-52.Open Driver GST  Dropdown,click,, "admin.transport.vehicle.driver_gst_type.dropdown"
-53.Select Amount,click,, "admin.transport.status.amount_option"
-54.Enter Driver Gst,type,50, "admin.transport.vehicle.driver_gst.input"
-55.Open Status Dropdown,click,, "admin.transport.vehicle.status.dropdown"
-56.Select Active,click,, "admin.transport.status.active_option"
-57.Upload Vehicle Image, uploadfile, "src/main/resources/test-data/volvo.jpg", "admin.transport.vehicle.image.file"
-58.Enter Notifiacation,type,50, "admin.transport.vehicle.notify_km.input"
-59.Enter Driver Request ETA,type,50, "admin.transport.vehicle.eta_limit.input"
-60.Enter Driver Request KM,type,50, "admin.transport.vehicle.km_limit.input"
-61.Open Night Charge Timing Status Dropdown,click,, "admin.transport.night.status.dropdown"
-62.Select Active,click,, "admin.transport.status.active_option"
-63.Click Surcharge Time Checkbox, click, , "admin.transport.night.everyday.checkbox"
-64.Enter From Time, type, 100000AM, "admin.transport.night.from_time.input"
-65.Enter To Time, type, 220000PM, "admin.transport.night.to_time.input"
-66.Open  Dropdown,click,, "admin.transport.night.type.dropdown"
-67.Select Amount,click,, "admin.transport.status.amount_option"
-68.Enter  Price, type,50, "admin.transport.night.price.input"
-69.Click  Submit,click,, "web.global.action.submit"
-70.Wait For Sucess,wait_until_visible, , "web.global.toast.info"
-71.Click Settings ,click,, "admin.transport.menu.settings"
-72.Click Promocode,click,, "admin.transport.promo.menu_item"
-73.Click Add Promo Code ,click,, "admin.transport.promo.add.btn"
-74.Open User List Dropdown,click,, "admin.transport.promo.user_list.dropdown"
-75.Select User,click,, "admin.transport.promo.user_option"
-76.Click Code Name Box,click,, "admin.transport.promo.codename.input"
-77.Enter Code Name, type, promoCode{randomAlpha}&gt;&gt; promoCodeName, "admin.transport.promo.codename.input"
-78.Open Discout Type Dropdown,click,, "admin.transport.promo.discount_type.dropdown"
-79.Select Discout Type,click,, "admin.transport.promo.discount_type.amount_option"
-80.Enter Expiry Date,type,12122026, "admin.transport.promo.expiry.input"
-81.Enter Discount Amount, type, 100, "admin.transport.promo.amount.input"
-82.Enter Minimum Order Amount, type, 1000, "admin.transport.promo.min_order.input"
-83.Enter Maximum Discount Amount, type, 100, "admin.transport.promo.max_discount.input"
-84.Enter Coupon Limit, type, 5, "admin.transport.promo.coupon_limit.input"
-85.Enter Usage Limit for One User, type, 2, "admin.transport.promo.user_limit.input"
-86.Enter Promo Code Description, type, Promo Dode For Gold Member, "admin.transport.promo.desc.textarea"
-87.Click Submit ,click,, "web.global.action.submit"
-88.Wait For Sucess, wait_until_visible, , "web.global.toast.info"
-89.wait,2000,,
-90.Click Settings ,click,, "admin.transport.menu.settings"
-91.Click Service Settings ,click,, "admin.transport.rules.menu_item"
-92.Enter Driver Accept Timeout, type, 60, "admin.transport.rules.timeout.input"
-93.Enter Driver Serach Radius, type, 50, "admin.transport.rules.radius.input"
-94.Click Submit ,click,, "web.global.action.submit"
-95.Wait For Sucess, wait_until_visible, , "web.global.toast.info"
-96.wait,1000,,
-97.Click Settings ,click,, "admin.transport.menu.settings"
-98.Click Requirment Document ,click,, "admin.transport.docs.menu_item"
-99.Click Add Document ,click,, "admin.transport.docs.add.btn"
-100.Enter Name, type, documet{randomAlpha}&gt;&gt; documentName, "admin.transport.docs.name.input"
-101.Open status Dropdown,click,, "admin.transport.docs.status.dropdown"
-102.Select Active,click,, "admin.transport.status.active_option"
-103.Click Document Expiry ,click,, "admin.transport.docs.expiry.checkbox"
-104.Click Mandatory Document ,click,, "admin.transport.docs.mandatory.checkbox"
-105.Click  Require Proof Number,click,, "admin.transport.docs.proof_no.checkbox"
-106.Enter Display Order, type, 10, "admin.transport.docs.order.input"
-107.Click Submit ,click,, "web.global.action.submit"
-108.Wait For Sucess, wait_until_visible, , "web.global.toast.info"
-109.Filter Document List,type,{documentName}, "admin.transport.docs.grid.name_filter"
-110.wait,1000,,
-111. Click Dashboard Icon,click,, "web.global.menu.dashboard"
-112.Click drivers menu,click,, "admin.drivers.menu.icon"
-113.Click Add Driver menu,click,, "admin.drivers.add_menu.link"
-114.Wait For Add Driver, wait_until_visible,, "admin.drivers.add_page.header"
-115.Click Service Category Dropdown,click,, "admin.drivers.service_dropdown.select"
-116.Select Bus Ride Option,click,, "admin.transport.dropdown.dynamic_service"
-117.Enter Driver Name, type, busdriver_{timestamp} &gt;&gt; busDriverName, "admin.drivers.fullname.input"
-118.Enter Email, type, busdriver_{timestamp}@gmail.com&gt;&gt;busEmail, "admin.drivers.email.input"
-119.Enter Contact Number, type, {randomPhone}&gt;&gt;busPhone, "admin.drivers.phone.input"
-120.Click Whatspp,click,, "admin.drivers.whatsapp.checkbox"
-121.Enter Whatspp Number,type,{busPhone}, "admin.drivers.whatsapp_phone.input"
-122.Upload Profile Image, uploadfile, "src/main/resources/test-data/busdriver.jpg", "admin.drivers.profile_image.file"
-123.Select Source,click,, "admin.drivers.source_dropdown.select"
-124.Select Instagram,click,, "admin.drivers.instagram_option.span"
-125.Select Male Gender, click, , "admin.drivers.male_gender.div"
-126.Click Vehicle Type Dropdown,click,, "admin.drivers.vehicle_dropdown.select"
-127.Select  volvo Option,click,, "admin.transport.dropdown.dynamic_vehicle"
-128.Enter Model Year, type, 2013, "admin.drivers.modelyear.input"
-129.Enter Plate No, type, KL-01-AB-1634, "admin.drivers.plateno.input"
-130. Enter Model Name, type, deisel, "admin.drivers.modelname.input"
-131.Upload Vehicle Image, uploadfile, "src/main/resources/test-data/busvolvo.jpeg", "admin.drivers.vehicle_image.file"
-132.Enter Bank Name, type, HDFC Bank, "admin.drivers.bankname.input"
-133.Enter Bank Location, type, Chennai, "admin.drivers.banklocation.input"
-134.Enter Account Number, type, 50100123456789, "admin.drivers.accountno.input"
-135.Enter Account Holder Name, type, {busDriverName}, "admin.drivers.accountholder.input"
-136.Enter Payment Email Address, type, {busEmail}, "admin.drivers.paymentemail.input"
-137.Enter IFSC Code, type, HDFC0001234, "admin.drivers.ifsc.input"
-138.Click Submit, click, , "web.global.action.submit"
-139.Wait For Driver Added,wait_until_visible, , "web.global.toast.success"
-140.Wait for Toast to hide, wait, 1000,
-141. Click Dashboard Icon,click,, "web.global.menu.dashboard"
-142.Click drivers menu,click,, "admin.drivers.menu.icon"
-143.Click Pending Documents,click,, "admin.drivers.pending_docs.link"
-144.Filter by Name,type,{busDriverName}, "admin.drivers.name_filter.input"
-145.Scroll Grid, tab, 7, "admin.drivers.name_filter.input"
-146.Click Doc Icon,click,, "admin.drivers.docs.icon"
-147.Driver Required Documents,verify,, "admin.drivers.required_docs.header"
-148.FilterDocumet List,type,{documentName}, "admin.drivers.docs_filter.input"
-149.Add Driving License,click,, "admin.drivers.docs.edit_icon"
-150.Upload Driving Iicense, uploadfile, "src/main/resources/test-data/license.jpg", "admin.drivers.profile_image.file"
-151.Enter Expiry Date,type,12-12-2026, "admin.drivers.doc_expiry.input"
-152.Click Submit, click, , "web.global.action.submit"
-153.Wait For Updated Succesfully, wait_until_visible, , "web.global.toast.updated"
-154.Click Approve Driver,click,, "admin.drivers.docs.approval"
-155.Verify Updated Succesfully, verify, , "web.global.toast.updated"
-156. Click Dashboard Icon,click,, "web.global.menu.dashboard"
-157.Click drivers menu,click,, "admin.drivers.menu.icon"
-158.Click Approved Drivers,click,, "admin.drivers.approved_docs.link"
-159.Wait For Approved Drivers List, wait_until_visible,, "admin.drivers.approved_page.header"
-160.Filter Approved Driver,type,{busDriverName}, "admin.drivers.name_filter.input"
-161.Click Transports Services Icon,click,, "admin.drivers.menu.icon"
-162.Click Transports Services Menu,click,, "admin.transport.menu.card"
-163.Wait For Transport Services, wait_until_visible,, "admin.transport.page.header"
-164.Filter Services List,type,{transportName}, "admin.transport.grid.name_filter"
-165.Click Edit Icon ,click,, "admin.drivers.docs.edit_icon"
-166.wait,2000,,
-167.Scroll Grid, tab, 5, "admin.transport.name.input"
-168.wait,2000,,
-169.Open status Dropdown,click,, "admin.transport.status.dropdown"
-170.Select Deactivate,click,, "admin.transport.status.deactivate_option"
-171.Click  Submit,click,, "web.global.action.submit"
-172.Wait For Sucess, wait_until_visible, , "web.global.toast.info"
-173.wait,2000,,</t>
   </si>
   <si>
     <t>1.Click Dashboard Icon,click,,"web.global.menu.dashboard"
@@ -2921,7 +2372,306 @@
 53.wait, 2000, , ""</t>
   </si>
   <si>
-    <t>1. Click badge,click,,"admin.deliveryservice.badge.shield"
+    <t>1.Click Dashboard Icon,click,,"web.global.menu.dashboard"
+2.Click Subscription Plan,click,,"admin.subscription.menu_link"
+3.Click Store subscription plan,click,,"admin.subscription.store.tab"
+4.Verify Store Subscription Plan Lists ,verify,,"admin.subscription.store.header"
+5.Click  Add New Subscription,click,,"admin.subscription.common.add_new.btn_widget"
+6.Open Service Category Dropdown,click,,"admin.subscription.common.category.dropdown"
+7.Select Food Delivery,click,,"admin.subscription.common.category.option_food"
+8.Enter Store Plan Name, type, StorePlan{randomAlpha}&gt;&gt; storeSubscriptionName, "admin.subscription.common.name.input"
+9.Enter Store Plan Name Arabic, type,عضو ذهبي, "admin.subscription.common.name_arabic.input"
+10.Enter Store Plan Name Tamil, type,தங்க உறுப்பினர், "admin.subscription.common.name_tamil.alt_input"
+11.Enter Store Plan Name Hindi, type,गोल्ड मेंबर, "admin.subscription.common.name_hindi.alt_input"
+12.Enter Number Of Days, type,100, "admin.subscription.common.days.input"
+13.Enter Price, type,5000, "admin.subscription.common.price.input"
+14.Enter Plan Description English, type,A premium tier status offering exclusive benefits and high-level rewards to loyal users, "admin.subscription.store.desc_english.textarea"
+15.Enter Plan Description Arabic, type,فئة عضوية مميزة تمنح المستخدمين المخلصين مزايا حصرية ومكافآت رفيعة المستوى, "admin.subscription.store.desc_arabic.textarea"
+16.Enter Plan Description Tamil, type,இட்து விசுவாசமான பயனர்களுக்கு பிரத்யேக நன்மைகள் மற்றும் சலுகைகளை வழங்கும் ஒரு பிரீமியம் உறுப்பினர் நிலையாகும், "admin.subscription.store.desc_tamil.textarea"
+17.Enter Plan Description Hindi, type,यह एक प्रीमियम सदस्यता स्तर है जो वफादार उपयोगकर्ताओं को विशेष लाभ और पुरस्कार प्रदान करता है, "admin.subscription.store.desc_hindi.textarea"
+18.Open status Dropdown,click,,"admin.subscription.common.status.dropdown"
+19.Select On,click,,"admin.subscription.common.status.option_on"
+20.Click Submit ,click,,"web.global.action.submit"
+21.Filter Services List,type,{storeSubscriptionName},"admin.subscription.common.filter.input"
+22.Click Edit ,click,,"admin.subscription.store.edit.icon"
+23.Click Close ,click,,"web.global.action.close"
+24.Click Active ,click,,"admin.subscription.store.active.icon"
+25.wait,2000,,
+26.Click Deactive,click,,"admin.subscription.store.inactive.icon"
+27.wait,2000,,
+28.Click Delete Plan,click,,"admin.subscription.store.delete.icon"
+29.Click Confirm Delete,click,,"admin.subscription.common.dialog.btn_delete_confirm"
+30.wait,3000,,
+31.Click Dashboard Icon,click,,"web.global.menu.dashboard"
+32.Click Subscription Plan,click,,"admin.subscription.menu_link"
+33.Click Driver subscription plan,click,,"admin.subscription.driver.tab"
+34.Verify Driver Subscription Plan Lists ,verify,,"admin.subscription.driver.header"
+35.Click  Add New Subscription,click,,"admin.subscription.common.add_new.btn_add"
+36.Open Service Category Dropdown,click,,"admin.subscription.common.category.dropdown"
+37.Select Auto Ride,click,,"admin.subscription.common.category.option_autoride"
+38.Enter Driver Plan Name, type, DriverPlan{randomAlpha}&gt;&gt; driverSubscriptionName, "admin.subscription.common.name.input"
+39.Enter Driver Plan Name Arabic, type,عضو ذهبي, "admin.subscription.common.name_arabic.input"
+40.Enter Driver Plan Name Tamil, type,தங்க உறுப்பினர், "admin.subscription.common.name_tamil.input"
+41.Enter Driver Plan Name Hindi, type,गोल्ड मेंबर, "admin.subscription.common.name_hindi.input"
+42.Enter Number Of Days, type,100, "admin.subscription.common.days.alt_input"
+43.Enter Number Of Free Rides, type,2, "admin.subscription.driver.free_rides.input"
+44.Enter Price, type,5000, "admin.subscription.common.price.input"
+45.Enter Plan Description English, type,A premium tier status offering exclusive benefits and high-level rewards to loyal users, "admin.subscription.driver.desc_english.textarea"
+46.Enter Plan Description Arabic, type,فئة عضوية مميزة تمنح المستخدمين المخلصين مزايا حصرية ومكافآت رفيعة المستوى, "admin.subscription.driver.desc_arabic.textarea"
+47.Enter Plan Description Tamil, type,இது விசுவாசமான பயனர்களுக்கு பிரத்யேக நன்மைகள் மற்றும் சலுகைகளை வழங்கும் ஒரு பிரीமியம் உறுப்பினர் நிலையாகும், "admin.subscription.driver.desc_tamil.textarea"
+48.Enter Plan Description Hindi, type,यह एक प्रीमियम सदस्यता स्तर है जो वफादार उपयोगकर्ताओं को विशेष लाभ और पुरस्कार प्रदान करता है, "admin.subscription.driver.desc_hindi.textarea"
+49.Open status Dropdown,click,,"admin.subscription.common.status.dropdown"
+50.Select On,click,,"admin.subscription.common.status.option_on"
+51.Click Submit ,click,,"web.global.action.submit"
+52.Filter Services List,type,{driverSubscriptionName},"admin.subscription.common.filter.input"
+53.Click Edit ,click,,"admin.subscription.driver.edit.icon"
+54.Click Close ,click,,"web.global.action.close"
+55.Click Active ,click,,"admin.subscription.driver.active.icon"
+56.wait,2000,,
+57.Click Deactive,click,,"admin.subscription.driver.inactive.icon"
+58.wait,2000,,
+59.Click Delete Plan,click,,"admin.subscription.driver.delete.icon"
+60.Click Confirm Delete,click,,"admin.subscription.common.dialog.btn_delete_confirm"
+61.wait,3000,,
+62. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+63.Click Subscription Plan,click,,"admin.subscription.menu_link"
+64.Click Provider subscription plan,click,,"admin.subscription.provider.tab"
+65.Verify Provider Subscription Plan Lists ,verify,,"admin.subscription.provider.header"
+66.Click  Add New Subscription,click,,"admin.subscription.common.add_new.btn_widget"
+67.Open Service Category Dropdown,click,,"admin.subscription.common.category.dropdown"
+68.Select Pest Control,click,,"admin.subscription.common.category.option_pest"
+69.Enter Provider Plan Name, type, ProviderPlan{randomAlpha}&gt;&gt; providerSubscriptionName, "admin.subscription.common.name.input"
+70.Enter Provider Plan Name Arabic, type,عضو ذهبي, "admin.subscription.common.name_arabic.alt_input"
+71.Enter Provider Plan Name Tamil, type,தங்க உறுப்பினர், "admin.subscription.common.name_tamil.alt_input"
+72.Enter Provider Plan Name Hindi, type,गोल्ड मेंबर, "admin.subscription.common.name_hindi.alt_input"
+73.Enter Number Of Days, type,100, "admin.subscription.common.days.input"
+74.Enter Price, type,5000, "admin.subscription.common.price.alt_input"
+75.Enter Plan Description English, type,A premium tier status offering exclusive benefits and high-level rewards to loyal users, "admin.subscription.provider.desc_english.textarea"
+76.Enter Plan Description Arabic, type,فئة عضوية مميزة تمنح المستخدمين المخلصين مزايا حصرية ومكافآت رفيعة المستوى, "admin.subscription.provider.desc_arabic.textarea"
+77.Enter Plan Description Tamil, type,இது விசுவாசமான பயனர்களுக்கு பிரத்யேக நன்மைகள் மற்றும் सலுகைகளை வழங்கும் ஒரு பிரீமியம் உறுப்பினர் நிலையாகும், "admin.subscription.provider.desc_tamil.textarea"
+78.Enter Plan Description Hindi, type,यह एक प्रीमियम सदस्यता स्तर है जो वफादार उपयोगकर्ताओं को विशेष लाभ और पुरस्कार प्रदान करता है, "admin.subscription.provider.desc_hindi.textarea"
+79.Open status Dropdown,click,,"admin.subscription.common.status.dropdown"
+80.Select On,click,,"admin.subscription.common.status.option_on"
+81.Click Submit ,click,,"web.global.action.submit"
+82.Filter Services List,type,{providerSubscriptionName},"admin.subscription.common.filter.input"
+83.Click Edit ,click,,"admin.subscription.provider.edit.icon"
+84.Click Close ,click,,"web.global.action.close"
+85.Click Active ,click,,"admin.subscription.provider.active.icon"
+86.wait,2000,,
+87.Click Deactive,click,,"admin.subscription.provider.inactive.icon"
+88.wait,2000,,
+89.Click Delete Plan,click,,"admin.subscription.provider.delete.icon"
+90.Click Confirm Delete,click,,"admin.subscription.common.dialog.btn_delete_confirm"
+91.wait,3000,,
+92.Click Dashboard Icon,click,,"web.global.menu.dashboard"
+93.Click Subscription Plan,click,,"admin.subscription.menu_link"
+94.Click Customer subscription plan,click,,"admin.subscription.customer.tab"
+95.Verify Customer Subscription Plan Lists ,verify,,"admin.subscription.customer.header"
+96.Click  Add New Subscription,click,,"admin.subscription.common.add_new.btn_widget"
+97.Open Service Category Dropdown,click,,"admin.subscription.common.category.dropdown"
+98.Select Pest Control,click,,"admin.subscription.common.category.option_pest"
+99.Enter Customer Plan Name, type,CustomerPlan{randomAlpha}&gt;&gt; custometSubscriptionName, "admin.subscription.common.name.input"
+100.Enter Driver Plan Name Arabic, type,عضو ذهبي, "admin.subscription.common.name_arabic.input"
+101.Enter Driver Plan Name Tamil, type,தங்க உறுப்பினர், "admin.subscription.common.name_tamil.alt_input"
+102.Enter Driver Plan Name Hindi, type,गोल्ड मेंबर, "admin.subscription.common.name_hindi.alt_input"
+103.Enter Number Of Days, type,100, "admin.subscription.common.days.input"
+104.Enter Number Of Free Rides, type,2, "admin.subscription.customer.free_rides.input"
+105.Enter Price, type,5000, "admin.subscription.common.price.input"
+106.Enter Plan Description English, type,A premium tier status offering exclusive benefits and high-level rewards to loyal users, "admin.subscription.customer.desc_english.textarea"
+107.Enter Plan Description Arabic, type,فئة عضوية مميزة تمنح المستخدمين المخلصين مزايا حصرية ومكافآت رفيعة المستوى, "admin.subscription.customer.desc_arabic.textarea"
+108.Enter Plan Description Tamil, type,இது விசுவாசமான பயனர்களுக்கு பிரத்யேக நன்மைகள் மற்றும் சலுகைகளை வழங்கும் ஒரு பிரீமியம் உறுப்பினர் நிலையாகும், "admin.subscription.customer.desc_tamil.textarea"
+109.Enter Plan Description Hindi, type,यह एक प्रीमियम सदस्यता स्तर है जो वफादार उपयोगकर्ताओं को विशेष लाभ और पुरस्कार प्रदान करता है, "admin.subscription.customer.desc_hindi.textarea"
+110.Open status Dropdown,click,,"admin.subscription.common.status.dropdown"
+111.Select On,click,,"admin.subscription.common.status.option_on"
+112.Click Submit ,click,,"web.global.action.submit"
+113.Filter Services List,type,{custometSubscriptionName},"admin.subscription.common.filter.input"
+114.Click Edit ,click,,"admin.subscription.customer.edit.icon"
+115.Click Close ,click,,"web.global.action.close"
+116.Click Active ,click,,"admin.subscription.customer.active.icon"
+117.wait,2000,,
+118.Click Deactive,click,,"admin.subscription.customer.inactive.icon"
+119.wait,2000,,
+120.Click Delete Plan,click,,"admin.subscription.customer.delete.icon"
+121.Click Confirm Delete,click,,"admin.subscription.common.dialog.btn_delete_confirm"
+122.wait,3000,,</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2. Click Transports Services Menu,click,, "admin.transport.menu.card"
+3.Wait For Transport Services, wait_until_visible,, "admin.transport.page.header"
+4.Click  Add Category,click,, "admin.transport.add_category.btn"
+5.Enter Service Name, type, Bus Ride{randomAlpha}&gt;&gt;transportName, "admin.transport.name.input"
+6.Enter Service Name Arabic, type, رحلة بالحافلة, "admin.transport.name_ar.input"
+7.Enter Slug, type, Bus Ride, "admin.transport.slug.input"
+8.Upload Transport Service Image, uploadfile, "src/main/resources/test-data/bus.jpg", "admin.transport.image.file"
+9.wait,2000,,
+10.Open status Dropdown,click,, "admin.transport.status.dropdown"
+11.Select Activate,click,, "admin.transport.status.activate_option"
+12.Open Select City Dropdown,click,, "admin.transport.city.dropdown"
+13.Select {areaName},click,, "admin.transport.city.dynamic_option"
+14.Click  Submit,click,, "web.global.action.submit"
+15.Wait Till Sucess, wait_until_visible, , "web.global.toast.info"
+16.wait,2000,,
+17.Click  back,click,, "admin.transport.back.btn"
+18. Click Dashboard Icon,click,, "web.global.menu.dashboard"
+19.Click Transports Services Menu,click,, "admin.transport.menu.card"
+20.Filter Services List,type,{transportName}, "admin.transport.grid.name_filter"
+21.Click Home Icon ,click,, "admin.transport.home.icon"
+22.Click Settings ,click,, "admin.transport.menu.settings"
+23.Click Vehicle Type,click,, "admin.transport.settings.vehicle_type"
+24.Click Add Vehicle Type,click,, "admin.transport.vehicle.add_type.btn"
+25.Enter Vehicle Type Name, type, volvo{randomAlpha}&gt;&gt;busTypeName, "admin.transport.vehicle.name.input"
+26.Enter Base Fare, type, 150, "admin.transport.vehicle.base_fare.input"
+27.Enter Base Fare Max Kilometer, type, 10, "admin.transport.vehicle.base_km.input"
+28.Open Extra Distance Fare Dropdown,click,, "admin.transport.vehicle.extra_fare_type.dropdown"
+29.Select Amount,click,, "admin.transport.status.amount_option"
+30.Enter Extra Distance Fare , type, 10, "admin.transport.vehicle.extra_fare.input"
+31.Enter Free Waiting Time , type, 10, "admin.transport.vehicle.waiting_free.input"
+32.Open Waiting Charge Dropdown,click,, "admin.transport.vehicle.waiting_type.dropdown"
+33.Select Amount,click,, "admin.transport.status.amount_option"
+34.Enter Waiting Rate , type, 10, "admin.transport.vehicle.waiting_rate.input"
+35.Enter Included Trip Waiting , type, 10, "admin.transport.vehicle.trip_waiting_free.input"
+36.Open Trip Waiting Charge Dropdown,click,, "admin.transport.vehicle.trip_waiting_type.dropdown"
+37.Select Amount,click,, "admin.transport.status.amount_option"
+38.Enter Trip Waiting Rate , type,50, "admin.transport.vehicle.trip_waiting_rate.input"
+39.Enter Free Pickup Distance , type,5, "admin.transport.vehicle.pickup_free.input"
+40.Open Pickup Charge Dropdown,click,, "admin.transport.vehicle.pickup_type.dropdown"
+41.Select Amount,click,, "admin.transport.status.amount_option"
+42.Enter Pickup Fee, type,50, "admin.transport.vehicle.pickup_fee.input"
+43.Open Customer Fee  Dropdown,click,, "admin.transport.vehicle.customer_type.dropdown"
+44.Select Amount,click,, "admin.transport.status.amount_option"
+45.Enter Customer Fee, type,50, "admin.transport.vehicle.customer_fee.input"
+46.Open Customer GST  Dropdown,click,, "admin.transport.vehicle.customer_gst_type.dropdown"
+47.Select Amount,click,, "admin.transport.status.amount_option"
+48.Enter  GST amount, type,50, "admin.transport.vehicle.customer_gst.input"
+49.Open Driver Fee  Dropdown,click,, "admin.transport.vehicle.driver_type.dropdown"
+50.Select Amount,click,, "admin.transport.status.amount_option"
+51.Enter  Driver Fee, type,50, "admin.transport.vehicle.driver_fee.input"
+52.Open Driver GST  Dropdown,click,, "admin.transport.vehicle.driver_gst_type.dropdown"
+53.Select Amount,click,, "admin.transport.status.amount_option"
+54.Enter Driver Gst,type,50, "admin.transport.vehicle.driver_gst.input"
+55.Open Status Dropdown,click,, "admin.transport.vehicle.status.dropdown"
+56.Select Active,click,, "admin.transport.status.active_option"
+57.Upload Vehicle Image, uploadfile, "src/main/resources/test-data/volvo.jpg", "admin.transport.vehicle.image.file"
+58.Enter Notifiacation,type,50, "admin.transport.vehicle.notify_km.input"
+59.Enter Driver Request ETA,type,50, "admin.transport.vehicle.eta_limit.input"
+60.Enter Driver Request KM,type,50, "admin.transport.vehicle.km_limit.input"
+61.Open Night Charge Timing Status Dropdown,click,, "admin.transport.night.status.dropdown"
+62.Select Active,click,, "admin.transport.status.active_option"
+63.Click Surcharge Time Checkbox, click, , "admin.transport.night.everyday.checkbox"
+64.Enter From Time, type, 100000AM, "admin.transport.night.from_time.input"
+65.Enter To Time, type, 220000PM, "admin.transport.night.to_time.input"
+66.Open  Dropdown,click,, "admin.transport.night.type.dropdown"
+67.Select Amount,click,, "admin.transport.status.amount_option"
+68.Enter  Price, type,50, "admin.transport.night.price.input"
+69.Click  Submit,click,, "web.global.action.submit"
+70.Wait For Sucess,wait_until_visible, , "web.global.toast.info"
+71.Click Settings ,click,, "admin.transport.menu.settings"
+72.Click Promocode,click,, "admin.transport.promo.menu_item"
+73.Click Add Promo Code ,click,, "admin.transport.promo.add.btn"
+74.Open User List Dropdown,click,, "admin.transport.promo.user_list.dropdown"
+75.Select User,click,, "admin.transport.promo.user_option"
+76.Click Code Name Box,click,, "admin.transport.promo.codename.input"
+77.Enter Code Name, type, promoCode{randomAlpha}&gt;&gt; promoCodeName, "admin.transport.promo.codename.input"
+78.Open Discout Type Dropdown,click,, "admin.transport.promo.discount_type.dropdown"
+79.Select Discout Type,click,, "admin.transport.promo.discount_type.amount_option"
+80.Enter Expiry Date,type,12122026, "admin.transport.promo.expiry.input"
+81.Enter Discount Amount, type, 100, "admin.transport.promo.amount.input"
+82.Enter Minimum Order Amount, type, 1000, "admin.transport.promo.min_order.input"
+83.Enter Maximum Discount Amount, type, 100, "admin.transport.promo.max_discount.input"
+84.Enter Coupon Limit, type, 5, "admin.transport.promo.coupon_limit.input"
+85.Enter Usage Limit for One User, type, 2, "admin.transport.promo.user_limit.input"
+86.Enter Promo Code Description, type, Promo Dode For Gold Member, "admin.transport.promo.desc.textarea"
+87.Click Submit ,click,, "web.global.action.submit"
+88.Wait For Sucess, wait_until_visible, , "web.global.toast.info"
+89.wait,2000,,
+90.Click Settings ,click,, "admin.transport.menu.settings"
+91.Click Service Settings ,click,, "admin.transport.rules.menu_item"
+92.Enter Driver Accept Timeout, type, 60, "admin.transport.rules.timeout.input"
+93.Enter Driver Serach Radius, type, 50, "admin.transport.rules.radius.input"
+94.Click Submit ,click,, "web.global.action.submit"
+95.Wait For Sucess, wait_until_visible, , "web.global.toast.info"
+96.wait,1000,,
+97.Click Settings ,click,, "admin.transport.menu.settings"
+98.Click Requirment Document ,click,, "admin.transport.docs.menu_item"
+99.Click Add Document ,click,, "admin.transport.docs.add.btn"
+100.Enter Name, type, documet{randomAlpha}&gt;&gt; documentName, "admin.transport.docs.name.input"
+101.Open status Dropdown,click,, "admin.transport.docs.status.dropdown"
+102.Select Active,click,, "admin.transport.status.active_option"
+103.Click Document Expiry ,click,, "admin.transport.docs.expiry.checkbox"
+104.Click Mandatory Document ,click,, "admin.transport.docs.mandatory.checkbox"
+105.Click  Require Proof Number,click,, "admin.transport.docs.proof_no.checkbox"
+106.Enter Display Order, type, 10, "admin.transport.docs.order.input"
+107.Click Submit ,click,, "web.global.action.submit"
+108.Wait For Sucess, wait_until_visible, , "web.global.toast.info"
+109.Filter Document List,type,{documentName}, "admin.transport.docs.grid.name_filter"
+110.wait,1000,,
+111. Click Dashboard Icon,click,, "web.global.menu.dashboard"
+112.Click drivers menu,click,, "admin.drivers.menu.icon"
+113.Click Add Driver menu,click,, "admin.drivers.add_menu.link"
+114.Wait For Add Driver, wait_until_visible,, "admin.drivers.add_page.header"
+115.Click Service Category Dropdown,click,, "admin.drivers.service_dropdown.select"
+116.Select Bus Ride Option,click,, "admin.transport.dropdown.dynamic_service"
+117.Enter Driver Name, type, busdriver_{timestamp} &gt;&gt; busDriverName, "admin.drivers.fullname.input"
+118.Enter Email, type, busdriver_{timestamp}@gmail.com&gt;&gt;busEmail, "admin.drivers.email.input"
+119.Enter Contact Number, type, {randomPhone}&gt;&gt;busPhone, "admin.drivers.phone.input"
+120.Click Whatspp,click,, "admin.drivers.whatsapp.checkbox"
+121.Enter Whatspp Number,type,{busPhone}, "admin.drivers.whatsapp_phone.input"
+122.Upload Profile Image, uploadfile, "src/main/resources/test-data/busdriver.jpg", "admin.drivers.profile_image.file"
+123.Select Source,click,, "admin.drivers.source_dropdown.select"
+124.Select Instagram,click,, "admin.drivers.instagram_option.span"
+125.Select Male Gender, click, , "admin.drivers.male_gender.div"
+126.Click Vehicle Type Dropdown,click,, "admin.drivers.vehicle_dropdown.select"
+127.Select  volvo Option,click,, "admin.transport.dropdown.dynamic_vehicle"
+128.Enter Model Year, type, 2013, "admin.drivers.modelyear.input"
+129.Enter Plate No, type, KL-01-AB-1634, "admin.drivers.plateno.input"
+130. Enter Model Name, type, deisel, "admin.drivers.modelname.input"
+131.Upload Vehicle Image, uploadfile, "src/main/resources/test-data/busvolvo.jpeg", "admin.drivers.vehicle_image.file"
+132.Enter Bank Name, type, HDFC Bank, "admin.drivers.bankname.input"
+133.Enter Bank Location, type, Chennai, "admin.drivers.banklocation.input"
+134.Enter Account Number, type, 50100123456789, "admin.drivers.accountno.input"
+135.Enter Account Holder Name, type, {busDriverName}, "admin.drivers.accountholder.input"
+136.Enter Payment Email Address, type, {busEmail}, "admin.drivers.paymentemail.input"
+137.Enter IFSC Code, type, HDFC0001234, "admin.drivers.ifsc.input"
+138.Click Submit, click, , "web.global.action.submit"
+139.Wait For Driver Added,wait_until_visible, , "web.global.toast.success"
+140.Wait for Toast to hide, wait, 1000,
+141. Click Dashboard Icon,click,, "web.global.menu.dashboard"
+142.Click drivers menu,click,, "admin.drivers.menu.icon"
+143.Click Pending Documents,click,, "admin.drivers.pending_docs.link"
+144.Filter by Name,type,{busDriverName}, "admin.drivers.name_filter.input"
+145.Scroll Grid, tab, 7, "admin.drivers.name_filter.input"
+146.Click Doc Icon,click,, "admin.drivers.docs.icon"
+147.Driver Required Documents,verify,, "admin.drivers.required_docs.header"
+148.FilterDocumet List,type,{documentName}, "admin.drivers.docs_filter.input"
+149.Add Driving License,click,, "admin.drivers.docs.edit_icon"
+150.Upload Driving Iicense, uploadfile, "src/main/resources/test-data/license.jpg", "admin.drivers.profile_image.file"
+151.Enter Expiry Date,type,12-12-2026, "admin.drivers.doc_expiry.input"
+152.Click Submit, click, , "web.global.action.submit"
+153.Wait For Updated Succesfully, wait_until_visible, , "web.global.toast.updated"
+154.Click Approve Driver,click,, "admin.drivers.docs.approval"
+155.Verify Updated Succesfully, verify, , "web.global.toast.updated"
+156. Click Dashboard Icon,click,, "web.global.menu.dashboard"
+157.Click drivers menu,click,, "admin.drivers.menu.icon"
+158.Click Approved Drivers,click,, "admin.drivers.approved_docs.link"
+159.Wait For Approved Drivers List, wait_until_visible,, "admin.drivers.approved_page.header"
+160.Filter Approved Driver,type,{busDriverName}, "admin.drivers.name_filter.input"
+161.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+162.Click Transports Services Menu,click,, "admin.transport.menu.card"
+163.Wait For Transport Services, wait_until_visible,, "admin.transport.page.header"
+164.Filter Services List,type,{transportName}, "admin.transport.grid.name_filter"
+165.Click Edit Icon ,click,, "admin.drivers.docs.edit_icon"
+166.wait,2000,,
+167.Scroll Grid, tab, 5, "admin.transport.name.input"
+168.wait,2000,,
+169.Open status Dropdown,click,, "admin.transport.status.dropdown"
+170.Select Deactivate,click,, "admin.transport.status.deactivate_option"
+171.Click  Submit,click,, "web.global.action.submit"
+172.Wait For Sucess, wait_until_visible, , "web.global.toast.info"
+173.wait,2000,,</t>
+  </si>
+  <si>
+    <t>1. Click Dashboard Icon,click,, "web.global.menu.dashboard"
 2. Click Delivery Services,click,,"admin.deliveryservice.menu"
 3. Wait For Delivery Services,wait_until_visible,,"admin.deliveryservice.header"
 4. Click Home Icon Food Delivery,click,,"admin.store.food_delivery.home_icon"
@@ -3000,7 +2750,7 @@
 77. wait,1000,,</t>
   </si>
   <si>
-    <t>1. Click badge,click,,"admin.deliveryservice.badge.shield"
+    <t>1. Click Dashboard Icon,click,, "web.global.menu.dashboard"
 2. Click Delivery Services,click,,"admin.deliveryservice.menu"
 3. Wait For Delivery Services,wait_until_visible,,"admin.deliveryservice.header"
 4. Click Home Icon Food Delivery,click,,"admin.store.food_delivery.home_icon"
@@ -3067,7 +2817,7 @@
 65. wait,1000,,</t>
   </si>
   <si>
-    <t>1. Click badge,click,,"admin.deliveryservice.badge.shield"
+    <t>1. Click Dashboard Icon,click,, "web.global.menu.dashboard"
 2. Click Delivery Services,click,,"admin.deliveryservice.menu"
 3. Wait For Delivery Services,wait_until_visible,,"admin.deliveryservice.header"
 4. Click Home Icon Food Delivery,click,,"admin.store.food_delivery.home_icon"
@@ -3166,7 +2916,7 @@
 97. wait,1000,,</t>
   </si>
   <si>
-    <t>1.Click badge, click, , "admin.deliveryservice.badge.shield"
+    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
 2.Click Delivery Services, click, , "admin.deliveryservice.menu"
 3.Verify Delivery Services, verify, , "admin.deliveryservice.header"
 4.Click Add Service Category, click, , "admin.deliveryservice.add_category_btn"
@@ -3307,7 +3057,7 @@
 139.Open Product Category Dropdown, click, , "admin.store.products.category_dropdown"
 140.Select curd, click, , "admin.deliveryservice.products.category.option_dynamic"
 141.wait, 1000, ,""
-142.Click badge, click, , "admin.deliveryservice.badge.shield"
+142.Click Dashboard Icon,click,, "web.global.menu.dashboard"
 143.Click Delivery Services, click, , "admin.deliveryservice.menu"
 144.Verify Delivery Services, verify, , "admin.deliveryservice.header"
 145.Filter Services List, type, {deliveryName}, "admin.deliveryservice.grid.filter_input"
@@ -3318,6 +3068,255 @@
 150.Click Submit, click, , "web.global.action.submit"
 151.Filter Services List, type, {deliveryName}, "admin.deliveryservice.grid.filter_input"
 152.wait, 1000, ,</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2.Click Delivery Services,click,,"admin.provider_service.menu_link"
+3.Verify Delivery Services,verify,,"admin.provider_service.on_demand_header"
+4.Filter service List,type,Plumbers,"admin.provider_service.services.filter.input"
+5.Click Home Icon Plumbers,click,,"admin.provider_service.services.home.icon_by_row_plumbers"
+6.Verify Plumbers Summary,verify,,"admin.provider_service.services.plumbers_summary.header"
+7.Click Providers,click,,"admin.provider_service.providers.root.button"
+8.Select Add Providers,click,,"admin.provider_service.providers.add_provider.menu"
+9.Verify Add Provider,verify,,"admin.provider_service.provider_form.header"
+10.Enter Provider Full Name, type, Plumber{randomAlpha}&gt;&gt; plumberName, "admin.provider_service.provider_form.fullname.input"
+11.Upload Plumber Image, uploadfile, "src/main/resources/test-data/plumber.jpg", "admin.provider_service.provider_form.avatar.file"
+12.Enter Email, type, Plumber_{timestamp}@gmail.com&gt;&gt;plumberEmail, "admin.provider_service.provider_form.email.input"
+13.Enter Contact Number, type, {randomPhone}, "admin.provider_service.provider_form.contact_number.input"
+14.Enter Landmark, type, Near LIC Building, "admin.provider_service.provider_form.landmark.input"
+15.Open Delivery Radius Dropdown,click,,"admin.provider_service.provider_form.radius.dropdown"
+16.Select Twenty Five Kilometer,click,,"admin.provider_service.provider_form.radius.option_25km"
+17.Enter Minimum Order, type, 10, "admin.provider_service.provider_form.min_order.input"
+18.Enter Provider Address, type, plumber chennai, "admin.provider_service.provider_form.address.input"
+19.wait,1000,,
+20.Select First Option,arrow_down,,"admin.provider_service.provider_form.address.input"
+21.Confirm Option,press_enter,,"admin.provider_service.provider_form.address.input"
+22.wait,1000,,
+23.Click Everyday Checkbox, click, , "admin.provider_service.provider_form.everyday.checkbox"
+24.Click 09:00 AM-10:00 AM, click, , "admin.provider_service.provider_form.time_slot.09_10am"
+25.Click 10:00 AM-11:00 AM, click, , "admin.provider_service.provider_form.time_slot.10_11am"
+26.Click 11:00 AM-12:00 PM, click, , "admin.provider_service.provider_form.time_slot.11_12pm"
+27.Click 12:00 PM-01:00 PM, click, , "admin.provider_service.provider_form.time_slot.12_01pm"
+28.Click 02:00 PM-03:00 PM, click, , "admin.provider_service.provider_form.time_slot.02_03pm"
+29.Click 03:00 PM-04:00 PM, click, , "admin.provider_service.provider_form.time_slot.03_04pm"
+30.Enter Bank Name, type, federal, "admin.provider_service.provider_form.bank_name.input"
+31.Enter Bank Location,type, chennai, "admin.provider_service.provider_form.bank_location.input"
+32.Scroll Grid, tab, 1, "admin.provider_service.provider_form.bank_location.input"
+33.Enter Account Number, type, 123456789012, "admin.provider_service.provider_form.account_number.input"
+34.Enter Account Holder Name, type, {plumberName}, "admin.provider_service.provider_form.account_holder.input"
+35.Enter Payment Email Address, type, {plumberEmail}, "admin.provider_service.provider_form.payment_email.input"
+36.Enter BIC Code, type, 1234, "admin.provider_service.provider_form.bic_code.input"
+37.Click Save, click, , "web.global.login.submit_btn"
+38.Verify Sucess, verify, , "web.global.toast.info"
+39.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
+40.Click Providers,click,,"admin.provider_service.providers.root.button"
+41.Select Pending Document Providers,click,,"admin.provider_service.providers.pending_docs.menu"
+42.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
+43.Click Document Icon,click,,"admin.provider_service.providers.grid.document.icon"
+44.Provider Required Documents,verify,,"admin.provider_service.provider_docs.header"
+45.FilterDocumet List,type,Store Address,"admin.provider_service.provider_docs.filter.input"
+46.Add Address Proof,click,,"admin.provider_service.provider_docs.edit_action.icon"
+47.Upload Address Proof, uploadfile, "src/main/resources/test-data/addressproof.png", "admin.provider_service.provider_docs.upload_input"
+48.Enter Expiry Date,type,2026-12-12,"admin.provider_service.provider_docs.expiry_date.input"
+49.Click Submit, click, , "web.global.action.submit"
+50.Verify Updated Succesfully, verify, , "web.global.toast.updated"
+51.FilterDocumet List,type,Store Address,"admin.provider_service.provider_docs.filter.input"
+52.Click Approve Store,click,,"admin.provider_service.provider_docs.approve.icon"
+53.Verify Updated Succesfully, verify, , "web.global.toast.updated"
+54.Click Back, click, , "admin.provider_service.global.action.back_widget_btn"
+55.Click Providers,click,,"admin.provider_service.providers.root.button"
+56.Select Provider List,click,,"admin.provider_service.providers.provider_list.menu"
+57.Verify Approved Provider,verify,,"admin.provider_service.providers.grid.approved_plumbers.header"
+58.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
+59.Click Doc Icon,click,,"admin.provider_service.providers.grid.document.icon"
+60.Click Eye Icon,click,,"admin.provider_service.providers.grid.view_eye.icon"
+61.Click Back, click, , "admin.provider_service.global.action.back_widget_btn"
+62.Verify Approved Provider,verify,,"admin.provider_service.providers.grid.approved_plumbers.header"
+63.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
+64.Scroll Grid, tab, 11, "admin.provider_service.providers.grid.name_filter"
+65.Click Wallet Icon,click,,"admin.provider_service.providers.grid.wallet.icon"
+66.Click Manage Transaction, click, , "admin.provider_service.wallet.manage_transaction.btn"
+67.Enter Wallet Amount, type, 1000, "admin.provider_service.wallet.amount.input"
+68.Open Choose Option Dropdown,click, , "admin.provider_service.wallet.options.dropdown"
+69.Select Add Money,click, , "admin.provider_service.wallet.options.add_money"
+70.Click Submit, click, , "web.global.action.submit"
+71.Verify Saved Succesfully, verify, , "web.global.toast.success"
+72.Click Manage Transaction, click, , "admin.provider_service.wallet.manage_transaction.btn"
+73.Enter Wallet Amount, type, 200, "admin.provider_service.wallet.amount.input"
+74.Open Choose Option Dropdown,click, , "admin.provider_service.wallet.options.dropdown"
+75.Select Deduct Money,click, , "admin.provider_service.wallet.options.deduct_money"
+76.Click Submit, click, , "web.global.action.submit"
+77.Verify Saved Succesfully, verify, , "web.global.toast.success"
+78.Click Back, click, , "admin.provider_service.global.action.back_normal_btn"
+79.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
+80.Click Doc Icon,click, , "admin.provider_service.providers.grid.document.icon"
+81.FilterDocumet List,type,Store Address,"admin.provider_service.provider_docs.filter.input"
+82.Click Reject Document,click, , "admin.provider_service.provider_docs.reject.icon"
+83.Click Reject Yes,click, , "web.global.dialog.btn_confirm_yes"
+84.Rejection Reason,type,document insufficent,"web.global.dialog.textarea_reason"
+85..Click Reject Yes,click, , "web.global.dialog.btn_confirm_yes"
+86.Click Back, click, , "admin.provider_service.global.action.back_widget_btn"
+87.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
+88.Scroll Grid, tab, 13, "admin.provider_service.providers.grid.name_filter"
+89.Click Block Provider,click, , "admin.provider_service.providers.grid.block.icon"
+90.Click Block Yes,click, , "web.global.dialog.btn_confirm_yes"
+91.Blocking Reason,type,customer complaints,"web.global.dialog.textarea_reason"
+92.Click block Yes,click, , "web.global.dialog.btn_confirm_yes"
+93.Click Providers,click, , "admin.provider_service.providers.root.button"
+94.Select Blocked Providers,click, , "admin.provider_service.providers.blocked_list.menu"
+95.Verify Blocked Provider,verify, , "admin.provider_service.providers.grid.blocked_plumbers.header"
+96.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
+97.Scroll Grid, tab, 12, "admin.provider_service.providers.grid.name_filter"
+98.Click Unblock Provider,click, , "admin.provider_service.providers.grid.unblock.icon"
+99.Click Providers,click, , "admin.provider_service.providers.root.button"
+100.Select Provider List,click, , "admin.provider_service.providers.provider_list.menu"
+101.Filter Plumber List,type,{plumberName},"admin.provider_service.providers.grid.name_filter"
+102.wait,1000,,</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2.Click Provider Services,click,,"admin.provider_service.menu_link"
+3.Verify Provider Services,verify,,"admin.provider_service.on_demand_header"
+4.Click Add New Services,click,,"admin.provider_service.services.add_new.btn"
+5.Enter Service Name, type, Painter{randomAlpha}&gt;&gt; serviceName, "admin.provider_service.services.name.input"
+6.Enter Service Name Tamil, type, பெயிண்டர், "admin.provider_service.services.name_tamil.input"
+7.Enter Service Name Arabic, type, دهان, "admin.provider_service.services.name_arabic.input"
+8.Enter Service Name Hindi, type, पेंटर, "admin.provider_service.services.name_hindi.input"
+9.Enter Slug, type, painter, "admin.provider_service.services.slug.input"
+10.Upload Service Image, uploadfile, "src/main/resources/test-data/painter.jpg", "admin.provider_service.services.image.file"
+11.wait,2000,,
+12.Open status Dropdown,click,,"admin.provider_service.services.status.dropdown"
+13.Select Activate,click,,"admin.provider_service.services.status.option_activate"
+14.Open Select City Dropdown,click,,"admin.provider_service.services.city.dropdown"
+15.Select {areaName},click,,"admin.provider_service.services.city.option_dynamic"
+16.Click Submit,click,,"web.global.action.submit"
+17.Filter Services List,type,{serviceName},"admin.provider_service.services.filter.input"
+18.Click Home Icon ,click,,"admin.provider_service.services.home.icon"
+19.Click Settings ,click,,"admin.provider_service.settings.menu.button"
+20.Click Requirment Document ,click,,"admin.provider_service.settings.req_document.tab"
+21.Click Add Document ,click,,"admin.provider_service.req_docs.add.btn"
+22.Enter Name, type, documet{randomAlpha}&gt;&gt; providerDocumentName, "admin.provider_service.req_docs.name.input"
+23.Open status Dropdown,click,,"admin.provider_service.req_docs.status.dropdown"
+24.Select Active,click,,"admin.provider_service.req_docs.status.option_active"
+25.Click Document Expiry ,click,,"admin.provider_service.req_docs.expiry_toggle"
+26.Click Mandatory Document ,click,,"admin.provider_service.req_docs.mandatory_toggle"
+27.Click Submit ,click,,"web.global.action.submit"
+28.Verify Sucess, verify, , "web.global.toast.info"
+29.Filter Document List,type,{providerDocumentName},"admin.provider_service.req_docs.filter.input"
+30.Click Settings ,click,,"admin.provider_service.settings.menu.button"
+31.Click Promocode ,click,,"admin.provider_service.settings.promocode.tab"
+32.Click Add Promo Code ,click,,"admin.provider_service.promocode.add.btn"
+33.Open User List Dropdown,click,,"admin.provider_service.promocode.user_list.dropdown"
+34.Select User,click,,"admin.provider_service.promocode.user_list.option_dynamic"
+35.Click Code Name Box,click,,"admin.provider_service.promocode.code_name.box"
+36.Enter Code Name, type, promoCode{randomAlpha}&gt;&gt; providerPromoCodeName, "admin.provider_service.promocode.code_name.box"
+37.Open Discout Type Dropdown,click,,"admin.provider_service.promocode.discount_type.dropdown"
+38.Select Discout Type,click,,"admin.provider_service.promocode.discount_type.option_amount"
+39.Enter Expiry Date,type,12122026,"admin.provider_service.promocode.expiry_date.input"
+40.Enter Discount Amount, type, 100, "admin.provider_service.promocode.discount_amount.input"
+41.Enter Minimum Order Amount, type, 1000, "admin.provider_service.promocode.min_order_amount.input"
+42.Enter Maximum Discount Amount, type, 100, "admin.provider_service.promocode.max_discount.input"
+43.Enter Coupon Limit, type, 5,"admin.provider_service.promocode.coupon_limit.input"
+44.Enter Usage Limit for One User, type, 2,"admin.provider_service.promocode.usage_limit_per_user.input"
+45.Enter Promo Code Description, type, Promo Dode For Gold Member,"admin.provider_service.promocode.description.textarea"
+46.Click Submit ,click,,"web.global.action.submit"
+47.Verify Sucess, verify, , "web.global.toast.info"
+48.Filter PromoCode List,type,{providerPromoCodeName},"admin.provider_service.promocode.filter.input"
+49.Click Providers,click,,"admin.provider_service.providers.root.button"
+50.Select Add Providers,click,,"admin.provider_service.providers.add_provider.menu"
+51.Verify Add Provider,verify,,"admin.provider_service.provider_form.header"
+52.Enter Provider Full Name, type, Painter{randomAlpha}&gt;&gt; painterName, "admin.provider_service.provider_form.fullname.input"
+53.Upload Painter Image, uploadfile, "src/main/resources/test-data/painter.jpg", "admin.provider_service.provider_form.avatar.file"
+54.Enter Email, type, Painter_{timestamp}@gmail.com&gt;&gt;painterEmail, "admin.provider_service.provider_form.email.input"
+55.Enter Contact Number, type, {randomPhone}, "admin.provider_service.provider_form.contact_number.input"
+56.Enter Landmark, type, Near LIC Building, "admin.provider_service.provider_form.landmark.input"
+57.Open Delivery Radius Dropdown,click,,"admin.provider_service.provider_form.radius.dropdown"
+58.Select Twenty Five Kilometer,click,,"admin.provider_service.provider_form.radius.option_25km"
+59.Enter Minimum Order, type, 10, "admin.provider_service.provider_form.min_order.input"
+60.Enter Provider Address, type, painter chennai, "admin.provider_service.provider_form.address.input"
+61.wait,1000,,
+62.Select First Option,arrow_down,,"admin.provider_service.provider_form.address.input"
+63.Confirm Option,press_enter,,"admin.provider_service.provider_form.address.input"
+64.wait,1000,,
+65.Click Everyday Checkbox, click, , "admin.provider_service.provider_form.everyday.checkbox"
+66.Click 09:00 AM-10:00 AM, click, , "admin.provider_service.provider_form.time_slot.09_10am"
+67.Click 10:00 AM-11:00 AM, click, , "admin.provider_service.provider_form.time_slot.10_11am"
+68.Click 11:00 AM-12:00 PM, click, , "admin.provider_service.provider_form.time_slot.11_12pm"
+69.Click 12:00 PM-01:00 PM, click, , "admin.provider_service.provider_form.time_slot.12_01pm"
+70.Click 02:00 PM-03:00 PM, click, , "admin.provider_service.provider_form.time_slot.02_03pm"
+71.Click 03:00 PM-04:00 PM, click, , "admin.provider_service.provider_form.time_slot.03_04pm"
+72.Enter Bank Name, type, federal, "admin.provider_service.provider_form.bank_name.input"
+73.Enter Bank Location,type, chennai, "admin.provider_service.provider_form.bank_location.input"
+74.Scroll Grid, tab, 1, "admin.provider_service.provider_form.bank_location.input"
+75.Enter Account Number, type, 123456789012, "admin.provider_service.provider_form.account_number.input"
+76.Enter Accont Holder Name, type, {painterName}, "admin.provider_service.provider_form.account_holder.input"
+77.Enter Payment Email Address, type, {painterEmail}, "admin.provider_service.provider_form.payment_email.input"
+78.Enter BIC Code, type, 1234, "admin.provider_service.provider_form.bic_code.input"
+79.Click Save, click, , "web.global.login.submit_btn"
+80.Verify Sucess, verify, , "web.global.toast.info"
+81.Filter Painter List,type,{painterName},"admin.provider_service.providers.grid.name_filter"
+82.Click Providers,click,,"admin.provider_service.providers.root.button"
+83.Select Pending Document Providers,click,,"admin.provider_service.providers.pending_docs.menu"
+84.Filter Plumber List,type,{painterName},"admin.provider_service.providers.grid.name_filter"
+85.Click Document Icon,click,,"admin.provider_service.providers.grid.document.icon"
+86.Provider Required Documents,verify,,"admin.provider_service.provider_docs.header"
+87.FilterDocumet List,type,{providerDocumentName},"admin.provider_service.provider_docs.filter.input"
+88.Add Address Proof,click,,"admin.provider_service.provider_docs.edit_action.icon"
+89.Upload Address Proof, uploadfile, "src/main/resources/test-data/addressproof.png", "admin.provider_service.provider_docs.upload_input"
+90.Enter Expiry Date,type,2026-12-12,"admin.provider_service.provider_docs.expiry_date.input"
+91.Click Submit, click, , "web.global.action.submit"
+92.Verify Updated Succesfully, verify, , "web.global.toast.updated"
+93.FilterDocumet List,type,{providerDocumentName},"admin.provider_service.provider_docs.filter.input"
+94.Click Approve Store,click,,"admin.provider_service.provider_docs.approve.icon"
+95.Verify Updated Succesfully, verify, , "web.global.toast.updated"
+96.Click Back, click, , "admin.provider_service.global.action.back_widget_btn"
+97.Click Providers,click,,"admin.provider_service.products.menu_category_btn"
+98.Click Add New Category,click,,"admin.provider_service.category.add_new.btn"
+99.Enter Category Name, type,residentialPainter{randomAlpha}&gt;&gt; painterCategoryName, "admin.provider_service.category.name.input"
+100.Enter Category Name Tamil, type, குடியிருப்பு பெயிண்டர், "admin.provider_service.category.name_tamil.input"
+101.Enter Category Name Arabic, type, دهان سكني, "admin.provider_service.category.name_arabic.input"
+102.Enter Category Name Hindi, type, आवासीय पेंटर, "admin.provider_service.category.name_hindi.input"
+103.Open Category status Dropdown,click,,"admin.provider_service.category.status.dropdown"
+104.Select Activate,click,,"admin.provider_service.category.status.option_active"
+105.Upload Category Image, uploadfile, "src/main/resources/test-data/painter.jpg", "admin.provider_service.category.image.file"
+106.wait,2000,,
+107.Click Submit,click,,"web.global.action.submit"
+108.Filter Category Name,type,{painterCategoryName},"admin.provider_service.category.filter.input"
+109.Click Providers,click,,"admin.provider_service.providers.root.button"
+110.Select Provider List,click,,"admin.provider_service.providers.provider_list.menu"
+111.Filter Painter List,type,{painterName},"admin.provider_service.providers.grid.name_filter"
+112.Scroll Grid, tab, 7, "admin.provider_service.providers.grid.name_filter"
+113.Click Package Icon,click,,"admin.provider_service.packages.icon"
+114.Click Add Package,click,,"admin.provider_service.packages.add_new.btn"
+115.Open Category Dropdown,click,,"admin.provider_service.packages.category.dropdown"
+116.Select Activate,click,,"admin.provider_service.packages.category.option_dynamic"
+117.Enter Package Name, type, package{randomAlpha}&gt;&gt; packageName, "admin.provider_service.packages.name.input"
+118.Enter Amount, type, 1000, "admin.provider_service.packages.amount.input"
+119.Open Max Book Quantity Dropdown,click,,"admin.provider_service.packages.max_book_qty.dropdown"
+120.Select 4,click,,"admin.provider_service.packages.max_book_qty.option_4"
+121.Open Status Dropdown,click,,"admin.provider_service.packages.status.dropdown"
+122.Select Activate,click,,"admin.provider_service.packages.status.option_activate"
+123.Enter Description, type, Premium residential painting package, "admin.provider_service.packages.description.textarea"
+124.Click Submit,click,,"web.global.action.submit"
+125.wait,1000,,
+126.Click back,click,,"admin.provider_service.global.action.back_normal_btn"
+127.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+128.Click Delivery Services,click,,"admin.provider_service.menu_link"
+129.Filter Services List,type,{serviceName},"admin.provider_service.services.filter.input"
+130.Click Edit Icon ,click,,"admin.provider_service.services.edit.icon"
+131.Enter Service Name Tamil, type, பெயிண்டர், "admin.provider_service.services.name_tamil.input"
+132.Enter Service Name Arabic, type, دهان, "admin.provider_service.services.name_arabic.input"
+133.Enter Service Name Hindi, type, पेंटर, "admin.provider_service.services.name_hindi.input"
+134.Scroll Grid, tab, 4, "admin.provider_service.services.name_hindi.input"
+135.Open status Dropdown,click,,"admin.provider_service.services.status.dropdown"
+136.Select Deactivate,click,,"admin.provider_service.services.status.option_deactivate"
+137.Click Submit,click,,"web.global.action.submit"
+138.Click back,click,,"admin.provider_service.global.action.back_normal_btn"
+139. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+140.Click badge,click,,"admin.provider_service.badge.icon"
+141.Click provider Services,click,,"admin.provider_service.menu_link"
+142.Filter Services List,type,{serviceName},"admin.provider_service.services.filter.input"
+143.wait,1000,,</t>
   </si>
 </sst>
 </file>
@@ -3734,7 +3733,7 @@
         <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>22</v>
@@ -3743,7 +3742,7 @@
         <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>37</v>
@@ -3812,13 +3811,13 @@
         <v>27</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>45</v>
@@ -3884,16 +3883,16 @@
         <v>30</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -3956,13 +3955,13 @@
         <v>32</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>45</v>
@@ -4015,36 +4014,36 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="G2" s="8" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4060,7 +4059,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F63FB6C5-854C-4D7D-9CEB-846B4D7D2F52}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF16C04E-51BB-4902-91C6-410B8EB3791F}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4101,19 +4100,19 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>53</v>
+        <v>118</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>46</v>
@@ -4132,7 +4131,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{319ADEF0-2336-4246-BBC3-461C4994D500}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E742ED82-3510-47F4-AA85-6344770C749C}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4173,22 +4172,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4204,7 +4203,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0F6277B-DBCF-4BFF-819C-1E90748D3258}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39F69F54-6E80-4C66-8F82-CEFA135D089A}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4245,22 +4244,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4317,22 +4316,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4384,7 +4383,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4404,13 +4403,13 @@
         <v>52</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>41</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4483,7 +4482,7 @@
         <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>41</v>
@@ -4538,7 +4537,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4558,13 +4557,13 @@
         <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>38</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -4606,7 +4605,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4620,19 +4619,19 @@
         <v>14</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>42</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4681,7 +4680,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4695,19 +4694,19 @@
         <v>15</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4756,7 +4755,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4770,19 +4769,19 @@
         <v>17</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>44</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4831,7 +4830,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4842,22 +4841,22 @@
         <v>29</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4915,22 +4914,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{932F4E60-82DC-4110-89C7-7715EDEB7920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{991FE53F-45BB-4A62-A524-8ECEED3CD777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="13" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>
@@ -1982,88 +1982,6 @@
   </si>
   <si>
     <t>1. Click Dashboard Icon,click,,"web.global.menu.dashboard"
-2. Click Customer Icon,click,,"admin.menu.customer_icon"
-3. Click Add Customers,click,,"admin.menu.add_customers"
-4. Wait For Customer Heading,wait_until_visible,,"admin.customer.add_heading"
-5. Enter Customer Name,type,customer{randomAlpha} &gt;&gt; customerName,"admin.customer.input_name"
-6. Enter Email,type,customer_{timestamp}@gmail.com&gt;&gt;customerEmail,"admin.customer.input_email"
-7. Enter Contact Number,type,{randomPhone},"admin.customer.input_phone"
-8. Open Gender,click,,"admin.customer.dropdown_gender"
-9. Select Male,click,,"admin.customer.select_gender_male"
-10. Upload Profile Image,uploadfile,"src/main/resources/test-data/customer.jpg","admin.customer.upload_profile_img"
-11. Click Submit,click,,"web.global.action.submit"
-12. Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
-13. Click Dashboard,click,,"web.global.menu.dashboard"
-14. Click Customer Icon,click,,"admin.menu.customer_icon"
-15. Click Verified Customers,click,,"admin.menu.verified_customers"
-16. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
-17. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
-18. Scroll Grid,tab,7,"admin.customer.filter_name"
-19. Click Edit Icon,click,,"admin.customer.grid.btn_edit"
-20. Click Close,click,,"web.global.action.close"
-21. Click Wallet Icon,click,,"admin.customer.grid.btn_wallet"
-22. Click Add Money,click,,"admin.customer.wallet.btn_add_money"
-23. Enter Wallet Amount,type,1000,"admin.customer.wallet.input_amount"
-24. Open Choose Option Dropdown,click,,"admin.customer.wallet.dropdown_option"
-25. Select Add Money,click,,"admin.customer.wallet.select_add_money"
-26. Click Submit,click,,"web.global.action.submit"
-27. Wait For Saved Successfully,wait_until_visible,,"web.global.toast.success"
-28. Click Add Money,click,,"admin.customer.wallet.btn_add_money"
-29. Enter Wallet Amount,type,200,"admin.customer.wallet.input_amount"
-30. Open Choose Option Dropdown,click,,"admin.customer.wallet.dropdown_option"
-31. Select Deduct Money,click,,"admin.customer.wallet.select_deduct_money"
-32. Click Submit,click,,"web.global.action.submit"
-33. Wait For Saved Successfully,wait_until_visible,,"web.global.toast.success"
-34. Click dashboard Icon,click,,"web.global.menu.dashboard"
-35. Click Customer Icon,click,,"admin.menu.customer_icon"
-36. Click Verified Customers,click,,"admin.menu.verified_customers"
-37. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
-38. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
-39. Scroll Grid,tab,7,"admin.customer.filter_name"
-40. Click Loyalty Points Icon,click,,"admin.customer.grid.btn_loyalty_points"
-41. Click Manage Loyalty Points,click,,"admin.customer.loyalty.btn_manage"
-42. Open Service Dropdown,click,,"admin.customer.loyalty.dropdown_service"
-43. Select Bike Ride,click,,"admin.customer.loyalty.select_bike_ride"
-44. Open Choose Option Dropdown,click,,"admin.customer.loyalty.dropdown_option"
-45. Select Add Points,click,,"admin.customer.loyalty.select_add_points"
-46. Enter Points,type,30,"admin.customer.loyalty.input_points"
-47. Click Submit,click,,"web.global.action.submit"
-48. Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
-49. Click Manage Loyalty Points,click,,"admin.customer.loyalty.btn_manage"
-50. Open Service Dropdown,click,,"admin.customer.loyalty.dropdown_service"
-51. Select Bike Ride,click,,"admin.customer.loyalty.select_bike_ride"
-52. Open Choose Option Dropdown,click,,"admin.customer.loyalty.dropdown_option"
-53. Select Deduct Points,click,,"admin.customer.loyalty.select_deduct_points"
-54. Enter Points,type,10,"admin.customer.loyalty.input_points"
-55. Click Submit,click,,"web.global.action.submit"
-56. Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
-57. Click Dashboard Icon,click,,"web.global.menu.dashboard"
-58. Click Customer Icon,click,,"admin.menu.customer_icon"
-59. Click Verified Customers,click,,"admin.menu.verified_customers"
-60. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
-61. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
-62. Scroll Grid,tab,7,"admin.customer.filter_name"
-63. Click Disable Icon,click,,"admin.customer.grid.btn_block"
-64. Click Disable User Yes,click,,"web.global.dialog.btn_confirm_yes"
-65. Disable Reason,type,Client Complaints,"web.global.dialog.textarea_reason"
-66. Click Reject Yes,click,,"web.global.dialog.btn_confirm_yes"
-67. Verify Added Successfully,verify,,"web.global.toast.info"
-68. Click Dashboard Icon,click,,"web.global.menu.dashboard"
-69. Click Customer Icon,click,,"admin.menu.customer_icon"
-70. Click Blocked Customers,click,,"admin.menu.blocked_customers"
-71. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
-72. Scroll Grid,tab,10,"admin.customer.filter_name"
-73.Wait For Enable Icon,wait_until_visible,,"admin.customer.grid.btn_status_enable"
-74. Click Enable Icon,click,,"admin.customer.grid.btn_status_enable"
-75. Click Enable Yes,click,,"web.global.dialog.btn_confirm_yes"
-76. Click Dashboard Icon,click,,"web.global.menu.dashboard"
-77. Click Customer Icon,click,,"admin.menu.customer_icon"
-78. Click Verified Customers,click,,"admin.menu.verified_customers"
-79. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
-80. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"</t>
-  </si>
-  <si>
-    <t>1. Click Dashboard Icon,click,,"web.global.menu.dashboard"
 2. Click Setting menu,click,,"web.global.menu.settings"
 3. Click City admin menu,click,,"admin.menu.city_admin"
 4. Wait For City Admin List,wait_until_visible,,"admin.city_admin.list_heading"
@@ -3350,6 +3268,89 @@
   </si>
   <si>
     <t>SA_TS_17</t>
+  </si>
+  <si>
+    <t>1. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+2. Click Customer Icon,click,,"admin.menu.customer_icon"
+3. Click Add Customers,click,,"admin.menu.add_customers"
+4. Wait For Customer Heading,wait_until_visible,,"admin.customer.add_heading"
+5. Enter Customer Name,type,customer{randomAlpha} &gt;&gt; customerName,"admin.customer.input_name"
+6. Enter Email,type,customer_{timestamp}@gmail.com&gt;&gt;customerEmail,"admin.customer.input_email"
+7. Enter Contact Number,type,{randomPhone},"admin.customer.input_phone"
+8.Enter Emergency Number,type,{randomPhone},"admin.customer.input_Emergency_phone"
+9. Open Gender,click,,"admin.customer.dropdown_gender"
+10. Select Male,click,,"admin.customer.select_gender_male"
+11. Upload Profile Image,uploadfile,"src/main/resources/test-data/customer.jpg","admin.customer.upload_profile_img"
+12. Click Submit,click,,"web.global.action.submit"
+13. Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
+14. Click Dashboard,click,,"web.global.menu.dashboard"
+15. Click Customer Icon,click,,"admin.menu.customer_icon"
+16. Click Verified Customers,click,,"admin.menu.verified_customers"
+17. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
+18. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+19. Scroll Grid,tab,7,"admin.customer.filter_name"
+20. Click Edit Icon,click,,"admin.customer.grid.btn_edit"
+21. Click Close,click,,"web.global.action.close"
+22. Click Wallet Icon,click,,"admin.customer.grid.btn_wallet"
+23. Click Add Money,click,,"admin.customer.wallet.btn_add_money"
+24. Enter Wallet Amount,type,1000,"admin.customer.wallet.input_amount"
+25. Open Choose Option Dropdown,click,,"admin.customer.wallet.dropdown_option"
+26. Select Add Money,click,,"admin.customer.wallet.select_add_money"
+27. Click Submit,click,,"web.global.action.submit"
+28. Wait For Saved Successfully,wait_until_visible,,"web.global.toast.success"
+29. Click Add Money,click,,"admin.customer.wallet.btn_add_money"
+30. Enter Wallet Amount,type,200,"admin.customer.wallet.input_amount"
+31. Open Choose Option Dropdown,click,,"admin.customer.wallet.dropdown_option"
+32. Select Deduct Money,click,,"admin.customer.wallet.select_deduct_money"
+33. Click Submit,click,,"web.global.action.submit"
+34. Wait For Saved Successfully,wait_until_visible,,"web.global.toast.success"
+35. Click dashboard Icon,click,,"web.global.menu.dashboard"
+36. Click Customer Icon,click,,"admin.menu.customer_icon"
+37. Click Verified Customers,click,,"admin.menu.verified_customers"
+38. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
+39. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+40. Scroll Grid,tab,7,"admin.customer.filter_name"
+41. Click Loyalty Points Icon,click,,"admin.customer.grid.btn_loyalty_points"
+42. Click Manage Loyalty Points,click,,"admin.customer.loyalty.btn_manage"
+43. Open Service Dropdown,click,,"admin.customer.loyalty.dropdown_service"
+44. Select Bike Ride,click,,"admin.customer.loyalty.select_bike_ride"
+45. Open Choose Option Dropdown,click,,"admin.customer.loyalty.dropdown_option"
+46. Select Add Points,click,,"admin.customer.loyalty.select_add_points"
+47. Enter Points,type,30,"admin.customer.loyalty.input_points"
+48. Click Submit,click,,"web.global.action.submit"
+49. Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
+50. Click Manage Loyalty Points,click,,"admin.customer.loyalty.btn_manage"
+51. Open Service Dropdown,click,,"admin.customer.loyalty.dropdown_service"
+52. Select Bike Ride,click,,"admin.customer.loyalty.select_bike_ride"
+53. Open Choose Option Dropdown,click,,"admin.customer.loyalty.dropdown_option"
+54. Select Deduct Points,click,,"admin.customer.loyalty.select_deduct_points"
+55. Enter Points,type,10,"admin.customer.loyalty.input_points"
+56. Click Submit,click,,"web.global.action.submit"
+57. Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
+58. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+59. Click Customer Icon,click,,"admin.menu.customer_icon"
+60. Click Verified Customers,click,,"admin.menu.verified_customers"
+61. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
+62. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+63. Scroll Grid,tab,7,"admin.customer.filter_name"
+64. Click Disable Icon,click,,"admin.customer.grid.btn_block"
+65. Click Disable User Yes,click,,"web.global.dialog.btn_confirm_yes"
+66. Disable Reason,type,Client Complaints,"web.global.dialog.textarea_reason"
+67. Click Reject Yes,click,,"web.global.dialog.btn_confirm_yes"
+68. Verify Added Successfully,verify,,"web.global.toast.info"
+69. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+70. Click Customer Icon,click,,"admin.menu.customer_icon"
+71. Click Blocked Customers,click,,"admin.menu.blocked_customers"
+72. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+73. Scroll Grid,tab,10,"admin.customer.filter_name"
+74.Wait For Enable Icon,wait_until_visible,,"admin.customer.grid.btn_status_enable"
+75. Click Enable Icon,click,,"admin.customer.grid.btn_status_enable"
+76. Click Enable Yes,click,,"web.global.dialog.btn_confirm_yes"
+77. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+78. Click Customer Icon,click,,"admin.menu.customer_icon"
+79. Click Verified Customers,click,,"admin.menu.verified_customers"
+80. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
+81. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"</t>
   </si>
 </sst>
 </file>
@@ -3850,7 +3851,7 @@
         <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>45</v>
@@ -3922,10 +3923,10 @@
         <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -3994,7 +3995,7 @@
         <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>45</v>
@@ -4047,10 +4048,10 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
@@ -4067,16 +4068,16 @@
         <v>56</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>57</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4145,7 +4146,7 @@
         <v>36</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>46</v>
@@ -4217,7 +4218,7 @@
         <v>55</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>58</v>
@@ -4289,7 +4290,7 @@
         <v>70</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>69</v>
@@ -4352,16 +4353,16 @@
         <v>72</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>69</v>
@@ -4421,7 +4422,7 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>64</v>
@@ -4508,7 +4509,7 @@
         <v>52</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>41</v>
@@ -4662,7 +4663,7 @@
         <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>38</v>
@@ -4955,7 +4956,7 @@
         <v>62</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>61</v>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{991FE53F-45BB-4A62-A524-8ECEED3CD777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F9C63FF-BF89-4D41-8468-98271F6D31C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="19" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>
@@ -30,7 +30,11 @@
     <sheet name="ProviderServiceCompleteTest" sheetId="46" r:id="rId15"/>
     <sheet name="SubscriptionPlanTest" sheetId="47" r:id="rId16"/>
     <sheet name="PanicCallTest" sheetId="49" r:id="rId17"/>
-    <sheet name="DataCleanUpSheet" sheetId="28" r:id="rId18"/>
+    <sheet name="DashboardTest" sheetId="50" r:id="rId18"/>
+    <sheet name="TransportServiceStatisticsTest" sheetId="51" r:id="rId19"/>
+    <sheet name="TransportDriverStatisticsTest" sheetId="52" r:id="rId20"/>
+    <sheet name="TransportServiceRidesTest" sheetId="53" r:id="rId21"/>
+    <sheet name="DataCleanUpSheet" sheetId="28" r:id="rId22"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -42,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="145">
   <si>
     <t>City Area</t>
   </si>
@@ -1358,9 +1362,6 @@
   </si>
   <si>
     <t>SA_TS_16</t>
-  </si>
-  <si>
-    <t>TC_CA_16_test_data_cleanup</t>
   </si>
   <si>
     <t>TransportCityAdmin</t>
@@ -3351,6 +3352,236 @@
 79. Click Verified Customers,click,,"admin.menu.verified_customers"
 80. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
 81. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"</t>
+  </si>
+  <si>
+    <t>Dashboard Test</t>
+  </si>
+  <si>
+    <t>TC_CA_17_Dashboard_Test</t>
+  </si>
+  <si>
+    <t>1.Click Today Button,Click,,"web.global.dashboard.today_statistics"
+2.Click Search Button,Click,,"web.global.dashboard.search_btn"
+3.Wait For Today Statistics,wait,2000,
+4.Click Clear Button,click,,"web.global.dashboard.clear_btn"
+5.Click Yesterday Button,Click,,"web.global.dashboard.yesterday_statistics"
+6.Click Search Button,Click,,"web.global.dashboard.search_btn"
+7.Wait For Yesterday Statistics,wait,2000,
+8.Click Clear Button,click,,"web.global.dashboard.clear_btn"
+9.Click This Week Button,Click,,"web.global.dashboard.this_week_statistics"
+10.Click Search Button,Click,,"web.global.dashboard.search_btn"
+11.Wait For This Week Statistics,wait,2000,
+12.Click Clear Button,click,,"web.global.dashboard.clear_btn"
+13.Click This Month Button,Click,,"web.global.dashboard.this_month_statistics"
+14.Click Search Button,Click,,"web.global.dashboard.search_btn"
+15.Wait For This Month Statistics,wait,2000,
+16.Click Clear Button,click,,"web.global.dashboard.clear_btn"
+17.Click Last Month Button,Click,,"web.global.dashboard.last_month_statistics"
+18.Click Search Button,Click,,"web.global.dashboard.search_btn"
+19.Wait For Last Month Statistics,wait,2000,
+20.Click Clear Button,click,,"web.global.dashboard.clear_btn"
+21.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
+22.Click Search Button,Click,,"web.global.dashboard.search_btn"
+23.Wait For This Year Statistics,wait,2000,
+24.Click Clear Button,click,,"web.global.dashboard.clear_btn"
+25.Click Last Year Button,Click,,"web.global.dashboard.last_year_statistics"
+26.Click Search Button,Click,,"web.global.dashboard.search_btn"
+27.Wait For Last Year Statistics,wait,2000,
+28.Click Clear Button,click,,"web.global.dashboard.clear_btn"</t>
+  </si>
+  <si>
+    <t>This test suite validates the dynamic filtering and search functionality of the global dashboard dashboard by systematically auditing various date ranges. The test executes a continuous loop across multiple chronological milestones—including Today, Yesterday, This Week, This Month, Last Month, This Year, and Last Year. For each specific time dimension, the script triggers the statistical filter lookup, applies a 2-second synchronization delay to ensure the backend payload renders correctly on the UI viewport, and completely resets the state using the clear function before cycling into the next date range parameters.</t>
+  </si>
+  <si>
+    <t>SA_TS_18</t>
+  </si>
+  <si>
+    <t>Tranport Service Statistic Test</t>
+  </si>
+  <si>
+    <t>TC_CA_18_Tranport_Service_Statistic_Test</t>
+  </si>
+  <si>
+    <t>This test suite validates the dynamic filtering and search functionality of the transport Serivice dashboard by systematically auditing various date ranges. The test executes a continuous loop across multiple chronological milestones—including Today, Yesterday, This Week, This Month, Last Month, This Year, and Last Year. For each specific time dimension, the script triggers the statistical filter lookup, applies a 2-second synchronization delay to ensure the backend payload renders correctly on the UI viewport, and completely resets the state using the clear function before cycling into the next date range parameters.</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2. Click Transports Services Menu,click,, "admin.transport.menu.card"
+3.Filter Services List,type,Auto Ride, "admin.transport.grid.name_filter"
+4.Click Home Icon ,click,, "admin.transport.home.icon"
+5.Click Today Button,Click,,"web.global.dashboard.today_statistics"
+6.Click Search Button,Click,,"web.global.dashboard.search_btn"
+7.wait For Today Statistics,wait,2000,
+8.Click Yesterday Button,Click,,"web.global.dashboard.yesterday_statistics"
+9.Click Search Button,Click,,"web.global.dashboard.search_btn"
+10.wait For Yesterday Statistics,wait,2000,
+11.Click This Week Button,Click,,"web.global.dashboard.this_week_statistics"
+12.Click Search Button,Click,,"web.global.dashboard.search_btn"
+13.wait For This Week Statistics,wait,2000,
+14.Click This Month Button,Click,,"web.global.dashboard.this_month_statistics"
+15.Click Search Button,Click,,"web.global.dashboard.search_btn"
+16.wait For This Month Statistics,wait,2000,
+17.Click Last Month Button,Click,,"web.global.dashboard.last_month_statistics"
+18.Click Search Button,Click,,"web.global.dashboard.search_btn"
+19.wait For Last Month Statistics,wait,2000,
+20.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
+21.Click Search Button,Click,,"web.global.dashboard.search_btn"
+22.wait For This Year Statistics,wait,2000,
+23.Click Last Year Button,Click,,"web.global.dashboard.last_year_statistics"
+24.Click Search Button,Click,,"web.global.dashboard.search_btn"
+25.wait For Last Year Statistics,wait,2000,</t>
+  </si>
+  <si>
+    <t>SA_TS_19</t>
+  </si>
+  <si>
+    <t>This test suite validates the dynamic filtering and search functionality of the transport Serivice driver dashboard by systematically auditing various date ranges. The test executes a continuous loop across multiple chronological milestones—including Today, Yesterday, This Week, This Month, Last Month, This Year, and Last Year. For each specific time dimension, the script triggers the statistical filter lookup, applies a 2-second synchronization delay to ensure the backend payload renders correctly on the UI viewport, and completely resets the state using the clear function before cycling into the next date range parameters.</t>
+  </si>
+  <si>
+    <t>Tranport Driver Statistic Test</t>
+  </si>
+  <si>
+    <t>TC_CA_19_Tranport_Driver_Statistic_Test</t>
+  </si>
+  <si>
+    <t>SA_TS_20</t>
+  </si>
+  <si>
+    <t>Transport Service Ride Tests</t>
+  </si>
+  <si>
+    <t>TC_CA_20_Transport_Service_Ride_Test</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2. Click Transports Services Menu,click,, "admin.transport.menu.card"
+3.Filter Services List,type,Auto Ride, "admin.transport.grid.name_filter"
+4.Click Drivers Icon,Click,,"admin.transport.driver.icon"
+5.Wait For Load,wait,2000,
+6.Click Today Button,Click,,"web.global.dashboard.today_statistics"
+7.Click Search Button,Click,,"web.global.dashboard.search_btn"
+8.wait For Today Statistics,wait,2000,
+9.Click Yesterday Button,Click,,"web.global.dashboard.yesterday_statistics"
+10.Click Search Button,Click,,"web.global.dashboard.search_btn"
+11.wait For Yesterday Statistics,wait,2000,
+12.Click This Week Button,Click,,"web.global.dashboard.this_week_statistics"
+13.Click Search Button,Click,,"web.global.dashboard.search_btn"
+14.wait For This Week Statistics,wait,2000,
+15.Click This Month Button,Click,,"web.global.dashboard.this_month_statistics"
+16.Click Search Button,Click,,"web.global.dashboard.search_btn"
+17.wait For This Month Statistics,wait,2000,
+18.Click Last Month Button,Click,,"web.global.dashboard.last_month_statistics"
+19.Click Search Button,Click,,"web.global.dashboard.search_btn"
+20.wait For Last Month Statistics,wait,2000,
+21.Click Last Year Button,Click,,"web.global.dashboard.last_year_statistics"
+22.Click Search Button,Click,,"web.global.dashboard.search_btn"
+23.wait For Last Year Statistics,wait,2000,
+24.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
+25.Click Search Button,Click,,"web.global.dashboard.search_btn"
+26.wait For This Year Statistics,wait,2000,
+27.Click Select Driver Dropdown,Click,,"admin.drivers.approved_driver.driver_dropdown"
+28.Enter Name In Drop Down,type,regression.approved_driver.name,"admin.drivers.approved_driver.driver_dropdown_searchbox"
+29.Click Driver Name,Click,,"admin.drivers.approved_driver.driver_dropdown_first"
+30.Click Vehicle Type Dropdown,Click,,"admin.drivers.approved_driver.vehicle_dropdown"
+31.Enter Vehicle Name,type,pink Auto,"admin.drivers.approved_driver.driver_dropdown_searchbox"
+32.Click Vehicle Name,click,,"admin.drivers.approved_driver.vehicle_dropdown_first"
+33.Click Service Dropdown,click,,"admin.drivers.approved_driver.service_dropdown"
+34.Select Service,type,Auto Ride,"admin.drivers.approved_driver.driver_dropdown_searchbox"
+35.Click Service Option,click,,"admin.drivers.approved_driver.service_dropdown_first"
+36.Click Search Button,Click,,"web.global.dashboard.search_btn"
+37.wait for Approved Driver Filtering,wait,3000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2. Click Transports Services Menu,click,, "admin.transport.menu.card"
+3.Filter Services List,type,Auto Ride, "admin.transport.grid.name_filter"
+4.Click Ride Button,click,,"admin.transport.rides.icon"
+5.Click Today Button,Click,,"web.global.dashboard.today_statistics"
+6.Click Search Button,Click,,"admin.transport.search_btn"
+7.wait For Today Statistics,wait,2000,
+8.Click Yesterday Button,Click,,"web.global.dashboard.yesterday_statistics"
+9.Click Search Button,Click,,"admin.transport.search_btn"
+10.wait For Yesterday Statistics,wait,2000,
+11.Click This Week Button,Click,,"web.global.dashboard.this_week_statistics"
+12.Click Search Button,Click,,"admin.transport.search_btn"
+13.wait For This Week Statistics,wait,2000,
+14.Click This Month Button,Click,,"web.global.dashboard.this_month_statistics"
+15.Click Search Button,Click,,"admin.transport.search_btn"
+16.wait For This Month Statistics,wait,2000,
+17.Click Last Month Button,Click,,"web.global.dashboard.last_month_statistics"
+18.Click Search Button,Click,,"admin.transport.search_btn"
+19.wait For Last Month Statistics,wait,2000,
+20.Click Last Year Button,Click,,"web.global.dashboard.last_year_statistics"
+21.Click Search Button,Click,,"admin.transport.search_btn"
+22.wait For Last Year Statistics,wait,2000,
+23.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
+24.Click Search Button,Click,,"admin.transport.search_btn"
+25.wait For This Year Statistics,wait,2000,
+26.Click Select Customer Dropdown,click,,"admin.transport.customer_dropdown"
+27.Enter Customer Name In Drop Down,type,regression.customer.name,"admin.transport.customer_dropdown_searchbox"
+28.Click Customer Name,click,,"admin.transport.customer_dropdown_first"
+29.Select Driver Dropdown,click,,"admin.transport.driver_dropdown"
+30.Enter Driver Name In Drop Down,type,regression.approved_driver.name,"admin.transport.driver_dropdown_searchbox"
+31.Click Driver Name,click,,"admin.transport.driver_dropdown_first"
+32.Select Vehicle Type  Dropdown,click,,"admin.transport.vehicle_type_dropdown"
+33.Enter Vehicle Type In Drop Down,type,Pink Auto,"admin.transport.vehicle_type_dropdown_searchbox"
+34.Click Vehicle Type,click,,"admin.transport.vehicle_type_dropdown_first"
+35.Select Status Type  Dropdown,click,,"admin.transport.status_type_dropdown"
+36.Enter Status Type In Drop Down,type,Completed Rides,"admin.transport.status_type_dropdown_searchbox"
+37.Click Status Type,click,,"admin.transport.status_type_dropdown_first"
+38.Click Search Button,click,,"admin.transport.search_btn"
+39.Click Status Filter Input,click,,"admin.transport.status_filter_input"
+40.Enter Status,type,complete,"admin.transport.status_filter_input"
+41.Click Chat Box,click,,"admin.transport.chat_box.icon"
+42.Wait For Chat,wait,2000,
+43.Close Chat,click,,"admin.transport.rides.messages_close.btn"
+44.Click Ride Detail Button,click,,"admin.transport.ride_details.icon" 
+45.Wait For Ride Detail,wait,2000
+46.Show Ride Details,click,,"admin.transport.ride_details.arrival_time_box"
+47.Wait For Ride Detail,wait,2000
+48.Click Back Button,click,,"admin.transport.ride_details.back_btn"
+49.Click Select Customer Dropdown,click,,"admin.transport.customer_dropdown"
+50.Enter Customer Name In Drop Down,type,regression.customer.name,"admin.transport.customer_dropdown_searchbox"
+51.Click Customer Name,click,,"admin.transport.customer_dropdown_first"
+52.Select Driver Dropdown,click,,"admin.transport.driver_dropdown"
+53.Enter Driver Name In Drop Down,type,regression.approved_driver.name,"admin.transport.driver_dropdown_searchbox"
+54.Click Driver Name,click,,"admin.transport.driver_dropdown_first"
+55.Select Vehicle Type  Dropdown,click,,"admin.transport.vehicle_type_dropdown"
+56.Enter Vehicle Type In Drop Down,type,Pink Auto,"admin.transport.vehicle_type_dropdown_searchbox"
+57.Click Vehicle Type,click,,"admin.transport.vehicle_type_dropdown_first"
+58.Select Status Type  Dropdown,click,,"admin.transport.status_type_dropdown"
+59.Enter Status Type In Drop Down,type,Incomplete Rides,"admin.transport.status_type_dropdown_searchbox"
+60.Click Status Type,click,,"admin.transport.status_type_dropdown_first"
+61.Click Search Button,click,,"admin.transport.search_btn"
+62.Wait For Incomplete Rides,wait,2000,
+63.Click Clear Button,click,,"admin.transport.ride_details.clear_btn"
+64.Select Status Type  Dropdown,click,,"admin.transport.status_type_dropdown"
+65.Enter Status Type In Drop Down,type,Cancelled Rides,"admin.transport.status_type_dropdown_searchbox"
+66.Click Status Type,click,,"admin.transport.status_type_dropdown_first"
+67.Click Search Button,click,,"admin.transport.search_btn"
+68.Wait For Cancelled Rides,wait,2000,
+69.Click Clear Button,click,,"admin.transport.ride_details.clear_btn"
+70.Select Status Type  Dropdown,click,,"admin.transport.status_type_dropdown"
+71.Enter Status Type In Drop Down,type,Scheduled Rides,"admin.transport.status_type_dropdown_searchbox"
+72.Click Status Type,click,,"admin.transport.status_type_dropdown_first"
+73.Click Search Button,click,,"admin.transport.search_btn"
+74.Wait For Scheduled Rides,wait,2000,
+75.Click Clear Button,click,,"admin.transport.ride_details.clear_btn"
+76.Select Status Type  Dropdown,click,,"admin.transport.status_type_dropdown"
+77.Enter Status Type In Drop Down,type,Pre-Acceptance Cancel Rides,"admin.transport.status_type_dropdown_searchbox"
+78.Click Status Type,click,,"admin.transport.status_type_dropdown_first"
+79.Click Search Button,click,,"admin.transport.search_btn"
+80.Wait For Pre-Acceptance Cancel Rides,wait,2000,
+</t>
+  </si>
+  <si>
+    <t>SA_TS_21</t>
+  </si>
+  <si>
+    <t>TC_CA_21_test_data_cleanup</t>
+  </si>
+  <si>
+    <t>This end-to-end regression test suite thoroughly validates the data filtering, search capabilities, and transaction monitoring matrices within the Transport Services administration panel. The test starts by targeting a specific vehicle class ("Auto Ride") and systematically loops through chronological milestone filters—ranging from Today to Last Year—to verify date-partitioned metrics rendering. It then transitions to a complex granular query verification phase by isolating discrete parameters across multiple dependent dropdown elements, including specific customer names, registered driver profiles, vehicle types ("Pink Auto"), and ride lifecycles (Completed, Incomplete, Cancelled, Scheduled, and Pre-Acceptance Cancel Rides). Additionally, the script tests contextual UI elements by verifying the operational initialization of intra-ride chat boxes and auditing specialized tracking panels, such as arrival time breakdowns and deep-dive ride detail metrics grids, ensuring robust data reporting with zero caching conflicts across state changes.</t>
   </si>
 </sst>
 </file>
@@ -3776,7 +4007,7 @@
         <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>37</v>
@@ -3845,13 +4076,13 @@
         <v>27</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>45</v>
@@ -3917,16 +4148,16 @@
         <v>30</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -3989,13 +4220,13 @@
         <v>32</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>45</v>
@@ -4048,10 +4279,10 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
@@ -4062,22 +4293,22 @@
         <v>53</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>56</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>57</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4140,13 +4371,13 @@
         <v>35</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>46</v>
@@ -4212,13 +4443,13 @@
         <v>40</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>55</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>58</v>
@@ -4284,13 +4515,13 @@
         <v>67</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>70</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>69</v>
@@ -4353,16 +4584,16 @@
         <v>72</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>69</v>
@@ -4381,7 +4612,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2F621F-9A1F-4BCF-BC43-4FD25385804C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23692DF2-D92E-4735-942F-857C385D78E2}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4420,24 +4651,24 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>64</v>
+        <v>124</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>65</v>
+        <v>127</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4448,9 +4679,79 @@
       <c r="E3" s="8"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9FEA58B-ACBB-4068-8C66-F4A14C3E8CAE}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="69.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="360" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -4489,7 +4790,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4509,13 +4810,13 @@
         <v>52</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>41</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4530,6 +4831,224 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A04AC2C5-FB17-478C-B9F4-6CCC13A451B0}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="69.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F55FCD48-3B50-4EDD-B265-9AB60F809D78}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="69.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2F621F-9A1F-4BCF-BC43-4FD25385804C}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="69.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="8"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4588,7 +5107,7 @@
         <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>41</v>
@@ -4643,7 +5162,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4663,13 +5182,13 @@
         <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>38</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -4711,7 +5230,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4725,19 +5244,19 @@
         <v>14</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>42</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4786,7 +5305,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4800,19 +5319,19 @@
         <v>15</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4861,7 +5380,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4875,19 +5394,19 @@
         <v>17</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>44</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4936,7 +5455,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -4950,19 +5469,19 @@
         <v>59</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>62</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -5020,22 +5539,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="D2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40CD8D22-D938-471C-9746-0A3DAF50DB87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2CD1B2E-433C-4905-B32A-49654B080792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="18" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="19" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>
@@ -25,16 +25,18 @@
     <sheet name="TransportServiceStatisticsTest" sheetId="51" r:id="rId10"/>
     <sheet name="TransportDriverStatisticsTest" sheetId="52" r:id="rId11"/>
     <sheet name="TransportServiceRidesTest" sheetId="53" r:id="rId12"/>
-    <sheet name="SubscriptionPlanTest" sheetId="47" r:id="rId13"/>
-    <sheet name="PanicCallTest" sheetId="49" r:id="rId14"/>
-    <sheet name="DashboardTest" sheetId="50" r:id="rId15"/>
-    <sheet name="AddStore" sheetId="40" r:id="rId16"/>
-    <sheet name="StoreOperations" sheetId="42" r:id="rId17"/>
-    <sheet name="StoreStatusManagement" sheetId="43" r:id="rId18"/>
-    <sheet name="DeliveryServiceCompleteTest" sheetId="44" r:id="rId19"/>
-    <sheet name="AddProvider" sheetId="45" r:id="rId20"/>
-    <sheet name="ProviderServiceCompleteTest" sheetId="46" r:id="rId21"/>
-    <sheet name="DataCleanUpSheet" sheetId="28" r:id="rId22"/>
+    <sheet name="TransportServiceAerialView" sheetId="54" r:id="rId13"/>
+    <sheet name="SubscriptionPlanTest" sheetId="47" r:id="rId14"/>
+    <sheet name="PanicCallTest" sheetId="49" r:id="rId15"/>
+    <sheet name="DashboardTest" sheetId="50" r:id="rId16"/>
+    <sheet name="AddStore" sheetId="40" r:id="rId17"/>
+    <sheet name="StoreOperations" sheetId="42" r:id="rId18"/>
+    <sheet name="StoreStatusManagement" sheetId="43" r:id="rId19"/>
+    <sheet name="DeliveryServiceCompleteTest" sheetId="44" r:id="rId20"/>
+    <sheet name="AddProvider" sheetId="45" r:id="rId21"/>
+    <sheet name="ProviderServiceCompleteTest" sheetId="46" r:id="rId22"/>
+    <sheet name="DEMO" sheetId="55" r:id="rId23"/>
+    <sheet name="DataCleanUpSheet" sheetId="28" r:id="rId24"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -46,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="151">
   <si>
     <t>City Area</t>
   </si>
@@ -3163,9 +3165,6 @@
     <t>SA_TS_21</t>
   </si>
   <si>
-    <t>TC_CA_21_test_data_cleanup</t>
-  </si>
-  <si>
     <t>This end-to-end regression test suite thoroughly validates the data filtering, search capabilities, and transaction monitoring matrices within the Transport Services administration panel. The test starts by targeting a specific vehicle class ("Auto Ride") and systematically loops through chronological milestone filters—ranging from Today to Last Year—to verify date-partitioned metrics rendering. It then transitions to a complex granular query verification phase by isolating discrete parameters across multiple dependent dropdown elements, including specific customer names, registered driver profiles, vehicle types ("Pink Auto"), and ride lifecycles (Completed, Incomplete, Cancelled, Scheduled, and Pre-Acceptance Cancel Rides). Additionally, the script tests contextual UI elements by verifying the operational initialization of intra-ride chat boxes and auditing specialized tracking panels, such as arrival time breakdowns and deep-dive ride detail metrics grids, ensuring robust data reporting with zero caching conflicts across state changes.</t>
   </si>
   <si>
@@ -3554,31 +3553,285 @@
     <t>TC_CA_11_Transport_Service_Ride_Test</t>
   </si>
   <si>
-    <t>TC_CA_12_subscription_plan_test</t>
-  </si>
-  <si>
-    <t>TC_CA_13_Panic_Call_Test</t>
-  </si>
-  <si>
-    <t>TC_CA_14_Dashboard_Test</t>
-  </si>
-  <si>
-    <t>TC_CA_15_add_store</t>
-  </si>
-  <si>
-    <t>TC_CA_16_store_oprerations</t>
-  </si>
-  <si>
-    <t>TC_CA_17_store_status_management</t>
-  </si>
-  <si>
-    <t>TC_CA_18_delivery_service_complete_test</t>
-  </si>
-  <si>
-    <t>TC_CA_19_add_provider</t>
-  </si>
-  <si>
-    <t>TC_CA_20_provider_service_full_lifecycle_test</t>
+    <t xml:space="preserve">1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2. Click Transports Services Menu,click,, "admin.transport.menu.card"
+3.Filter Services List,type,Auto Ride, "admin.transport.grid.name_filter"
+4.Click Home Icon,Click,,"admin.transport.home.icon"
+5.Click AerialView Button,click,,"admin.transport.aerial_view.top_menu_btn"
+6.Click All Button,click,,"admin.transport.aerial_view.submenu_all_btn"
+7.Click Eye Button,click_if_present,,"admin.transport.aerial_view.eye_icon"
+8.Click Popup Close Button,click_if_present,,"admin.transport.aerial_view.eye_icon_close"
+9.Click AerialView Button,click,,"admin.transport.aerial_view.top_menu_btn"
+10.Click available button,click,,"admin.transport.aerial_view.submenu_available_btn"
+11.Click Eye Button,click_if_present,,"admin.transport.aerial_view.eye_icon"
+12.Click Popup Close Button,click_if_present,,"admin.transport.aerial_view.eye_icon_close"
+13.Click AerialView Button,click,,"admin.transport.aerial_view.top_menu_btn"
+14.Click Enroute to pickup,click,,"admin.transport.aerial_view.submenu_enroute_pickup_btn"
+15.Click Eye Button,click_if_present,,"admin.transport.aerial_view.eye_icon"
+16.Click Popup Close Button,click_if_present,,"admin.transport.aerial_view.eye_icon_close"
+17.Click AerialView Button,click,,"admin.transport.aerial_view.top_menu_btn"
+18.Click Reached Pickup,click,,"admin.transport.aerial_view.submenu_reached_pickup_btn"
+19.Click Eye Button,click_if_present,,"admin.transport.aerial_view.eye_icon"
+20.Click Popup Close Button,click_if_present,,"admin.transport.aerial_view.eye_icon_close"
+21.Click AerialView Button,click,,"admin.transport.aerial_view.top_menu_btn"
+22.Click Ongoing Button,click,,"admin.transport.aerial_view.submenu_ongoing_btn"
+23.Click Eye Button,click_if_present,,"admin.transport.aerial_view.eye_icon"
+24.Click Popup Close Button,click_if_present,,"admin.transport.aerial_view.eye_icon_close"
+</t>
+  </si>
+  <si>
+    <t>Transport Service Aerial View</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Data Dependency:  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">The SuperAdminLogin test suite must be always executed before this test.This ensures the browser is already logged in as a Super Admin. Without this step, the automation will encounter a "Redirect to Login" or "Access Denied" error. The framework is configured to automatically handle this login for you if it hasn't been done yet.
+RunSheet:SuperAdminLogin
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Authentication State</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: The user is already authenticated as an Admin/Super Admin with active session permissions for Provider and Document Management.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Navigation State:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The browser must be on the Dashboard page (https://dev.we1.co/#/page-module/dashboard_dynamic). The dashboard.url must be correctly mapped in the config.properties file.
+</t>
+    </r>
+  </si>
+  <si>
+    <t>This targeted regression test suite validates the operational map metrics and driver tracking grids within the Transport Services Aerial View monitoring control center. The test targets a specific service class ("Auto Ride") and systematically loops through all real-time operational filters in the geospatial dashboard—specifically auditing the telemetry statuses for All, Available, Enroute to Pickup, Reached Pickup, and Ongoing tracking segments. For each individual status layout, the script uses the fault-tolerant click_if_present keyword to launch detailed map overlay info-popups via the tracking eye icon, verifies panel readability, and dismisses the popup cleanly before moving to the next status. This process ensures that dynamic map layers, dispatcher tooltips, and real-time operational status updates function flawlessly across the administrative workspace without crashing due to unexpected timing or missing elements.</t>
+  </si>
+  <si>
+    <t>TC_CA_12_Transport_Service_Aerial_View</t>
+  </si>
+  <si>
+    <t>TC_CA_13_subscription_plan_test</t>
+  </si>
+  <si>
+    <t>TC_CA_14_Panic_Call_Test</t>
+  </si>
+  <si>
+    <t>TC_CA_15_Dashboard_Test</t>
+  </si>
+  <si>
+    <t>TC_CA_16_add_store</t>
+  </si>
+  <si>
+    <t>TC_CA_17_store_oprerations</t>
+  </si>
+  <si>
+    <t>TC_CA_18_store_status_management</t>
+  </si>
+  <si>
+    <t>TC_CA_19_delivery_service_complete_test</t>
+  </si>
+  <si>
+    <t>TC_CA_20_add_provider</t>
+  </si>
+  <si>
+    <t>TC_CA_21_provider_service_full_lifecycle_test</t>
+  </si>
+  <si>
+    <t>SA_TS_22</t>
+  </si>
+  <si>
+    <t>TC_CA_22_test_data_cleanup</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Data Dependency:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The SuperAdminLogin test suite must be always executed before this test.This ensures the browser is already logged in as a Super Admin. Without this step, the automation will encounter a "Redirect to Login" or "Access Denied" error. The framework is configured to automatically handle this login for you if it hasn't been done yet.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">RunSheet: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">SuperAdminLogin
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Authentication State</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: The user is already authenticated as an Admin/Super Admin with active session permissions for Provider and Document Management.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Navigation State:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The browser must be on the Dashboard page (https://dev.we1.co/#/page-module/dashboard_dynamic). The dashboard.url must be correctly mapped in the config.properties file.
+</t>
+    </r>
+  </si>
+  <si>
+    <t>TC_CA_XX_Demo</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2.Click Transport Service,Click,,"//h2[@id='Transport Services']"
+3.Click Search Box,click,,"//input[@class='ag-input-field-input ag-text-field-input']"
+4.Enter Services,type,Auto Ride,"//input[@class='ag-input-field-input ag-text-field-input']"
+5.Click Home Icon,Click,,"//i[@title='Home']"
+6.Click Earning Report,click,,"//button[text()=" Earnings Reports "]"
+7.Click Today Button,Click,,"//button[normalize-space()='Today']"
+8.Click Yesterday Button,Click,,"//button[normalize-space()='Yesterday']"
+9.Click This Week Button,Click,,"//button[normalize-space()='This Week']"
+10.Click This Month Button,Click,,"//button[normalize-space()='This Month']"
+11.Click Last Month Button,Click,,"//button[normalize-space()='Last Month']"
+12.Click This Year Button,Click,,"//button[normalize-space()='This Year']"
+13.Click Last Year Button,Click,,"//button[normalize-space()='Last Year']"
+14.Click This Year Button,Click,,"//button[normalize-space()='This Year']"
+15.Click Driver dropdown,click,,"//div[@id='Select Driver']//span[@role='combobox']"
+16.Click Search Name,click,,"//input[@role='searchbox']"
+17.Search Driver Name,type,sujan pariyar,"//input[@role='searchbox']" 
+18.Click Driver Name,click,,"//li[@role='option' and @aria-label='Sujan Pariyar A']"
+19.Click Customer Search Dropdown,click,,"//div[@id='Select Customer']"
+20.Click Search Box,click,,"//input[@role='searchbox']"
+21.Search Customer name,type,mohamed yasir,"//input[@role='searchbox']"
+22.Select The Customer,click,,"//li[@id='Select Customer_0']//span[@class='ng-star-inserted']"
+23.Click payment type,click,,"//div[@id='Select Payment Type']"
+24.Click Select cash Payment Type,click,,"//li[@id='Select Payment Type_0']"
+25.Click payment type,click,,"//div[@id='Select Payment Type']"
+26.Click Razor Payment,click,,"//li[@id='Select Payment Type_1']"
+27.Click payment type,click,,"//div[@id='Select Payment Type']"
+28.Click wallet option,click,,"//li[@id='Select Payment Type_2']"
+29.Click payment type,click,,"//div[@id='Select Payment Type']"
+30.Click Select cash Payment Type,click,,"//li[@id='Select Payment Type_0']"
+31.Click Driver Payment Status,click,,"//div[@id='Select Driver Payment Status']"
+32.Click Settled Button,click,,"//li[@role='option' and @aria-label='Settled']"
+33.Click Driver Payment Status,click,,"//div[@id='Select Driver Payment Status']"
+34.Click Unsettled Button,click,,"//li[@role='option' and @aria-label='Unsettled']"
+35.Click Search Button,click,,"//button[normalize-space()='Search']
+36.Click Clear Button,click,,"//button[normalize-space()='Clear']"
+37.Click payment type,click,,"//div[@id='Select Payment Type']"
+38.Click Select cash Payment Type,click,,"//li[@id='Select Payment Type_0']"
+39.Click Driver Payment Status,click,,"//div[@id='Select Driver Payment Status']"
+40.Click Unsettled Button,click,,"//li[@role='option' and @aria-label='Unsettled']"
+41.Click Search Button,click,,"//button[normalize-space()='Search']
+42.Click Check Box,click,,"//input[@id='ag-13832-input']"
+43.Click Payment StatusFilter,click,,"//input[@aria-label='Payment Status Filter Input']"
+44.Scroll Grid,tab,24,"//input[@aria-label='Payment Status Filter Input']"
+45.Click Eye Button,Click,,"//i[@title='View']"
+46.Click Mark As Settle Button,click,,"//button[normalize-space()='Mark As Settle']"</t>
   </si>
 </sst>
 </file>
@@ -3992,7 +4245,7 @@
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>62</v>
@@ -4067,13 +4320,13 @@
     </row>
     <row r="2" spans="1:8" ht="360" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>108</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>109</v>
@@ -4145,7 +4398,7 @@
         <v>113</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>112</v>
@@ -4217,10 +4470,10 @@
         <v>115</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>117</v>
@@ -4242,6 +4495,78 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{705BF950-38CF-4525-A333-E60DE1739EA0}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="69.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39F69F54-6E80-4C66-8F82-CEFA135D089A}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4283,19 +4608,19 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>61</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>60</v>
@@ -4313,7 +4638,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBB09688-59B4-47C6-9CAD-FED2B503D101}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4355,13 +4680,13 @@
     </row>
     <row r="2" spans="1:8" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>100</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>99</v>
@@ -4385,7 +4710,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23692DF2-D92E-4735-942F-857C385D78E2}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4427,13 +4752,13 @@
     </row>
     <row r="2" spans="1:8" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>106</v>
@@ -4457,7 +4782,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9950CA5-B845-4E23-9843-8D459D399E99}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4499,13 +4824,13 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>21</v>
@@ -4529,7 +4854,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DE0E168-E98A-49FE-8885-7B5F3F3678F3}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4571,13 +4896,13 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>23</v>
@@ -4601,7 +4926,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9584B63-AFDB-41EC-A160-356B47922D15}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4643,13 +4968,13 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>25</v>
@@ -4659,85 +4984,6 @@
       </c>
       <c r="F2" s="2" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8A1C6E6-1358-42F0-B7B3-06420689DEE4}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="44.33203125" customWidth="1"/>
-    <col min="8" max="8" width="27.109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4795,7 +5041,7 @@
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>38</v>
@@ -4832,6 +5078,85 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8A1C6E6-1358-42F0-B7B3-06420689DEE4}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="69.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="44.33203125" customWidth="1"/>
+    <col min="8" max="8" width="27.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF16C04E-51BB-4902-91C6-410B8EB3791F}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4873,13 +5198,13 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>27</v>
@@ -4903,7 +5228,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E742ED82-3510-47F4-AA85-6344770C749C}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4945,13 +5270,13 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>46</v>
@@ -4975,7 +5300,79 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4B640C4-00BD-478A-A57E-A90215D007C2}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="69.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2F621F-9A1F-4BCF-BC43-4FD25385804C}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5017,19 +5414,19 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>56</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>57</v>
@@ -5092,7 +5489,7 @@
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -5167,7 +5564,7 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>9</v>
@@ -5235,7 +5632,7 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>10</v>
@@ -5310,7 +5707,7 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>11</v>
@@ -5385,7 +5782,7 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>12</v>
@@ -5460,7 +5857,7 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>50</v>
@@ -5472,7 +5869,7 @@
         <v>53</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>52</v>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{478306CE-18DC-4A19-A861-631FCDFB7C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E09C16-5673-4917-BAF0-BB9DBF048673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="11" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="21" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>
@@ -26,17 +26,18 @@
     <sheet name="TransportDriverStatisticsTest" sheetId="52" r:id="rId11"/>
     <sheet name="TransportServiceRidesTest" sheetId="53" r:id="rId12"/>
     <sheet name="TransportServiceAerialView" sheetId="54" r:id="rId13"/>
-    <sheet name="SubscriptionPlanTest" sheetId="47" r:id="rId14"/>
-    <sheet name="PanicCallTest" sheetId="49" r:id="rId15"/>
-    <sheet name="DashboardTest" sheetId="50" r:id="rId16"/>
-    <sheet name="AddStore" sheetId="40" r:id="rId17"/>
-    <sheet name="StoreOperations" sheetId="42" r:id="rId18"/>
-    <sheet name="StoreStatusManagement" sheetId="43" r:id="rId19"/>
-    <sheet name="DeliveryServiceCompleteTest" sheetId="44" r:id="rId20"/>
-    <sheet name="AddProvider" sheetId="45" r:id="rId21"/>
-    <sheet name="ProviderServiceCompleteTest" sheetId="46" r:id="rId22"/>
-    <sheet name="DEMO" sheetId="55" r:id="rId23"/>
-    <sheet name="DataCleanUpSheet" sheetId="28" r:id="rId24"/>
+    <sheet name="TransportServiceEarningReports" sheetId="55" r:id="rId14"/>
+    <sheet name="TransportProviderLists" sheetId="56" r:id="rId15"/>
+    <sheet name="SubscriptionPlanTest" sheetId="47" r:id="rId16"/>
+    <sheet name="PanicCallTest" sheetId="49" r:id="rId17"/>
+    <sheet name="DashboardTest" sheetId="50" r:id="rId18"/>
+    <sheet name="AddStore" sheetId="40" r:id="rId19"/>
+    <sheet name="StoreOperations" sheetId="42" r:id="rId20"/>
+    <sheet name="StoreStatusManagement" sheetId="43" r:id="rId21"/>
+    <sheet name="DeliveryServiceCompleteTest" sheetId="44" r:id="rId22"/>
+    <sheet name="AddProvider" sheetId="45" r:id="rId23"/>
+    <sheet name="ProviderServiceCompleteTest" sheetId="46" r:id="rId24"/>
+    <sheet name="DataCleanUpSheet" sheetId="28" r:id="rId25"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="159">
   <si>
     <t>City Area</t>
   </si>
@@ -3659,37 +3660,7 @@
     <t>TC_CA_12_Transport_Service_Aerial_View</t>
   </si>
   <si>
-    <t>TC_CA_13_subscription_plan_test</t>
-  </si>
-  <si>
-    <t>TC_CA_14_Panic_Call_Test</t>
-  </si>
-  <si>
-    <t>TC_CA_15_Dashboard_Test</t>
-  </si>
-  <si>
-    <t>TC_CA_16_add_store</t>
-  </si>
-  <si>
-    <t>TC_CA_17_store_oprerations</t>
-  </si>
-  <si>
-    <t>TC_CA_18_store_status_management</t>
-  </si>
-  <si>
-    <t>TC_CA_19_delivery_service_complete_test</t>
-  </si>
-  <si>
-    <t>TC_CA_20_add_provider</t>
-  </si>
-  <si>
-    <t>TC_CA_21_provider_service_full_lifecycle_test</t>
-  </si>
-  <si>
     <t>SA_TS_22</t>
-  </si>
-  <si>
-    <t>TC_CA_22_test_data_cleanup</t>
   </si>
   <si>
     <r>
@@ -3783,55 +3754,167 @@
     </r>
   </si>
   <si>
-    <t>TC_CA_XX_Demo</t>
+    <t>Transport Service Earning Reports Complete Test</t>
+  </si>
+  <si>
+    <t>TC_CA_13_Transport_Service_Earning_Reports</t>
+  </si>
+  <si>
+    <t>SA_TS_23</t>
   </si>
   <si>
     <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-2.Click Transport Service,Click,,"//h2[@id='Transport Services']"
-3.Click Search Box,click,,"//input[@class='ag-input-field-input ag-text-field-input']"
-4.Enter Services,type,Auto Ride,"//input[@class='ag-input-field-input ag-text-field-input']"
-5.Click Home Icon,Click,,"//i[@title='Home']"
-6.Click Earning Report,click,,"//button[text()=" Earnings Reports "]"
-7.Click Today Button,Click,,"//button[normalize-space()='Today']"
-8.Click Yesterday Button,Click,,"//button[normalize-space()='Yesterday']"
-9.Click This Week Button,Click,,"//button[normalize-space()='This Week']"
-10.Click This Month Button,Click,,"//button[normalize-space()='This Month']"
-11.Click Last Month Button,Click,,"//button[normalize-space()='Last Month']"
-12.Click This Year Button,Click,,"//button[normalize-space()='This Year']"
-13.Click Last Year Button,Click,,"//button[normalize-space()='Last Year']"
-14.Click This Year Button,Click,,"//button[normalize-space()='This Year']"
-15.Click Driver dropdown,click,,"//div[@id='Select Driver']//span[@role='combobox']"
-16.Click Search Name,click,,"//input[@role='searchbox']"
-17.Search Driver Name,type,sujan pariyar,"//input[@role='searchbox']" 
-18.Click Driver Name,click,,"//li[@role='option' and @aria-label='Sujan Pariyar A']"
-19.Click Customer Search Dropdown,click,,"//div[@id='Select Customer']"
-20.Click Search Box,click,,"//input[@role='searchbox']"
-21.Search Customer name,type,mohamed yasir,"//input[@role='searchbox']"
-22.Select The Customer,click,,"//li[@id='Select Customer_0']//span[@class='ng-star-inserted']"
-23.Click payment type,click,,"//div[@id='Select Payment Type']"
-24.Click Select cash Payment Type,click,,"//li[@id='Select Payment Type_0']"
-25.Click payment type,click,,"//div[@id='Select Payment Type']"
-26.Click Razor Payment,click,,"//li[@id='Select Payment Type_1']"
-27.Click payment type,click,,"//div[@id='Select Payment Type']"
-28.Click wallet option,click,,"//li[@id='Select Payment Type_2']"
-29.Click payment type,click,,"//div[@id='Select Payment Type']"
-30.Click Select cash Payment Type,click,,"//li[@id='Select Payment Type_0']"
-31.Click Driver Payment Status,click,,"//div[@id='Select Driver Payment Status']"
-32.Click Settled Button,click,,"//li[@role='option' and @aria-label='Settled']"
-33.Click Driver Payment Status,click,,"//div[@id='Select Driver Payment Status']"
-34.Click Unsettled Button,click,,"//li[@role='option' and @aria-label='Unsettled']"
-35.Click Search Button,click,,"//button[normalize-space()='Search']
-36.Click Clear Button,click,,"//button[normalize-space()='Clear']"
-37.Click payment type,click,,"//div[@id='Select Payment Type']"
-38.Click Select cash Payment Type,click,,"//li[@id='Select Payment Type_0']"
-39.Click Driver Payment Status,click,,"//div[@id='Select Driver Payment Status']"
-40.Click Unsettled Button,click,,"//li[@role='option' and @aria-label='Unsettled']"
-41.Click Search Button,click,,"//button[normalize-space()='Search']
-42.Click Check Box,click,,"//input[@id='ag-13832-input']"
-43.Click Payment StatusFilter,click,,"//input[@aria-label='Payment Status Filter Input']"
-44.Scroll Grid,tab,24,"//input[@aria-label='Payment Status Filter Input']"
-45.Click Eye Button,Click,,"//i[@title='View']"
-46.Click Mark As Settle Button,click,,"//button[normalize-space()='Mark As Settle']"</t>
+2.Click Transport Service,Click,,"admin.transport.menu.card"
+3.Enter Services,type,Auto Ride,"admin.transport.grid.name_filter"
+4.Click Home Icon,Click,,"admin.transport.home.icon"
+6.Click Earning Report,click,,"admin.transport.earning_reports.top_menu_btn"
+7.Click Today Button,Click,,"web.global.dashboard.today_statistics"
+8.Wait For Today Statistics,wait,2000,
+9.Click Yesterday Button,Click,,"web.global.dashboard.yesterday_statistics"
+10.Wait For Yesterday Statistics,wait,2000,
+11.Click This Week Button,Click,,"web.global.dashboard.this_week_statistics"
+12.Wait For This Week Statistics,wait,2000,
+13.Click This Month Button,Click,,"web.global.dashboard.this_month_statistics"
+14.Wait For This Month Statistics,wait,2000,
+15.Click Last Month Button,Click,,"web.global.dashboard.last_month_statistics"
+16.Wait For Last Month Statistics,wait,2000,
+17.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
+18.Wait For This Year Statistics,wait,2000,
+19.Click Last Year Button,Click,,"web.global.dashboard.last_year_statistics"
+20.Wait For Last Year Statistics,wait,2000,
+21.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
+22.Wait For This Year Statistics,wait,2000,
+23.Select Driver Dropdown,click,,"admin.transport.earning_reports.driver_dropdown"
+24.Enter Driver Name In Drop Down,type,regression.approved_driver.name,"admin.transport.driver_dropdown_searchbox"
+25.Click Driver Name,click,,"admin.transport.driver_earning_reports_dropdown_first"
+26.Click Select Customer Dropdown,click,,"admin.transport.earning_reports.customer_dropdown"
+27.Enter Customer Name In Drop Down,type,regression.customer.name,"admin.transport.customer_dropdown_searchbox"
+28.Click Customer Name,click,,"admin.transport.customer_earning_reports_dropdown_first"
+29.Click payment type,click,,"admin.transport.earning_reports.payment_type_dropdown"
+30.Click Select cash Payment Type,click,,"admin.transport.earning_reports.payment_type_cash"
+31.Wait For Cash Payment,wait,2000,
+32.Click payment type,click,,"admin.transport.earning_reports.payment_type_dropdown"
+33.Click Razor Payment,click,,"admin.transport.earning_reports.payment_type_razorpay"
+34.Wait For Razor Payment,wait,2000,
+35.Click payment type,click,,"admin.transport.earning_reports.payment_type_dropdown"
+36.Click wallet option,click,,"admin.transport.earning_reports.payment_type_wallet"
+37.Wait For Wallet Payment,wait,2000,
+38.Click payment type,click,,"admin.transport.earning_reports.payment_type_dropdown"
+39.Click Select cash Payment Type,click,,"admin.transport.earning_reports.payment_type_cash"
+40.Click Driver Payment Status,click,,"admin.transport.earning_reports.payment_status_dropdown"
+41.Click Settled Option,click,,"admin.transport.earning_reports.payment_status_settled"
+42.Wait For Settled Payment,wait,2000,
+43.Click Driver Payment Status,click,,"admin.transport.earning_reports.payment_status_dropdown"
+44.Click Unsettled Option,click,,"admin.transport.earning_reports.payment_status_unsettled"
+45.Click Search Button,click,,"admin.transport.earning_reports.search_btn"
+46.Click Clear Button,click,,"admin.transport.earning_reports.clear_btn"
+47.Click payment type,click,,"admin.transport.earning_reports.payment_type_dropdown"
+48.Click Select cash Payment Type,click,,"admin.transport.earning_reports.payment_type_cash"
+49.Click Driver Payment Status,click,,"admin.transport.earning_reports.payment_status_dropdown"
+50.Click Unsettled Option,click,,"admin.transport.earning_reports.payment_status_unsettled"
+51.Click Search Button,click,,"admin.transport.earning_reports.search_btn"
+52.Wait For Unsettled Transaction,wait,2000,
+53.Click Checkbox,click,"admin.transport.earning_reports.checkbox"
+54.Wait For  Check box Selection,wait,1000,
+55.Click Settle Transaction Button,click,"admin.transport.earning_reports.mark_as_settle_btn"
+55.Wait For  Settlement,wait,1000,
+56.Click Payment StatusFilter,click,,"admin.transport.earning_reports.payment_status_filter"
+57.Scroll Grid,tab,24,"admin.transport.earning_reports.payment_status_filter"
+58.Click Eye Button,Click,,"admin.transport.earning_reports.eye_btn"
+59.Wait For View,wait,200,
+60.Close Earning Report View,click,,"admin.transport.earning_reports.eye_btn_close"
+61.Wait For Close,wait,2000,</t>
+  </si>
+  <si>
+    <t>This comprehensive regression test suite validates the billing algorithms, transactional search grids, and balance clearing pipelines within the Transport Services Earning Reports dashboard. The script targets a specific logistical sector ("Auto Ride") and continuously cycles through multi-tiered filter matrices—ranging from chronological time boundaries (Today, Yesterday, This Week, This Month, Last Month, and This Year) to dedicated account entities like designated driver profiles and customer records. It thoroughly audits payment channel routing by validating interface adjustments between Cash, Razorpay, and Digital Wallet modes, and accurately tests automated ledger balances by isolating Settled vs. Unsettled states. Crucially, the execution verifies critical backend database updates by selecting outstanding line entries, launching a transactional Settle Transaction command to alter balance properties on the fly, and performing grid scans and deep-dive element tracking views (via modal eye overlays) to ensure immediate data synchronization with zero stale state failures.</t>
+  </si>
+  <si>
+    <t>Transport Provider List Tests</t>
+  </si>
+  <si>
+    <t>TC_CA_14_Transport_Provider_List_Test</t>
+  </si>
+  <si>
+    <t>TC_CA_15_subscription_plan_test</t>
+  </si>
+  <si>
+    <t>TC_CA_16_Panic_Call_Test</t>
+  </si>
+  <si>
+    <t>TC_CA_17_Dashboard_Test</t>
+  </si>
+  <si>
+    <t>TC_CA_18_add_store</t>
+  </si>
+  <si>
+    <t>TC_CA_19_store_oprerations</t>
+  </si>
+  <si>
+    <t>TC_CA_20_store_status_management</t>
+  </si>
+  <si>
+    <t>TC_CA_21_delivery_service_complete_test</t>
+  </si>
+  <si>
+    <t>TC_CA_22_add_provider</t>
+  </si>
+  <si>
+    <t>TC_CA_23_provider_service_full_lifecycle_test</t>
+  </si>
+  <si>
+    <t>SA_TS_24</t>
+  </si>
+  <si>
+    <t>TC_CA_24_test_data_cleanup</t>
+  </si>
+  <si>
+    <t>This end-to-end regression test suite thoroughly validates the data segmentation, grid pagination, and report generation matrices within the Transport Providers List administrative module. The script begins by executing a complete chronological analytics loop across time boundaries—including Today, Yesterday, This Week, This Month, Last Month, and This Year—to confirm the accuracy of date-partitioned metrics rendering. It then transitions to structural grid filtering by systematically isolating discrete vehicle classes—specifically Taxi Ride, Bike Ride, and Auto Ride profiles—and verifying layout updates post-clearance. Finally, the test exercises grid controls by navigating structural data pagination anchors (Next, Previous, Last, and First pages) and executes a comprehensive verification of the reporting subsystem by triggering automated file extractions for both PDF and Excel formats, ensuring stable export channels with zero cross-query caching conflicts.</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard,Click,,"web.global.menu.dashboard"
+2.Click Providers Button,click,,"admin.provider.side_bar.menu_card"
+3.Click Transport Providers List,click,,"admin.provider.transport_provider_list.side_menu"
+4.Click Today Button,Click,,"web.global.dashboard.today_statistics"
+5.Wait For Today Statistics,wait,2000,
+6.Click Yesterday Button,Click,,"web.global.dashboard.yesterday_statistics"
+7.Wait For Yesterday Statistics,wait,2000,
+8.Click This Week Button,Click,,"web.global.dashboard.this_week_statistics"
+9.Wait For This Week Statistics,wait,2000,
+10.Click This Month Button,Click,,"web.global.dashboard.this_month_statistics"
+11.Wait For This Month Statistics,wait,2000,
+12.Click Last Month Button,Click,,"web.global.dashboard.last_month_statistics"
+13.Wait For Last Month Statistics,wait,2000,
+14.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
+15.Wait For This Year Statistics,wait,2000,
+16.Click Last Year Button,Click,,"web.global.dashboard.last_year_statistics"
+17.Wait For Last Year Statistics,wait,2000,
+18.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
+19.Wait For This Year Statistics,wait,2000,
+20.Click Service Type,click,,"admin.provider.service_type.drop_down"
+21.Click Taxi Ride,click,,"admin.provider.service_type.drop_down.option_taxi_ride"
+22.Click Search Button,click,,"admin.provider.transport_provider_list.search_btn"
+23.Wait for Taxi Provider List,wait,2000,
+24.Click Clear Button,click,,"admin.provider.transport_provider_list.clear_btn"
+25.Click Service Type,click,,"admin.provider.service_type.drop_down"
+26.Click Bike RIde,click,,"admin.provider.service_type.drop_down.option_bike_ride"
+27.Click Search Button,click,,"admin.provider.transport_provider_list.search_btn"
+28.Wait for Bike Provider List,wait,2000,
+29.Click Clear Button,click,,"admin.provider.transport_provider_list.clear_btn"
+30.Click Service Type,click,,"admin.provider.service_type.drop_down"
+31.Click Auto Ride,click,,"admin.provider.service_type.drop_down.option_auto_ride"
+32.Click Search Button,click,"admin.provider.transport_provider_list.search_btn"
+33.Wait for Auto Provider List,wait,2000,
+34.Click Clear Button,click,,"admin.provider.transport_provider_list.clear_btn"
+35.Click Next Page Button,click,,"admin.provider.transport_provider_list.grid_next_page"
+36.Click Previous Page Button,click,,"admin.provider.transport_provider_list.grid_previous_page"
+37.Click Last Pageination Button,click,,"admin.provider.transport_provider_list.grid_last_page"
+38.Click First Pegination Button,click,,"admin.provider.transport_provider_list.grid_first_page"
+39.Wait For Pagination,wait,2000,
+40.Click Download Button,hover,,"admin.provider.transport_provider_list.download_btn"
+41.Click PDf Button,click,,"admin.provider.transport_provider_list.pdf_download_btn"
+42.Wait For Pdf Download,wait,5000,
+43.Click Excel Button,click,,"admin.provider.transport_provider_list.excel_download_btn"
+44.Wait For Excel Download,wait,2000,</t>
   </si>
 </sst>
 </file>
@@ -4567,6 +4650,150 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4B640C4-00BD-478A-A57E-A90215D007C2}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="69.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05D8E6DC-EF3B-4D1D-A5D5-95A75B0B28AA}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="69.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39F69F54-6E80-4C66-8F82-CEFA135D089A}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4608,13 +4835,13 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>61</v>
@@ -4638,7 +4865,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBB09688-59B4-47C6-9CAD-FED2B503D101}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4680,13 +4907,13 @@
     </row>
     <row r="2" spans="1:8" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>100</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>99</v>
@@ -4710,7 +4937,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23692DF2-D92E-4735-942F-857C385D78E2}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4752,13 +4979,13 @@
     </row>
     <row r="2" spans="1:8" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>106</v>
@@ -4782,7 +5009,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9950CA5-B845-4E23-9843-8D459D399E99}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4824,163 +5051,19 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DE0E168-E98A-49FE-8885-7B5F3F3678F3}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9584B63-AFDB-41EC-A160-356B47922D15}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>36</v>
@@ -5078,6 +5161,150 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DE0E168-E98A-49FE-8885-7B5F3F3678F3}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="69.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9584B63-AFDB-41EC-A160-356B47922D15}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" customWidth="1"/>
+    <col min="5" max="5" width="69.33203125" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8A1C6E6-1358-42F0-B7B3-06420689DEE4}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5120,13 +5347,13 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>47</v>
@@ -5156,7 +5383,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF16C04E-51BB-4902-91C6-410B8EB3791F}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5198,13 +5425,13 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>27</v>
@@ -5228,7 +5455,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E742ED82-3510-47F4-AA85-6344770C749C}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5270,13 +5497,13 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>46</v>
@@ -5300,79 +5527,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4B640C4-00BD-478A-A57E-A90215D007C2}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2F621F-9A1F-4BCF-BC43-4FD25385804C}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5414,13 +5569,13 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>56</v>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{187C733B-455F-4454-993D-10A1E6145C33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63FAD1B5-8A6A-4744-B3C4-77AA53A1DBF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>
@@ -1947,89 +1947,6 @@
     <t>SA_TS_17</t>
   </si>
   <si>
-    <t>1. Click Dashboard Icon,click,,"web.global.menu.dashboard"
-2. Click Customer Icon,click,,"admin.menu.customer_icon"
-3. Click Add Customers,click,,"admin.menu.add_customers"
-4. Wait For Customer Heading,wait_until_visible,,"admin.customer.add_heading"
-5. Enter Customer Name,type,customer{randomAlpha} &gt;&gt; customerName,"admin.customer.input_name"
-6. Enter Email,type,customer_{timestamp}@gmail.com&gt;&gt;customerEmail,"admin.customer.input_email"
-7. Enter Contact Number,type,{randomPhone},"admin.customer.input_phone"
-8.Enter Emergency Number,type,{randomPhone},"admin.customer.input_Emergency_phone"
-9. Open Gender,click,,"admin.customer.dropdown_gender"
-10. Select Male,click,,"admin.customer.select_gender_male"
-11. Upload Profile Image,uploadfile,"src/main/resources/test-data/customer.jpg","admin.customer.upload_profile_img"
-12. Click Submit,click,,"web.global.action.submit"
-13. Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
-14. Click Dashboard,click,,"web.global.menu.dashboard"
-15. Click Customer Icon,click,,"admin.menu.customer_icon"
-16. Click Verified Customers,click,,"admin.menu.verified_customers"
-17. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
-18. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
-19. Scroll Grid,tab,7,"admin.customer.filter_name"
-20. Click Edit Icon,click,,"admin.customer.grid.btn_edit"
-21. Click Close,click,,"web.global.action.close"
-22. Click Wallet Icon,click,,"admin.customer.grid.btn_wallet"
-23. Click Add Money,click,,"admin.customer.wallet.btn_add_money"
-24. Enter Wallet Amount,type,1000,"admin.customer.wallet.input_amount"
-25. Open Choose Option Dropdown,click,,"admin.customer.wallet.dropdown_option"
-26. Select Add Money,click,,"admin.customer.wallet.select_add_money"
-27. Click Submit,click,,"web.global.action.submit"
-28. Wait For Saved Successfully,wait_until_visible,,"web.global.toast.success"
-29. Click Add Money,click,,"admin.customer.wallet.btn_add_money"
-30. Enter Wallet Amount,type,200,"admin.customer.wallet.input_amount"
-31. Open Choose Option Dropdown,click,,"admin.customer.wallet.dropdown_option"
-32. Select Deduct Money,click,,"admin.customer.wallet.select_deduct_money"
-33. Click Submit,click,,"web.global.action.submit"
-34. Wait For Saved Successfully,wait_until_visible,,"web.global.toast.success"
-35. Click dashboard Icon,click,,"web.global.menu.dashboard"
-36. Click Customer Icon,click,,"admin.menu.customer_icon"
-37. Click Verified Customers,click,,"admin.menu.verified_customers"
-38. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
-39. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
-40. Scroll Grid,tab,7,"admin.customer.filter_name"
-41. Click Loyalty Points Icon,click,,"admin.customer.grid.btn_loyalty_points"
-42. Click Manage Loyalty Points,click,,"admin.customer.loyalty.btn_manage"
-43. Open Service Dropdown,click,,"admin.customer.loyalty.dropdown_service"
-44. Select Bike Ride,click,,"admin.customer.loyalty.select_bike_ride"
-45. Open Choose Option Dropdown,click,,"admin.customer.loyalty.dropdown_option"
-46. Select Add Points,click,,"admin.customer.loyalty.select_add_points"
-47. Enter Points,type,30,"admin.customer.loyalty.input_points"
-48. Click Submit,click,,"web.global.action.submit"
-49. Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
-50. Click Manage Loyalty Points,click,,"admin.customer.loyalty.btn_manage"
-51. Open Service Dropdown,click,,"admin.customer.loyalty.dropdown_service"
-52. Select Bike Ride,click,,"admin.customer.loyalty.select_bike_ride"
-53. Open Choose Option Dropdown,click,,"admin.customer.loyalty.dropdown_option"
-54. Select Deduct Points,click,,"admin.customer.loyalty.select_deduct_points"
-55. Enter Points,type,10,"admin.customer.loyalty.input_points"
-56. Click Submit,click,,"web.global.action.submit"
-57. Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
-58. Click Dashboard Icon,click,,"web.global.menu.dashboard"
-59. Click Customer Icon,click,,"admin.menu.customer_icon"
-60. Click Verified Customers,click,,"admin.menu.verified_customers"
-61. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
-62. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
-63. Scroll Grid,tab,7,"admin.customer.filter_name"
-64. Click Disable Icon,click,,"admin.customer.grid.btn_block"
-65. Click Disable User Yes,click,,"web.global.dialog.btn_confirm_yes"
-66. Disable Reason,type,Client Complaints,"web.global.dialog.textarea_reason"
-67. Click Reject Yes,click,,"web.global.dialog.btn_confirm_yes"
-68. Verify Added Successfully,verify,,"web.global.toast.info"
-69. Click Dashboard Icon,click,,"web.global.menu.dashboard"
-70. Click Customer Icon,click,,"admin.menu.customer_icon"
-71. Click Blocked Customers,click,,"admin.menu.blocked_customers"
-72. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
-73. Scroll Grid,tab,10,"admin.customer.filter_name"
-74.Wait For Enable Icon,wait_until_visible,,"admin.customer.grid.btn_status_enable"
-75. Click Enable Icon,click,,"admin.customer.grid.btn_status_enable"
-76. Click Enable Yes,click,,"web.global.dialog.btn_confirm_yes"
-77. Click Dashboard Icon,click,,"web.global.menu.dashboard"
-78. Click Customer Icon,click,,"admin.menu.customer_icon"
-79. Click Verified Customers,click,,"admin.menu.verified_customers"
-80. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
-81. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"</t>
-  </si>
-  <si>
     <t>Dashboard Test</t>
   </si>
   <si>
@@ -2882,70 +2799,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">1.Click Dashboard,click,,"web.global.menu.dashboard"
-2.Click Report Issue,click,,"admin.report_issue.side_bar.menu"
-3.Click Customer Report Issue,click,,"admin.report_issue.side_bar_sub_menu.driver_report_issues"
-4.Click Today Button,click,,"web.global.dashboard.today_statistics"
-5.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
-6.Wait For Today Statistics,wait,2000,
-7.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
-8.Click Yesterday Button,Click,,"web.global.dashboard.yesterday_statistics"
-9.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
-10.Wait For Yesterday Statistics,wait,2000,
-11.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
-12.Click This Week Button,Click,,"web.global.dashboard.this_week_statistics"
-13.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
-14.Wait For This Week Statistics,wait,2000,
-15.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
-16.Click This Month Button,Click,,"web.global.dashboard.this_month_statistics"
-17.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
-18.Wait For This Month Statistics,wait,2000,
-19.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
-20.Click Last Month Button,Click,,"web.global.dashboard.last_month_statistics"
-21.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
-22.Wait For Last Month Statistics,wait,2000,
-23.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
-24.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
-25.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
-26.Wait For This Year Statistics,wait,2000,
-27.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
-28.Click Last Year Button,Click,,"web.global.dashboard.last_year_statistics"
-29.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
-30.Wait For Last Year Statistics,wait,2000,
-31.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
-32.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
-33.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
-34.Wait For This Year Statistics,wait,2000,
-35.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
-37.Click Created By Dropdown,click,,"admin.report_issue.driver_report_issues.created_by_dropdown"
-38.Click Search Box ,click,,"admin.report_issue.driver_report_issues.created_by_dropdown_search_box"
-39.Click The First Name,click,,"admin.report_issue.driver_report_issues.created_by_dropdown_first_name"
-40.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
-41.Wait For Name Load,wait,2000
-42.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
-43.Click Status Dropdown,click_if_present,,"admin.report_issue.driver_report_issues.status_dropdown"
-43.Click Unresolved Option,click_if_present,,"admin.report_issue.driver_report_issues.status_dropdown_unresolved_option"
-44.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
-45.Wait For Unresolved Load,wait,2000
-46.Scroll Grid,tab,8,"admin.report_issue.driver_report_issues.ticket_id_filter_input"
-47.Click Eye Icon,click,,"admin.report_issue.driver_report_issues.eye_icon"
-48.Click Close Eye View,click,,"admin.report_issue.driver_report_issues.close_eye_icon"
-49.Click Chat Button,click,,"admin.report_issue.driver_report_issues.chat_icon"
-50.Wait For Chat load,wait,2000
-51.Click Chat close,click_if_present,,"admin.report_issue.driver_report_issues.close_chat_icon"
-52.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
-53.Wait For Clear,wait,1000,
-54.Click Status Dropdown,click_if_present,,"admin.report_issue.driver_report_issues.status_dropdown"
-55.Click resolved Option,click_if_present,,"admin.report_issue.driver_report_issues.status_dropdown_resolved_option"
-56.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
-57.Wait For Resolved Load,wait,2000
-58.Click Resolve Button,click,,"admin.report_issue.driver_report_issues.resolve_thumbs_icon"
-59.Click Confirm Resolve,click,,"admin.report_issue.driver_report_issues.resolve_confirm_yes"
-60.Wait For Resolve,wait,1000,
-61.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
-</t>
-  </si>
-  <si>
     <t>Geo Fencing Test</t>
   </si>
   <si>
@@ -2989,30 +2842,6 @@
   </si>
   <si>
     <t>TC_CA_29_test_data_cleanup</t>
-  </si>
-  <si>
-    <t>1.Click Dashboard,Click,,"web.global.menu.dashboard"
-2.Click Setting Button,click,,"admin.setting.sidebar.menu"
-3.Click Geo Fencing,click,,"admin.setting.geo_fencing.sidebar_menu"
-4.Add Restrict Area,click,,"admin.setting.geo_fencing.add_restricted_area_btn"
-5.Enter Restricted Area Name,type,officers training academy chennai,"admin.setting.geo_fencing.area_name_input_field"
-6.Click The Status Button On,click,,"admin.setting.geo_fencing.status_toggle_button"
-7.Map Polygon,draw polygon,"-120;-120 : 120;-120 : 120;120 : -120;120 : -120;-120","//div[@class='ol-layer']//canvas"
-8.Click Submit Button,click,,"admin.setting.geo_fencing.form_submit_button"
-9.Wait For Submit,wait,2000,
-10.Enter Search Area,type,officers training academy chennai,"admin.setting.geo_fencing.area_search_filter"
-11.Wait For Load,wait,2000
-12.Click Edit Button,click,,"admin.setting.geo_fencing.edit_button"
-13.Enter Restricted Area Name,type,Airport Chennai,"admin.setting.geo_fencing.area_name_input_field"
-14.Click The Status Button On,click,,"admin.setting.geo_fencing.status_toggle_button"
-15.Map Polygon,draw polygon,"-120;-120 : 120;-120 : 120;120 : -120;120 : -120;-120","//div[@class='ol-layer']//canvas"
-16.Click Submit Button,click,,"admin.setting.geo_fencing.form_submit_button"
-17.Wait For Submit,wait,2000,
-18.Enter Search Area,type,Airport Chennai,"admin.setting.geo_fencing.area_search_filter"
-19.Wait For Load,wait,2000,
-20.Click Delete Button,click,,"admin.setting.geo_fencing.delete_button"
-21.Click Yes Delete It Button,click,,"admin.setting.geo_fencing.confirm_delete_button"
-22.Wait For Delete,wait,2000,</t>
   </si>
   <si>
     <t>1.Click Dashboard Icon,click,,"web.global.menu.dashboard"
@@ -4216,6 +4045,187 @@
 141.Click provider Services,click,,"admin.provider_service.menu_link"
 142.Filter Services List,type,{serviceName},"admin.provider_service.services.filter.input"
 143.wait,1000,,</t>
+  </si>
+  <si>
+    <t>1. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+2. Click Customer Icon,click,,"admin.menu.customer_icon"
+3. Click Add Customers,click,,"admin.menu.add_customers"
+4. Wait For Customer Heading,wait_until_visible,,"admin.customer.add_heading"
+5. Enter Customer Name,type,customer{randomAlpha} &gt;&gt; customerName,"admin.customer.input_name"
+6. Enter Email,type,customer_{timestamp}@gmail.com&gt;&gt;customerEmail,"admin.customer.input_email"
+7. Enter Contact Number,type,{randomPhone},"admin.customer.input_phone"
+8.Enter Emergency Number,type,{randomPhone},"admin.customer.input_Emergency_phone"
+9. Open Gender,click,,"admin.customer.dropdown_gender"
+10. Select Male,click,,"admin.customer.select_gender_male"
+11. Upload Profile Image,uploadfile,"src/main/resources/test-data/customer.jpg","admin.customer.upload_profile_img"
+12. Click Submit,click,,"web.global.action.submit"
+13. Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
+14. Click Dashboard,click,,"web.global.menu.dashboard"
+15. Click Customer Icon,click,,"admin.menu.customer_icon"
+16. Click Verified Customers,click,,"admin.menu.verified_customers"
+17. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
+18. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+19. Scroll Grid,tab,7,"admin.customer.filter_name"
+20. Click Edit Icon,click,,"admin.customer.grid.btn_edit"
+21. Click Close,click,,"web.global.action.close"
+22. Click Wallet Icon,click,,"admin.customer.grid.btn_wallet"
+23. Click Add Money,click,,"admin.customer.wallet.btn_add_money"
+24. Enter Wallet Amount,type,1000,"admin.customer.wallet.input_amount"
+25. Open Choose Option Dropdown,click,,"admin.customer.wallet.dropdown_option"
+26. Select Add Money,click,,"admin.customer.wallet.select_add_money"
+27. Click Submit,click,,"web.global.action.submit"
+28. Wait For Saved Successfully,wait_until_visible,,"web.global.toast.success"
+29. Click Add Money,click,,"admin.customer.wallet.btn_add_money"
+30. Enter Wallet Amount,type,200,"admin.customer.wallet.input_amount"
+31. Open Choose Option Dropdown,click,,"admin.customer.wallet.dropdown_option"
+32. Select Deduct Money,click,,"admin.customer.wallet.select_deduct_money"
+33. Click Submit,click,,"web.global.action.submit"
+34. Wait For Saved Successfully,wait_until_visible,,"web.global.toast.success"
+35. Click dashboard Icon,click,,"web.global.menu.dashboard"
+36. Click Customer Icon,click,,"admin.menu.customer_icon"
+37. Click Verified Customers,click,,"admin.menu.verified_customers"
+38. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
+39. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+40. Scroll Grid,tab,7,"admin.customer.filter_name"
+41. Click Loyalty Points Icon,click,,"admin.customer.grid.btn_loyalty_points"
+42. Click Manage Loyalty Points,click,,"admin.customer.loyalty.btn_manage"
+43. Open Service Dropdown,click,,"admin.customer.loyalty.dropdown_service"
+44. Select Bike Ride,click,,"admin.customer.loyalty.select_auto_ride"
+45. Open Choose Option Dropdown,click,,"admin.customer.loyalty.dropdown_option"
+46. Select Add Points,click,,"admin.customer.loyalty.select_add_points"
+47. Enter Points,type,30,"admin.customer.loyalty.input_points"
+48. Click Submit,click,,"web.global.action.submit"
+49. Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
+50. Click Manage Loyalty Points,click,,"admin.customer.loyalty.btn_manage"
+51. Open Service Dropdown,click,,"admin.customer.loyalty.dropdown_service"
+52. Select Bike Ride,click,,"admin.customer.loyalty.select_auto_ride"
+53. Open Choose Option Dropdown,click,,"admin.customer.loyalty.dropdown_option"
+54. Select Deduct Points,click,,"admin.customer.loyalty.select_deduct_points"
+55. Enter Points,type,10,"admin.customer.loyalty.input_points"
+56. Click Submit,click,,"web.global.action.submit"
+57. Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
+58. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+59. Click Customer Icon,click,,"admin.menu.customer_icon"
+60. Click Verified Customers,click,,"admin.menu.verified_customers"
+61. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
+62. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+63. Scroll Grid,tab,7,"admin.customer.filter_name"
+64. Click Disable Icon,click,,"admin.customer.grid.btn_block"
+65. Click Disable User Yes,click,,"web.global.dialog.btn_confirm_yes"
+66. Disable Reason,type,Client Complaints,"web.global.dialog.textarea_reason"
+67. Click Reject Yes,click,,"web.global.dialog.btn_confirm_yes"
+68. Verify Added Successfully,verify,,"web.global.toast.info"
+69. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+70. Click Customer Icon,click,,"admin.menu.customer_icon"
+71. Click Blocked Customers,click,,"admin.menu.blocked_customers"
+72. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+73. Scroll Grid,tab,10,"admin.customer.filter_name"
+74.Wait For Enable Icon,wait_until_visible,,"admin.customer.grid.btn_status_enable"
+75. Click Enable Icon,click,,"admin.customer.grid.btn_status_enable"
+76. Click Enable Yes,click,,"web.global.dialog.btn_confirm_yes"
+77. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+78. Click Customer Icon,click,,"admin.menu.customer_icon"
+79. Click Verified Customers,click,,"admin.menu.verified_customers"
+80. Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
+81. Filter Customer Name List,type,{customerName},"admin.customer.filter_name"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Click Dashboard,click,,"web.global.menu.dashboard"
+2.Click Report Issue,click,,"admin.report_issue.side_bar.menu"
+3.Click Customer Report Issue,click,,"admin.report_issue.side_bar_sub_menu.driver_report_issues"
+4.Click Today Button,click,,"web.global.dashboard.today_statistics"
+5.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
+6.Wait For Today Statistics,wait,2000,
+7.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
+8.Click Yesterday Button,Click,,"web.global.dashboard.yesterday_statistics"
+9.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
+10.Wait For Yesterday Statistics,wait,2000,
+11.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
+12.Click This Week Button,Click,,"web.global.dashboard.this_week_statistics"
+13.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
+14.Wait For This Week Statistics,wait,2000,
+15.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
+16.Click This Month Button,Click,,"web.global.dashboard.this_month_statistics"
+17.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
+18.Wait For This Month Statistics,wait,2000,
+19.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
+20.Click Last Month Button,Click,,"web.global.dashboard.last_month_statistics"
+21.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
+22.Wait For Last Month Statistics,wait,2000,
+23.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
+24.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
+25.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
+26.Wait For This Year Statistics,wait,2000,
+27.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
+28.Click Last Year Button,Click,,"web.global.dashboard.last_year_statistics"
+29.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
+30.Wait For Last Year Statistics,wait,2000,
+31.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
+32.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
+33.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
+34.Wait For This Year Statistics,wait,2000,
+35.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
+37.Click Created By Dropdown,click,,"admin.report_issue.driver_report_issues.created_by_dropdown"
+38.Click Search Box ,click,,"admin.report_issue.driver_report_issues.created_by_dropdown_search_box"
+39.Click The First Name,click,,"admin.report_issue.driver_report_issues.created_by_dropdown_first_name"
+40.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
+41.Wait For Name Load,wait,2000
+42.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
+43.Click Status Dropdown,click,,"admin.report_issue.driver_report_issues.status_dropdown"
+43.Click Unresolved Option,click,,"admin.report_issue.driver_report_issues.status_dropdown_unresolved_option"
+44.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
+45.Wait For Unresolved Load,wait,2000
+46.Scroll Grid,tab,8,"admin.report_issue.driver_report_issues.ticket_id_filter_input"
+47.Click Eye Icon,click,,"admin.report_issue.driver_report_issues.eye_icon"
+48.Click Close Eye View,click,,"admin.report_issue.driver_report_issues.close_eye_icon"
+49.Click Chat Button,click,,"admin.report_issue.driver_report_issues.chat_icon"
+50.Wait For Chat load,wait,2000
+51.Click Chat close,click_if_present,,"admin.report_issue.driver_report_issues.close_chat_icon"
+52.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
+53.Wait For Clear,wait,1000,
+54.Click Status Dropdown,click,,"admin.report_issue.driver_report_issues.status_dropdown"
+55.Click resolved Option,click,,"admin.report_issue.driver_report_issues.status_dropdown_resolved_option"
+56.Click Search Button,click,,"admin.report_issue.driver_report_issues.search_btn"
+57.Wait For Resolved Load,wait,2000
+58.Click Resolve Button,click,,"admin.report_issue.driver_report_issues.resolve_thumbs_icon"
+59.Click Confirm Resolve,click,,"admin.report_issue.driver_report_issues.resolve_confirm_yes"
+60.Wait For Resolve,wait,1000,
+61.Click Clear Button,click,,"admin.report_issue.driver_report_issues.clear_btn"
+</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard,Click,,"web.global.menu.dashboard"
+2.Click Setting Button,click,,"admin.setting.sidebar.menu"
+3.Click Geo Fencing,click,,"admin.setting.geo_fencing.sidebar_menu"
+4.Add Restrict Area,click,,"admin.setting.geo_fencing.add_restricted_area_btn"
+5.Enter Restricted Area Name,type,officers training academy chennai,"admin.setting.geo_fencing.area_name_input_field"
+6.Click The Status Button On,click,,"admin.setting.geo_fencing.status_toggle_button"
+7. Enter Search Location,type,officers training academy chennai,"admin.city_area.input_search_location"
+8. Select First Option,arrow_down,,"admin.city_area.input_search_location"
+9. Confirm Option,press_enter,,"admin.city_area.input_search_location"
+10. wait,3000,,
+11.Map Polygon,draw polygon,"-120;-120 : 120;-120 : 120;120 : -120;120 : -120;-120","//div[@class='ol-layer']//canvas"
+12.wait,3000,,
+13.Click Submit Button,click,,"admin.setting.geo_fencing.form_submit_button"
+14.Wait For Submit,wait,2000,
+15.Enter Search Area,type,officers training academy chennai,"admin.setting.geo_fencing.area_search_filter"
+16.Wait For Load,wait,2000
+17.Click Edit Button,click,,"admin.setting.geo_fencing.edit_button"
+18.Enter Restricted Area Name,type,Airport Chennai,"admin.setting.geo_fencing.area_name_input_field"
+19.Click The Status Button On,click,,"admin.setting.geo_fencing.status_toggle_button"
+20. Enter Search Location,type,Airport Chennai,"admin.city_area.input_search_location"
+21. wait,1000,,
+22. Select First Option,arrow_down,,"admin.city_area.input_search_location"
+23. Confirm Option,press_enter,,"admin.city_area.input_search_location"
+24. wait,1000,,
+25.Map Polygon,draw polygon,"-120;-120 : 120;-120 : 120;120 : -120;120 : -120;-120","//div[@class='ol-layer']//canvas"
+26.Click Submit Button,click,,"admin.setting.geo_fencing.form_submit_button"
+27.Wait For Submit,wait,2000,
+28.Enter Search Area,type,Airport Chennai,"admin.setting.geo_fencing.area_search_filter"
+29.Wait For Load,wait,2000,
+30.Click Delete Button,click,,"admin.setting.geo_fencing.delete_button"
+31.Click Yes Delete It Button,click,,"admin.setting.geo_fencing.confirm_delete_button"
+32.Wait For Delete,wait,2000,</t>
   </si>
 </sst>
 </file>
@@ -4629,7 +4639,7 @@
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>62</v>
@@ -4704,19 +4714,19 @@
     </row>
     <row r="2" spans="1:8" ht="360" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>60</v>
@@ -4779,16 +4789,16 @@
         <v>30</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>60</v>
@@ -4851,16 +4861,16 @@
         <v>42</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>60</v>
@@ -4923,19 +4933,19 @@
         <v>45</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4995,19 +5005,19 @@
         <v>51</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>129</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -5067,19 +5077,19 @@
         <v>54</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>134</v>
-      </c>
       <c r="D2" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -5139,22 +5149,22 @@
         <v>59</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D2" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>140</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -5217,13 +5227,13 @@
         <v>58</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>61</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>60</v>
@@ -5286,16 +5296,16 @@
         <v>93</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>90</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>60</v>
@@ -5355,13 +5365,13 @@
     </row>
     <row r="2" spans="1:8" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>90</v>
@@ -5428,7 +5438,7 @@
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>38</v>
@@ -5440,7 +5450,7 @@
         <v>43</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>94</v>
+        <v>181</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>32</v>
@@ -5506,19 +5516,19 @@
     </row>
     <row r="2" spans="1:8" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>60</v>
@@ -5578,22 +5588,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>148</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G2" s="8"/>
     </row>
@@ -5651,22 +5661,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>151</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G2" s="8"/>
     </row>
@@ -5724,22 +5734,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="G2" s="8"/>
     </row>
@@ -5797,19 +5807,19 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>36</v>
@@ -5869,13 +5879,13 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>23</v>
@@ -5941,19 +5951,19 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>36</v>
@@ -6014,19 +6024,19 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>47</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>48</v>
@@ -6092,19 +6102,19 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>37</v>
@@ -6164,19 +6174,19 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>49</v>
@@ -6237,7 +6247,7 @@
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -6312,19 +6322,19 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>56</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>57</v>
@@ -6386,7 +6396,7 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>9</v>
@@ -6454,7 +6464,7 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>10</v>
@@ -6466,7 +6476,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>33</v>
@@ -6529,7 +6539,7 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>11</v>
@@ -6541,7 +6551,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>34</v>
@@ -6604,7 +6614,7 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>12</v>
@@ -6616,7 +6626,7 @@
         <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>35</v>
@@ -6679,7 +6689,7 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>50</v>
@@ -6691,7 +6701,7 @@
         <v>53</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>52</v>
@@ -6767,7 +6777,7 @@
         <v>69</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>70</v>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC472F1-866B-4609-A023-418DE2A35072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDAA42DD-6314-4ABC-850C-0AA7A6F7CB32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>
@@ -1471,42 +1471,6 @@
     <t>7.Select Auto Ride Option,click,,"//span[normalize-space()='Auto Ride']"
 8.Wait for Auto Ride,wait_until_visible,,"//label[contains(.,'Driver Services')]/following-sibling::mat-checkbox"
 9.Click Auto Ride, click, , "//label[contains(.,'Driver Services')]/following-sibling::mat-checkbox"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click Dashboard Icon,click,,"web.global.menu.dashboard"
-2. Click Setting menu,click,,"web.global.menu.settings"
-3. Click City area menu,click,,"admin.menu.city_area"
-4. Wait For Area List,wait_until_visible,,"admin.city_area.list_heading"
-5. Click Add City Area button,click,,"admin.city_area.btn_add"
-6. Wait For City Area heading,wait_until_visible,,"admin.city_area.add_heading"
-7. Enter Area Name,type,triplicane_{timestamp} &gt;&gt; areaName,"admin.city_area.input_name"
-8. Open Status Dropdown,click,,"admin.city_area.dropdown_status"
-9. Select Active,click,,"admin.city_area.select_status_active"
-10. Enter City Area,type,triplicane,"admin.city_area.input_search_location"
-11. wait,1000,,
-12. Select First Option,arrow_down,,"admin.city_area.input_search_location"
-13. Confirm Option,press_enter,,"admin.city_area.input_search_location"
-14. wait,1000,,
-15. Map Polygon,draw polygon,"-120;-120 : 120;-120 : 120;120 : -120;120 : -120;-120","//div[@class='ol-layer']//canvas"
-16. Click Submit,click,,"web.global.action.submit"
-17. Wait For Success Message,wait_until_visible,,"web.global.toast.success"
-18. Click Dashboard Icon,click,,"web.global.menu.dashboard"
-19. Click Transport Services,click,,"admin.transport.menu.card"
-20. Wait For Transport Page,wait_until_visible,,"admin.transport.page.header"
-21. Click Add Category,click,,"admin.transport.add_category.btn"
-22. Open Select City Dropdown,click,,"admin.transport.city.dropdown"
-23. Search City Area,type,{areaName},"admin.transport.input_filter_city"
-24. Verify Area in Dropdown,verify,,"admin.transport.city.dynamic_option"
-25. Click close,click,,"web.global.action.close"
-26.Click Dashboard Icon,click,,"web.global.menu.dashboard"
-27. Click Setting menu,click,,"web.global.menu.settings"
-28. Click City admin menu,click,,"admin.menu.city_admin"
-29. Wait For City Admin List,wait_until_visible,,"admin.city_admin.list_heading"
-30. Click Add City Admin button,click,,"admin.city_admin.btn_add"
-31. Open Select City Dropdown,click,,"admin.city_admin.select_city_dropdown"
-32. Select {areaName},click,,"admin.city_admin.select_dynamic_option"
-33. Verify Selection,verify,,"admin.city_admin.verify_dropdown_value"
-</t>
   </si>
   <si>
     <t>Removed Test Cases</t>
@@ -2495,69 +2459,6 @@
   </si>
   <si>
     <t>SA_TS_23</t>
-  </si>
-  <si>
-    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
-2.Click Transport Service,Click,,"admin.transport.menu.card"
-3.Enter Services,type,Auto Ride,"admin.transport.grid.name_filter"
-4.Click Home Icon,Click,,"admin.transport.home.icon"
-6.Click Earning Report,click,,"admin.transport.earning_reports.top_menu_btn"
-7.Click Today Button,Click,,"web.global.dashboard.today_statistics"
-8.Wait For Today Statistics,wait,2000,
-9.Click Yesterday Button,Click,,"web.global.dashboard.yesterday_statistics"
-10.Wait For Yesterday Statistics,wait,2000,
-11.Click This Week Button,Click,,"web.global.dashboard.this_week_statistics"
-12.Wait For This Week Statistics,wait,2000,
-13.Click This Month Button,Click,,"web.global.dashboard.this_month_statistics"
-14.Wait For This Month Statistics,wait,2000,
-15.Click Last Month Button,Click,,"web.global.dashboard.last_month_statistics"
-16.Wait For Last Month Statistics,wait,2000,
-17.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
-18.Wait For This Year Statistics,wait,2000,
-19.Click Last Year Button,Click,,"web.global.dashboard.last_year_statistics"
-20.Wait For Last Year Statistics,wait,2000,
-21.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
-22.Wait For This Year Statistics,wait,2000,
-23.Select Driver Dropdown,click,,"admin.transport.earning_reports.driver_dropdown"
-24.Enter Driver Name In Drop Down,type,regression.approved_driver.name,"admin.transport.driver_dropdown_searchbox"
-25.Click Driver Name,click,,"admin.transport.driver_earning_reports_dropdown_first"
-26.Click Select Customer Dropdown,click,,"admin.transport.earning_reports.customer_dropdown"
-27.Enter Customer Name In Drop Down,type,regression.customer.name,"admin.transport.customer_dropdown_searchbox"
-28.Click Customer Name,click,,"admin.transport.customer_earning_reports_dropdown_first"
-29.Click payment type,click,,"admin.transport.earning_reports.payment_type_dropdown"
-30.Click Select cash Payment Type,click,,"admin.transport.earning_reports.payment_type_cash"
-31.Wait For Cash Payment,wait,2000,
-32.Click payment type,click,,"admin.transport.earning_reports.payment_type_dropdown"
-33.Click Razor Payment,click,,"admin.transport.earning_reports.payment_type_razorpay"
-34.Wait For Razor Payment,wait,2000,
-35.Click payment type,click,,"admin.transport.earning_reports.payment_type_dropdown"
-36.Click wallet option,click,,"admin.transport.earning_reports.payment_type_wallet"
-37.Wait For Wallet Payment,wait,2000,
-38.Click payment type,click,,"admin.transport.earning_reports.payment_type_dropdown"
-39.Click Select cash Payment Type,click,,"admin.transport.earning_reports.payment_type_cash"
-40.Click Driver Payment Status,click,,"admin.transport.earning_reports.payment_status_dropdown"
-41.Click Settled Option,click,,"admin.transport.earning_reports.payment_status_settled"
-42.Wait For Settled Payment,wait,2000,
-43.Click Driver Payment Status,click,,"admin.transport.earning_reports.payment_status_dropdown"
-44.Click Unsettled Option,click,,"admin.transport.earning_reports.payment_status_unsettled"
-45.Click Search Button,click,,"admin.transport.earning_reports.search_btn"
-46.Click Clear Button,click,,"admin.transport.earning_reports.clear_btn"
-47.Click payment type,click,,"admin.transport.earning_reports.payment_type_dropdown"
-48.Click Select cash Payment Type,click,,"admin.transport.earning_reports.payment_type_cash"
-49.Click Driver Payment Status,click,,"admin.transport.earning_reports.payment_status_dropdown"
-50.Click Unsettled Option,click,,"admin.transport.earning_reports.payment_status_unsettled"
-51.Click Search Button,click,,"admin.transport.earning_reports.search_btn"
-52.Wait For Unsettled Transaction,wait,2000,
-53.Click Checkbox,click,"admin.transport.earning_reports.checkbox"
-54.Wait For  Check box Selection,wait,1000,
-55.Click Settle Transaction Button,click,"admin.transport.earning_reports.mark_as_settle_btn"
-55.Wait For  Settlement,wait,1000,
-56.Click Payment StatusFilter,click,,"admin.transport.earning_reports.payment_status_filter"
-57.Scroll Grid,tab,24,"admin.transport.earning_reports.payment_status_filter"
-58.Click Eye Button,Click,,"admin.transport.earning_reports.eye_btn"
-59.Wait For View,wait,200,
-60.Close Earning Report View,click,,"admin.transport.earning_reports.eye_btn_close"
-61.Wait For Close,wait,2000,</t>
   </si>
   <si>
     <t>This comprehensive regression test suite validates the billing algorithms, transactional search grids, and balance clearing pipelines within the Transport Services Earning Reports dashboard. The script targets a specific logistical sector ("Auto Ride") and continuously cycles through multi-tiered filter matrices—ranging from chronological time boundaries (Today, Yesterday, This Week, This Month, Last Month, and This Year) to dedicated account entities like designated driver profiles and customer records. It thoroughly audits payment channel routing by validating interface adjustments between Cash, Razorpay, and Digital Wallet modes, and accurately tests automated ledger balances by isolating Settled vs. Unsettled states. Crucially, the execution verifies critical backend database updates by selecting outstanding line entries, launching a transactional Settle Transaction command to alter balance properties on the fly, and performing grid scans and deep-dive element tracking views (via modal eye overlays) to ensure immediate data synchronization with zero stale state failures.</t>
@@ -4194,38 +4095,138 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">1. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+2. Click Setting menu,click,,"web.global.menu.settings"
+3. Click City area menu,click,,"admin.menu.city_area"
+4. Wait For Area List,wait_until_visible,,"admin.city_area.list_heading"
+5. Click Add City Area button,click,,"admin.city_area.btn_add"
+6. Wait For City Area heading,wait_until_visible,,"admin.city_area.add_heading"
+7. Enter Area Name,type,triplicane_{timestamp} &gt;&gt; areaName,"admin.city_area.input_name"
+8. Open Status Dropdown,click,,"admin.city_area.dropdown_status"
+9. Select Active,click,,"admin.city_area.select_status_active"
+10. Enter City Area,type,triplicane,"admin.city_area.input_search_location"
+11. wait,1000,,
+12. Select First Option,arrow_down,,"admin.city_area.input_search_location"
+13. Confirm Option,press_enter,,"admin.city_area.input_search_location"
+14. wait,1000,,
+15. Map Polygon,draw polygon,"-60;-60 : 60;-60 : 60;60 : -60;60","//div[@class='ol-layer']//canvas"
+16. Click Submit,click,,"web.global.action.submit"
+17. Wait For Success Message,wait_until_visible,,"web.global.toast.success"
+18. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+19. Click Transport Services,click,,"admin.transport.menu.card"
+20. Wait For Transport Page,wait_until_visible,,"admin.transport.page.header"
+21. Click Add Category,click,,"admin.transport.add_category.btn"
+22. Open Select City Dropdown,click,,"admin.transport.city.dropdown"
+23. Search City Area,type,{areaName},"admin.transport.input_filter_city"
+24. Verify Area in Dropdown,verify,,"admin.transport.city.dynamic_option"
+25. Click close,click,,"web.global.action.close"
+26.Click Dashboard Icon,click,,"web.global.menu.dashboard"
+27. Click Setting menu,click,,"web.global.menu.settings"
+28. Click City admin menu,click,,"admin.menu.city_admin"
+29. Wait For City Admin List,wait_until_visible,,"admin.city_admin.list_heading"
+30. Click Add City Admin button,click,,"admin.city_admin.btn_add"
+31. Open Select City Dropdown,click,,"admin.city_admin.select_city_dropdown"
+32. Select {areaName},click,,"admin.city_admin.select_dynamic_option"
+33. Verify Selection,verify,,"admin.city_admin.verify_dropdown_value"
+</t>
+  </si>
+  <si>
     <t>1.Click Dashboard,Click,,"web.global.menu.dashboard"
 2.Click Setting Button,click,,"admin.setting.sidebar.menu"
 3.Click Geo Fencing,click,,"admin.setting.geo_fencing.sidebar_menu"
 4.Add Restrict Area,click,,"admin.setting.geo_fencing.add_restricted_area_btn"
-5.Enter Restricted Area Name,type,officers training academy chennai,"admin.setting.geo_fencing.area_name_input_field"
+5.Enter Restricted Area Name,type,chennai airport,"admin.setting.geo_fencing.area_name_input_field"
 6.Click The Status Button On,click,,"admin.setting.geo_fencing.status_toggle_button"
-7. Enter Search Location,type,officers training academy chennai,"admin.city_area.input_search_location"
-8. Select First Option,arrow_down,,"admin.city_area.input_search_location"
-9. Confirm Option,press_enter,,"admin.city_area.input_search_location"
-10. wait,3000,,
-11.Map Polygon,draw polygon,"-120;-120 : 120;-120 : 120;120 : -120;120 : -120;-120","//div[@class='ol-layer']//canvas"
-12.wait,3000,,
-13.Click Submit Button,click,,"admin.setting.geo_fencing.form_submit_button"
-14.Wait For Submit,wait,2000,
-15.Enter Search Area,type,officers training academy chennai,"admin.setting.geo_fencing.area_search_filter"
-16.Wait For Load,wait,2000
-17.Click Edit Button,click,,"admin.setting.geo_fencing.edit_button"
-18.Enter Restricted Area Name,type,Airport Chennai,"admin.setting.geo_fencing.area_name_input_field"
-19.Click The Status Button On,click,,"admin.setting.geo_fencing.status_toggle_button"
-20. Enter Search Location,type,Airport Chennai,"admin.city_area.input_search_location"
-21. wait,1000,,
-22. Select First Option,arrow_down,,"admin.city_area.input_search_location"
-23. Confirm Option,press_enter,,"admin.city_area.input_search_location"
-24. wait,1000,,
-25.Map Polygon,draw polygon,"-120;-120 : 120;-120 : 120;120 : -120;120 : -120;-120","//div[@class='ol-layer']//canvas"
-26.Click Submit Button,click,,"admin.setting.geo_fencing.form_submit_button"
-27.Wait For Submit,wait,2000,
-28.Enter Search Area,type,Airport Chennai,"admin.setting.geo_fencing.area_search_filter"
-29.Wait For Load,wait,2000,
-30.Click Delete Button,click,,"admin.setting.geo_fencing.delete_button"
-31.Click Yes Delete It Button,click,,"admin.setting.geo_fencing.confirm_delete_button"
-32.Wait For Delete,wait,2000,</t>
+7. Enter Search Location,type,chennai airport,"admin.city_area.input_search_location"
+8.Wait For Options To Load,wait,3000,
+9. Select First Option,arrow_down,,"admin.city_area.input_search_location"
+10. Confirm Option,press_enter,,"admin.city_area.input_search_location"
+11. Wait For Map To Load,wait,3000,
+12.Map Polygon,draw polygon,"-60;-60 : 60;-60 : 60;60 : -60;60","//div[@class='ol-layer']//canvas"
+13.Wait For Polygon Draw,wait,3000,
+14.Click Submit Button,click,,"admin.setting.geo_fencing.form_submit_button"
+15.Wait For Submit,wait,2000,
+16.Enter Search Area,type,chennai airport,"admin.setting.geo_fencing.area_search_filter"
+17.Wait For Load,wait,2000
+18.Click Edit Button,click,,"admin.setting.geo_fencing.edit_button"
+19.Enter Restricted Area Name,type,chennai port trust,"admin.setting.geo_fencing.area_name_input_field"
+20.Click The Status Button On,click,,"admin.setting.geo_fencing.status_toggle_button"
+21. Enter Search Location,type,chennai port trust,"admin.city_area.input_search_location"
+22. wait,1000,,
+23. Select First Option,arrow_down,,"admin.city_area.input_search_location"
+24. Confirm Option,press_enter,,"admin.city_area.input_search_location"
+25. wait,1000,,
+26.Map Polygon,draw polygon,"-60;-60 : 60;-60 : 60;60 : -60;60","//div[@class='ol-layer']//canvas"
+27.Click Submit Button,click,,"admin.setting.geo_fencing.form_submit_button"
+28.Wait For Submit,wait,2000,
+29.Enter Search Area,type,chennai port trust,"admin.setting.geo_fencing.area_search_filter"
+30.Wait For Load,wait,2000,
+31.Click Delete Button,click,,"admin.setting.geo_fencing.delete_button"
+32.Click Yes Delete It Button,click,,"admin.setting.geo_fencing.confirm_delete_button"
+33.Wait For Delete,wait,2000,</t>
+  </si>
+  <si>
+    <t>1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+2.Click Transport Service,Click,,"admin.transport.menu.card"
+3.Enter Services,type,Auto Ride,"admin.transport.grid.name_filter"
+4.Click Home Icon,Click,,"admin.transport.home.icon"
+6.Click Earning Report,click,,"admin.transport.earning_reports.top_menu_btn"
+7.Click Today Button,Click,,"web.global.dashboard.today_statistics"
+8.Wait For Today Statistics,wait,2000,
+9.Click Yesterday Button,Click,,"web.global.dashboard.yesterday_statistics"
+10.Wait For Yesterday Statistics,wait,2000,
+11.Click This Week Button,Click,,"web.global.dashboard.this_week_statistics"
+12.Wait For This Week Statistics,wait,2000,
+13.Click This Month Button,Click,,"web.global.dashboard.this_month_statistics"
+14.Wait For This Month Statistics,wait,2000,
+15.Click Last Month Button,Click,,"web.global.dashboard.last_month_statistics"
+16.Wait For Last Month Statistics,wait,2000,
+17.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
+18.Wait For This Year Statistics,wait,2000,
+19.Click Last Year Button,Click,,"web.global.dashboard.last_year_statistics"
+20.Wait For Last Year Statistics,wait,2000,
+21.Click This Year Button,Click,,"web.global.dashboard.this_year_statistics"
+22.Wait For This Year Statistics,wait,2000,
+23.Select Driver Dropdown,click,,"admin.transport.earning_reports.driver_dropdown"
+24.Enter Driver Name In Drop Down,type,regression.approved_driver.name,"admin.transport.driver_dropdown_searchbox"
+25.Click Driver Name,click,,"admin.transport.driver_earning_reports_dropdown_first"
+26.Click Select Customer Dropdown,click,,"admin.transport.earning_reports.customer_dropdown"
+27.Enter Customer Name In Drop Down,type,regression.customer.name,"admin.transport.customer_dropdown_searchbox"
+28.Click Customer Name,click,,"admin.transport.customer_earning_reports_dropdown_first"
+29.Click payment type,click,,"admin.transport.earning_reports.payment_type_dropdown"
+30.Click Select cash Payment Type,click,,"admin.transport.earning_reports.payment_type_cash"
+31.Wait For Cash Payment,wait,2000,
+32.Click payment type,click,,"admin.transport.earning_reports.payment_type_dropdown"
+33.Click Razor Payment,click,,"admin.transport.earning_reports.payment_type_razorpay"
+34.Wait For Razor Payment,wait,2000,
+35.Click payment type,click,,"admin.transport.earning_reports.payment_type_dropdown"
+36.Click wallet option,click,,"admin.transport.earning_reports.payment_type_wallet"
+37.Wait For Wallet Payment,wait,2000,
+38.Click payment type,click,,"admin.transport.earning_reports.payment_type_dropdown"
+39.Click Select cash Payment Type,click,,"admin.transport.earning_reports.payment_type_cash"
+40.Click Driver Payment Status,click,,"admin.transport.earning_reports.payment_status_dropdown"
+41.Click Settled Option,click,,"admin.transport.earning_reports.payment_status_settled"
+42.Wait For Settled Payment,wait,2000,
+43.Click Driver Payment Status,click,,"admin.transport.earning_reports.payment_status_dropdown"
+44.Click Unsettled Option,click,,"admin.transport.earning_reports.payment_status_unsettled"
+45.Click Search Button,click,,"admin.transport.earning_reports.search_btn"
+46.Click Clear Button,click,,"admin.transport.earning_reports.clear_btn"
+47.Click payment type,click,,"admin.transport.earning_reports.payment_type_dropdown"
+48.Click Select cash Payment Type,click,,"admin.transport.earning_reports.payment_type_cash"
+49.Click Driver Payment Status,click,,"admin.transport.earning_reports.payment_status_dropdown"
+50.Click Unsettled Option,click,,"admin.transport.earning_reports.payment_status_unsettled"
+51.Click Search Button,click,,"admin.transport.earning_reports.search_btn"
+52.Wait For Unsettled Transaction,wait,2000,
+53.Click Checkbox,click,"admin.transport.earning_reports.checkbox"
+54.Wait For  Check box Selection,wait,1000,
+55.Click Settle Transaction Button,click,"admin.transport.earning_reports.mark_as_settle_btn"
+55.Wait For  Settlement,wait,1000,
+56.Click Payment StatusFilter,click,,"admin.transport.earning_reports.payment_status_filter"
+57.Scroll Grid,tab,25,"admin.transport.earning_reports.payment_status_filter"
+58.Click Eye Button,Click,,"admin.transport.earning_reports.eye_btn"
+59.Wait For View,wait,200,
+60.Close Earning Report View,click,,"admin.transport.earning_reports.eye_btn_close"
+61.Wait For Close,wait,2000,</t>
   </si>
 </sst>
 </file>
@@ -4639,7 +4640,7 @@
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>62</v>
@@ -4714,19 +4715,19 @@
     </row>
     <row r="2" spans="1:8" ht="360" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>60</v>
@@ -4789,16 +4790,16 @@
         <v>30</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>60</v>
@@ -4861,16 +4862,16 @@
         <v>42</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>60</v>
@@ -4933,19 +4934,19 @@
         <v>45</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -5005,19 +5006,19 @@
         <v>51</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>128</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>130</v>
+        <v>183</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -5077,19 +5078,19 @@
         <v>54</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C2" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -5138,7 +5139,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -5149,22 +5150,22 @@
         <v>59</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>138</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -5227,13 +5228,13 @@
         <v>58</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>61</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>60</v>
@@ -5293,19 +5294,19 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>60</v>
@@ -5365,19 +5366,19 @@
     </row>
     <row r="2" spans="1:8" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>60</v>
@@ -5430,7 +5431,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -5438,7 +5439,7 @@
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>38</v>
@@ -5450,13 +5451,13 @@
         <v>43</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -5516,19 +5517,19 @@
     </row>
     <row r="2" spans="1:8" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>60</v>
@@ -5580,7 +5581,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -5588,22 +5589,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G2" s="8"/>
     </row>
@@ -5653,7 +5654,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -5661,22 +5662,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G2" s="8"/>
     </row>
@@ -5726,7 +5727,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -5734,22 +5735,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="G2" s="8"/>
     </row>
@@ -5807,19 +5808,19 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>36</v>
@@ -5879,22 +5880,22 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -5951,19 +5952,19 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>36</v>
@@ -6016,36 +6017,36 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>47</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>48</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -6102,19 +6103,19 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>37</v>
@@ -6174,19 +6175,19 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>49</v>
@@ -6247,7 +6248,7 @@
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -6259,7 +6260,7 @@
         <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>76</v>
+        <v>181</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>32</v>
@@ -6322,19 +6323,19 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>56</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>57</v>
@@ -6388,7 +6389,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -6396,7 +6397,7 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>9</v>
@@ -6408,13 +6409,13 @@
         <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -6464,7 +6465,7 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>10</v>
@@ -6476,7 +6477,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>33</v>
@@ -6539,7 +6540,7 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>11</v>
@@ -6551,7 +6552,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>34</v>
@@ -6614,7 +6615,7 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>12</v>
@@ -6626,7 +6627,7 @@
         <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>35</v>
@@ -6681,7 +6682,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -6689,7 +6690,7 @@
     </row>
     <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>50</v>
@@ -6701,13 +6702,13 @@
         <v>53</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>52</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -6777,7 +6778,7 @@
         <v>69</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>70</v>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{512B79EF-7F04-4A2C-A84C-EFB163308031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="17" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Hybrid_Framework\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Framework_For_WE1_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{512B79EF-7F04-4A2C-A84C-EFB163308031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93B200E7-37B5-47FB-B4D4-D6F24856E45A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="185">
   <si>
     <t>City Area</t>
   </si>
@@ -4227,6 +4227,9 @@
 59.Wait For View,wait,200,
 60.Close Earning Report View,click,,"admin.transport.earning_reports.eye_btn_close"
 61.Wait For Close,wait,2000,</t>
+  </si>
+  <si>
+    <t>Test Case ID</t>
   </si>
 </sst>
 </file>
@@ -4620,7 +4623,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2</v>
+        <v>184</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>3</v>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Framework_For_WE1_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93B200E7-37B5-47FB-B4D4-D6F24856E45A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ADF90FE-3740-4F57-BF2C-6189E4F6ABDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="26" activeTab="29" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="252">
   <si>
     <t>City Area</t>
   </si>
@@ -62,15 +62,9 @@
     <t>Requirement Title</t>
   </si>
   <si>
-    <t>Test Case ID(s)</t>
-  </si>
-  <si>
     <t>Test Case Description</t>
   </si>
   <si>
-    <t>Test Step Description</t>
-  </si>
-  <si>
     <t>Precondition</t>
   </si>
   <si>
@@ -102,9 +96,6 @@
   </si>
   <si>
     <t>Validate that the admin can successfully add a new Auto driver by entering valid driver details and vehicle details and approve him from pendind documents by adding documents and verify he is coming in on approved drivers list .</t>
-  </si>
-  <si>
-    <t>TC_CA_00_super_admin_login</t>
   </si>
   <si>
     <t>Verify successful authentication of the Super Admin role using valid credentials and Dashboard access validation.</t>
@@ -867,15 +858,6 @@
   </si>
   <si>
     <t>Customer</t>
-  </si>
-  <si>
-    <t>TC_CA_01_add_customer</t>
-  </si>
-  <si>
-    <t>TC_CA_02_add_city_area</t>
-  </si>
-  <si>
-    <t>TC_CA_03_add_city_admin</t>
   </si>
   <si>
     <t>SA_TS_11</t>
@@ -1346,18 +1328,6 @@
   </si>
   <si>
     <t>TransportCityAdmin</t>
-  </si>
-  <si>
-    <t>TC_CA_04_add_verify_auto_driver</t>
-  </si>
-  <si>
-    <t>TC_CA_05_add_verify_bike_driver</t>
-  </si>
-  <si>
-    <t>TC_CA_06_add_verify_taxi_driver</t>
-  </si>
-  <si>
-    <t>TC_CA_07_transport_service_complete_test</t>
   </si>
   <si>
     <t>This test case validates the end-to-end lifecycle of an tranport city admin. The workflow initiates with the configuration of a new City Admin profile—integrating dynamic data generation for credentials and city mapping—while assigning permissions across specific transport services (Bike, Taxi, Auto) and driver management modules.The process systematically transitions from the super-admin creation phase to a live login validation, where the new admin’s restricted environment is audited to ensure the presence of authorized transport menus and the successful exclusion of unauthorized delivery and provider service modules. The validation cycle culminates in the execution of complex driver onboarding within the newly created admin account—spanning personal, vehicle, and banking data integration—thereby confirming the platform’s security architecture, hierarchical permission integrity, and the operational stability of city-specific administrative workflows.</t>
@@ -1460,9 +1430,6 @@
   </si>
   <si>
     <t>SA_TS_08</t>
-  </si>
-  <si>
-    <t>TC_CA_08_add_transport_city_admin</t>
   </si>
   <si>
     <t>Removed Steps</t>
@@ -2223,33 +2190,7 @@
     <t>SA_RD_01</t>
   </si>
   <si>
-    <t>SA_RD_21
-SA_RD_22
-SA_RD_23
-SA_RD_24</t>
-  </si>
-  <si>
-    <t>SA_RD_56</t>
-  </si>
-  <si>
-    <t>SA_RD_64</t>
-  </si>
-  <si>
-    <t>SA_RD_26
-SA_RD_27
-SA_RD_28</t>
-  </si>
-  <si>
     <t>SA_TS_09</t>
-  </si>
-  <si>
-    <t>TC_CA_09_Tranport_Service_Statistic_Test</t>
-  </si>
-  <si>
-    <t>TC_CA_10_Tranport_Driver_Statistic_Test</t>
-  </si>
-  <si>
-    <t>TC_CA_11_Transport_Service_Ride_Test</t>
   </si>
   <si>
     <t xml:space="preserve">1.Click Dashboard Icon,click,, "web.global.menu.dashboard"
@@ -2355,9 +2296,6 @@
     <t>This targeted regression test suite validates the operational map metrics and driver tracking grids within the Transport Services Aerial View monitoring control center. The test targets a specific service class ("Auto Ride") and systematically loops through all real-time operational filters in the geospatial dashboard—specifically auditing the telemetry statuses for All, Available, Enroute to Pickup, Reached Pickup, and Ongoing tracking segments. For each individual status layout, the script uses the fault-tolerant click_if_present keyword to launch detailed map overlay info-popups via the tracking eye icon, verifies panel readability, and dismisses the popup cleanly before moving to the next status. This process ensures that dynamic map layers, dispatcher tooltips, and real-time operational status updates function flawlessly across the administrative workspace without crashing due to unexpected timing or missing elements.</t>
   </si>
   <si>
-    <t>TC_CA_12_Transport_Service_Aerial_View</t>
-  </si>
-  <si>
     <t>SA_TS_22</t>
   </si>
   <si>
@@ -2455,9 +2393,6 @@
     <t>Transport Service Earning Reports Complete Test</t>
   </si>
   <si>
-    <t>TC_CA_13_Transport_Service_Earning_Reports</t>
-  </si>
-  <si>
     <t>SA_TS_23</t>
   </si>
   <si>
@@ -2465,9 +2400,6 @@
   </si>
   <si>
     <t>Transport Provider List Tests</t>
-  </si>
-  <si>
-    <t>TC_CA_14_Transport_Provider_List_Test</t>
   </si>
   <si>
     <t>SA_TS_24</t>
@@ -2528,9 +2460,6 @@
     <t>Transport Service Review Tests</t>
   </si>
   <si>
-    <t>TC_CA_15_Transport_Service_Review_Test</t>
-  </si>
-  <si>
     <t>14.Click Select Cutomer,click,,"//span[@aria-label='Select a customer']"
 15.Enter Name,type,Mohamed Yasir,"//input[@role='searchbox']"
 16.Click The Customer Name,click,,"//span[@class='ng-star-inserted']"
@@ -2580,9 +2509,6 @@
   </si>
   <si>
     <t>SA_TS_26</t>
-  </si>
-  <si>
-    <t>TC_CA_16_subscription_plan_test</t>
   </si>
   <si>
     <t>Report Issue FAQ Tests</t>
@@ -2703,46 +2629,7 @@
     <t>Geo Fencing Test</t>
   </si>
   <si>
-    <t>TC_CA_17_Geo_Fencing_Test</t>
-  </si>
-  <si>
-    <t>TC_CA_18_Panic_Call_Test</t>
-  </si>
-  <si>
-    <t>TC_CA_19_Dashboard_Test</t>
-  </si>
-  <si>
-    <t>TC_CA_20_Report_Issue_Faq_Test</t>
-  </si>
-  <si>
-    <t>TC_CA_21_Customer_Report_Issues</t>
-  </si>
-  <si>
-    <t>TC_CA_22_Driver_Report_Issues</t>
-  </si>
-  <si>
-    <t>TC_CA_23_add_store</t>
-  </si>
-  <si>
-    <t>TC_CA_24_store_oprerations</t>
-  </si>
-  <si>
-    <t>TC_CA_25_store_status_management</t>
-  </si>
-  <si>
-    <t>TC_CA_26_delivery_service_complete_test</t>
-  </si>
-  <si>
-    <t>TC_CA_27_add_provider</t>
-  </si>
-  <si>
-    <t>TC_CA_28_provider_service_full_lifecycle_test</t>
-  </si>
-  <si>
     <t>SA_TS_29</t>
-  </si>
-  <si>
-    <t>TC_CA_29_test_data_cleanup</t>
   </si>
   <si>
     <t>1.Click Dashboard Icon,click,,"web.global.menu.dashboard"
@@ -4229,7 +4116,484 @@
 61.Wait For Close,wait,2000,</t>
   </si>
   <si>
-    <t>Test Case ID</t>
+    <t>Test Case ID [Manual]</t>
+  </si>
+  <si>
+    <t>Test Case ID [Regression]</t>
+  </si>
+  <si>
+    <t>TC_RG_00_super_admin_login</t>
+  </si>
+  <si>
+    <t>TC_SA_00_super_admin_login</t>
+  </si>
+  <si>
+    <t>Manual Test  Steps</t>
+  </si>
+  <si>
+    <t>Regression Test Steps</t>
+  </si>
+  <si>
+    <t>1. Enter the Email as "super_admin@gmail.com" in the Email field.
+2. Enter the Password as "R1mep@321" in the Password field.
+3. Click the LOGIN button.
+4. Verify that the Dashboard Summary page is displayed.</t>
+  </si>
+  <si>
+    <t>TC_SA_01_add_customer</t>
+  </si>
+  <si>
+    <t>TC_RG_01_add_customer</t>
+  </si>
+  <si>
+    <t>1. Navigate to Customer Management &gt; Add Customer.
+2. Fill in all required customer details (Name, Email, Contact Number, Emergency Contact, Gender, and Profile Image) and submit the form.
+3. Navigate to Verified Customers and search for the newly created customer.
+4. Click Edit to verify customer profile details, then close the modal.
+5. Open Customer Wallet and perform an "Add Money" transaction (e.g., 1000) followed by a "Deduct Money" transaction (e.g., 200).
+6. Open Loyalty Points Management for the customer and add 30 points for Bike Ride service, then deduct 10 points for the same service.
+7. Block/Disable the customer account from the Verified Customers list, providing a valid reason (e.g., "Client Complaints").
+8. Navigate to Blocked Customers, locate the customer, and re-enable their account.
+9. Return to Verified Customers and verify that the customer is successfully restored to active status.</t>
+  </si>
+  <si>
+    <t>TC_RG_02_add_city_area</t>
+  </si>
+  <si>
+    <t>TC_SA_02_add_city_area</t>
+  </si>
+  <si>
+    <t>SA_RD_02</t>
+  </si>
+  <si>
+    <t>1. Navigate to Settings &gt; City Area.
+2. Click Add City Area and enter the Area Name (e.g., "triplicane" with a unique timestamp).
+3. Set the status to Active, search for "triplicane" in the location search bar, and select the location.
+4. Draw the polygon boundary on the map canvas to define the city area and submit the form.
+5. Verify that the city area is created successfully via the confirmation toast message.
+6. Navigate to Transport Services &gt; Add Category, open the Select City dropdown, and verify that the newly created city area is listed as an option.
+7. Navigate to Settings &gt; City Admin, click Add City Admin, and verify that the newly created city area is available and selectable in the City dropdown.</t>
+  </si>
+  <si>
+    <t>SA_RD_03</t>
+  </si>
+  <si>
+    <t>TC_RG_03_add_city_admin</t>
+  </si>
+  <si>
+    <t>TC_SA_03_add_city_admin</t>
+  </si>
+  <si>
+    <t>1. Navigate to Settings &gt; City Admin and click the Add City Admin button.
+2. Fill in the required admin details including Name, Email, Password, and select the target City/Area from the dropdown.
+3. Configure the role permissions by assigning specific checkboxes across modules:
+   - Transport Service (Auto Ride)
+   - Customers (Add, Verified, Non-Verified, Blocked, and Deleted Customers)
+   - Providers (Transport Providers List)
+   - Drivers (Add, Approved, Un-Approved, Blocked, Reject, and Deleted Drivers)
+   - Subscription Plan &amp; Cash Out (Driver Subscription Plan, Driver Cash Out)
+   - Report Issue (Customer, Driver, and Provider Report Issues, Settings, FAQs)
+4. Submit the form and verify that the creation confirmation message appears.
+5. Filter the City Admin list by the newly created Admin Name to confirm the record exists.</t>
+  </si>
+  <si>
+    <t>SA_RD_04</t>
+  </si>
+  <si>
+    <t>TC_RG_04_add_verify_auto_driver</t>
+  </si>
+  <si>
+    <t>TC_SA_04_add_verify_auto_driver</t>
+  </si>
+  <si>
+    <t>1. Navigate to Drivers &gt; Add Driver and enter all required driver profile details (Service Category, Driver Type, Name, Email, Contact &amp; WhatsApp Numbers, Profile Image, Source, Gender, and Vehicle Specifications).
+2. Enter the driver's bank and payment details (Bank Name, Location, Account Number, Account Holder Name, Payment Email, and IFSC Code) and submit the form to create the driver record.
+3. Navigate to Drivers &gt; Pending Documents, filter for the newly created driver, and open their required document details.
+4. Upload the mandatory Driving License document, set a valid Expiry Date, submit the document, and approve the driver.
+5. Navigate to Drivers &gt; Approved Drivers, filter for the approved driver, and open their document view mode to verify that the approved license and profile status display correctly.</t>
+  </si>
+  <si>
+    <t>SA_RD_05</t>
+  </si>
+  <si>
+    <t>TC_RG_05_add_verify_bike_driver</t>
+  </si>
+  <si>
+    <t>TC_SA_05_add_verify_bike_driver</t>
+  </si>
+  <si>
+    <t>1. Navigate to Drivers &gt; Add Driver and enter all required driver profile details (Service Category as Bike Ride, Driver Type, Name, Email, Contact &amp; WhatsApp Numbers, Profile Image, Source, Gender, and Vehicle Specifications).
+2. Enter the driver's bank and payment details (Bank Name, Location, Account Number, Account Holder Name, Payment Email, and IFSC Code) and submit the form to create the bike driver record.
+3. Navigate to Drivers &gt; Pending Documents, filter for the newly created bike driver, and open their required document details.
+4. Upload the mandatory Driving License document, set a valid Expiry Date, submit the document, and approve the driver.
+5. Navigate to Drivers &gt; Approved Drivers, filter for the approved bike driver, and open their document view mode to verify that the approved license and profile status display correctly.</t>
+  </si>
+  <si>
+    <t>SA_RD_06</t>
+  </si>
+  <si>
+    <t>TC_RG_06_add_verify_taxi_driver</t>
+  </si>
+  <si>
+    <t>TC_SA_06_add_verify_taxi_driver</t>
+  </si>
+  <si>
+    <t>2. Enter the driver's bank and payment details (Bank Name, Location, Account Number, Account Holder Name, Payment Email, and IFSC Code) and submit the form to create the taxi driver record.</t>
+  </si>
+  <si>
+    <t>3. Navigate to Drivers &gt; Pending Documents, filter for the newly created taxi driver, and open their required document details.</t>
+  </si>
+  <si>
+    <t>4. Upload the mandatory Driving License document, set a valid Expiry Date, submit the document, and approve the driver.</t>
+  </si>
+  <si>
+    <t>5. Navigate to Drivers &gt; Approved Drivers, filter for the approved taxi driver, and open their document view mode to verify that the approved license and profile status display correctly.</t>
+  </si>
+  <si>
+    <t>SA_RD_07</t>
+  </si>
+  <si>
+    <t>TC_RG_07_transport_service_complete_test</t>
+  </si>
+  <si>
+    <t>TC_SA_07_transport_service_complete_test</t>
+  </si>
+  <si>
+    <t>1. Navigate to Transport Services and add a new category (e.g., "Bus Ride"), filling in Arabic name, slug, image, status (Active), and selecting the target city/area.
+2. In Transport Settings &gt; Vehicle Type, add a new vehicle type (e.g., "volvo") with base fare, extra distance rates, waiting charges, pickup fees, customer/driver fees, GST, active status, image, notification limits, and night surcharge configurations.
+3. In Transport Settings &gt; Promocode, create a new promo code with user target, code name, discount amount, expiry date, order minimums, and usage limits.
+4. In Transport Settings &gt; Service Settings, update global dispatch rules including driver accept timeout and search radius.
+5. In Transport Settings &gt; Requirement Document, configure a new mandatory document type requiring proof number and expiry verification.
+6. Navigate to Drivers &gt; Add Driver and register a new driver assigned to the newly created "Bus Ride" category and "volvo" vehicle type along with profile, vehicle, and bank details.
+7. Navigate to Drivers &gt; Pending Documents, locate the driver, upload the newly configured mandatory document with expiry date, and approve the driver.
+8. Verify that the approved bus driver appears correctly in the Approved Drivers list.
+9. Return to Transport Services, filter for the created service category, edit its details (update name, slug, and set status to Deactivate), and submit changes.</t>
+  </si>
+  <si>
+    <t>TC_RG_08_add_transport_city_admin</t>
+  </si>
+  <si>
+    <t>TC_SA_08_add_transport_city_admin</t>
+  </si>
+  <si>
+    <t>1. Navigate to Transport Services, create a new transport category (e.g., "lorryRide"), upload image, select city/area, and set status to Active.
+2. In Transport Settings &gt; Vehicle Type, add a new vehicle type (e.g., "tempo") associated with the new transport category, configure fare structures, fee rules, GST, and night surcharge settings.
+3. Navigate to Settings &gt; City Admin, create a new City Admin account, assign the newly created transport category and driver management permissions, and submit.
+4. Log out as Super Admin, log in with the new City Admin credentials, and verify access to the dashboard.
+5. As City Admin, navigate to Drivers &gt; Add Driver and register a new driver under the "lorryRide" service category and "tempo" vehicle type with complete profile, vehicle, and bank details.
+6. Toggle the sidebar to verify that only assigned navigation options (Transport and Driver management sub-menus) are present, while unassigned modules (Delivery and Provider services) are hidden.
+7. Log out as City Admin and log back in as Super Admin.
+8. Navigate to Transport Services, filter for the created service category ("lorryRide"), edit its status to Deactivate, and save changes.</t>
+  </si>
+  <si>
+    <t>1. Navigate to Drivers &gt; Add Driver and enter all required driver profile details (Service Category as Taxi Ride, Driver Type, Name, Email, Contact &amp; WhatsApp Numbers, Profile Image, Source, Gender, and SUV Vehicle Specifications).
+2. Enter the driver's bank and payment details (Bank Name, Location, Account Number, Account Holder Name, Payment Email, and IFSC Code) and submit the form to create the taxi driver record.
+3. Navigate to Drivers &gt; Pending Documents, filter for the newly created taxi driver, and open their required document details.
+4. Upload the mandatory Driving License document, set a valid Expiry Date, submit the document, and approve the driver.
+5. Navigate to Drivers &gt; Approved Drivers, filter for the approved taxi driver, and open their document view mode to verify that the approved license and profile status display correctly.</t>
+  </si>
+  <si>
+    <t>TC_RG_09_Tranport_Service_Statistic_Test</t>
+  </si>
+  <si>
+    <t>TC_SA_09_Tranport_Service_Statistic_Test</t>
+  </si>
+  <si>
+    <t>1. Navigate to Transport Services and filter the services list by "Auto Ride".
+2. Navigate to the Dashboard home page.
+3. Filter and verify dashboard statistics for each available time period range: Today, Yesterday, This Week, This Month, Last Month, This Year, and Last Year.</t>
+  </si>
+  <si>
+    <t>TC_RG_10_Tranport_Driver_Statistic_Test</t>
+  </si>
+  <si>
+    <t>TC_SA_10_Tranport_Driver_Statistic_Test</t>
+  </si>
+  <si>
+    <t>1. Navigate to Transport Services and filter the services list by "Auto Ride".
+2. Click the Drivers icon to open the Transport Drivers dashboard view.
+3. Filter and verify the driver statistics across each available time range: Today, Yesterday, This Week, This Month, Last Month, Last Year, and This Year.
+4. Apply specific filter criteria by selecting a target Driver Name, Vehicle Type (e.g., "pink Auto"), and Service Category ("Auto Ride").
+5. Click Search to filter and verify the approved drivers data grid based on the applied criteria.</t>
+  </si>
+  <si>
+    <t>TC_RG_11_Transport_Service_Ride_Test</t>
+  </si>
+  <si>
+    <t>TC_SA_11_Transport_Service_Ride_Test</t>
+  </si>
+  <si>
+    <t>1. Navigate to Transport Services, filter by "Auto Ride", and click the Rides icon to open the Rides Dashboard.
+2. Filter and verify ride statistics across each date range: Today, Yesterday, This Week, This Month, Last Month, Last Year, and This Year.
+3. Filter rides by specific Customer, Driver, Vehicle Type ("Pink Auto"), and Status ("Completed Rides").
+4. Open a completed ride record to view chat logs, verify ride arrival details, and return to the main rides list.
+5. Filter, search, and verify ride records across remaining status types (Incomplete, Cancelled, Scheduled, and Pre-Acceptance Cancel Rides), clearing filters between each search.</t>
+  </si>
+  <si>
+    <t>TC_RG_12_Transport_Service_Aerial_View</t>
+  </si>
+  <si>
+    <t>TC_SA_12_Transport_Service_Aerial_View</t>
+  </si>
+  <si>
+    <t>1. Navigate to Transport Services, filter by "Auto Ride", and navigate to the Home view.
+2. Open the Aerial View section and filter by "All" drivers to view live positions on the map.
+3. Open driver details via the view (eye) icon, verify information, and close the details popup.
+4. Filter Aerial View by driver operational statuses—Available, Enroute to Pickup, Reached Pickup, and Ongoing—verifying map details and closing popups for each status.</t>
+  </si>
+  <si>
+    <t>TC_RG_13_Transport_Service_Earning_Reports</t>
+  </si>
+  <si>
+    <t>TC_SA_13_Transport_Service_Earning_Reports</t>
+  </si>
+  <si>
+    <t>1. Navigate to Transport Services, filter by "Auto Ride", click the Home icon, and open the Earning Report module.
+2. Verify earnings statistics across all available date ranges: Today, Yesterday, This Week, This Month, Last Month, This Year, and Last Year.
+3. Filter earnings reports by selecting a specific Driver and Customer.
+4. Filter and verify transactions across different Payment Types (Cash, Razorpay, and Wallet).
+5. Filter by Driver Payment Status (Settled vs. Unsettled).
+6. Select an unsettled Cash transaction, mark/settle the transaction using the "Settle Transaction" button, and verify settlement.
+7. Locate the transaction in the grid, click the View (eye) icon to verify individual earning details, and close the details view.</t>
+  </si>
+  <si>
+    <t>TC_RG_14_Transport_Provider_List_Test</t>
+  </si>
+  <si>
+    <t>TC_SA_14_Transport_Provider_List_Test</t>
+  </si>
+  <si>
+    <t>1. Navigate to Providers &gt; Transport Providers List.
+2. Verify provider statistics across each available date range: Today, Yesterday, This Week, This Month, Last Month, This Year, and Last Year.
+3. Filter and search transport providers by individual Service Types (Taxi Ride, Bike Ride, and Auto Ride), clearing filters between each search.
+4. Test grid pagination controls by navigating to Next, Previous, Last, and First pages.
+5. Export the provider list data in PDF and Excel formats.</t>
+  </si>
+  <si>
+    <t>TC_RG_15_Transport_Service_Review_Test</t>
+  </si>
+  <si>
+    <t>TC_SA_15_Transport_Service_Review_Test</t>
+  </si>
+  <si>
+    <t>1. Navigate to Transport Services, filter by "Auto Ride", click the Home icon, and open the Review module.
+2. Verify review statistics across each available date range: Today, Yesterday, This Week, This Month, Last Month, This Year, and Last Year.
+3. Clear filters, then filter the review list by specific Customer Name and Driver Name.
+4. Verify rating management actions on the filtered review: test Disapprove rating, Approve rating, and verify the Delete rating workflow by triggering delete and clicking Cancel Delete.</t>
+  </si>
+  <si>
+    <t>TC_RG_16_subscription_plan_test</t>
+  </si>
+  <si>
+    <t>TC_SA_16_subscription_plan_test</t>
+  </si>
+  <si>
+    <t>1. Navigate to Subscription Plan &gt; Store Subscription Plan, verify the list header, and create a new plan (selecting Food Delivery, multi-language plan names/descriptions, duration, price, and Active status).
+2. Filter for the newly created Store Plan, open edit mode, close the modal, test activating and deactivating the plan, then delete the plan after confirming the prompt.
+3. Navigate to Subscription Plan &gt; Driver Subscription Plan, verify the list header, and create a new plan (selecting Auto Ride, multi-language fields, duration, free rides limit, price, and Active status).
+4. Filter for the created Driver Plan, verify edit popup, toggle active/deactive status, and delete the plan.
+5. Navigate to Subscription Plan &gt; Provider Subscription Plan, verify the list header, and create a new plan (selecting service category, multi-language details, duration, price, and Active status).
+6. Filter for the created Provider Plan, open/close edit modal, toggle active/deactive status, and delete the plan.
+7. Navigate to Subscription Plan &gt; Customer Subscription Plan, verify the list header, and create a new plan (selecting service category, multi-language details, duration, free rides limit, price, and Active status).
+8. Filter for the created Customer Plan, open/close edit modal, toggle active/deactive status, and delete the plan.</t>
+  </si>
+  <si>
+    <t>1. Navigate to Settings &gt; Geo Fencing and click "Add Restricted Area".
+2. Enter the restricted area name ("Chennai Airport"), enable the status toggle, search and select "Chennai Airport" on the map location input.
+3. Draw a restricted polygon area on the map canvas and submit the form to save the restricted area.
+4. Filter the restricted area list by searching for "Chennai Airport", then click the Edit button for the record.
+5. Update the restricted area details by changing the name to "Chennai Port Trust", toggling the status, searching and selecting "Chennai Port Trust", redraw/update the map polygon, and submit the changes.
+6. Filter the restricted area list by searching for "Chennai Port Trust", click the Delete button, and confirm the deletion prompt.</t>
+  </si>
+  <si>
+    <t>TC_SA_17_Geo_Fencing_Test</t>
+  </si>
+  <si>
+    <t>TC_RG_17_Geo_Fencing_Test</t>
+  </si>
+  <si>
+    <t>TC_RG_18_Panic_Call_Test</t>
+  </si>
+  <si>
+    <t>TC_SA_18_Panic_Call_Test</t>
+  </si>
+  <si>
+    <t>1. Navigate to Settings &gt; Panic Call Setting and click "Add Panic Call".
+2. Enter the emergency contact details (Name in English, Tamil, and Hindi, Contact Number) and set the status to Active.
+3. Submit the form to create the panic call entry.
+4. Filter/search the panic call list for the newly created entry.
+5. Click the Edit button, change the status to Deactive, and submit the changes.
+6. Click the Delete button on the panic call entry and confirm the deletion prompt.</t>
+  </si>
+  <si>
+    <t>TC_RG_19_Dashboard_Test</t>
+  </si>
+  <si>
+    <t>TC_SA_19_Dashboard_Test</t>
+  </si>
+  <si>
+    <t>1. Filter dashboard statistics for "Today", click Search to load data, and then click Clear to reset the filter.
+2. Filter dashboard statistics for "Yesterday", click Search to load data, and clear the filter.
+3. Filter dashboard statistics for "This Week", click Search to load data, and clear the filter.
+4. Filter dashboard statistics for "This Month", click Search to load data, and clear the filter.
+5. Filter dashboard statistics for "Last Month", click Search to load data, and clear the filter.
+6. Filter dashboard statistics for "This Year", click Search to load data, and clear the filter.
+7. Filter dashboard statistics for "Last Year", click Search to load data, and clear the filter.</t>
+  </si>
+  <si>
+    <t>TC_RG_20_Report_Issue_Faq_Test</t>
+  </si>
+  <si>
+    <t>TC_RG_SA_Report_Issue_Faq_Test</t>
+  </si>
+  <si>
+    <t>1. Navigate to Report Issue &gt; FAQs and click "Add FAQs".
+2. Enter the FAQ Title ("How do I permanently delete my account?") and Description, then submit to save the FAQ.
+3. Search for the created FAQ in the FAQs list and test toggling its status by deactivating and then reactivating it.
+4. Click the Edit button, update the FAQ Title ("how to report issue that you faced?") and Description, and submit the changes.
+5. Search for the updated FAQ in the list, click Delete, and confirm the deletion prompt.</t>
+  </si>
+  <si>
+    <t>TC_RG_21_Customer_Report_Issues</t>
+  </si>
+  <si>
+    <t>TC_SA_21_Customer_Report_Issues</t>
+  </si>
+  <si>
+    <t>1. Navigate to Report Issue &gt; Customer Report Issue.
+2. Filter customer reported issues across all date ranges (Today, Yesterday, This Week, This Month, Last Month, This Year, and Last Year), clearing filters after each search.
+3. Filter reported issues by a specific customer using the "Created By" dropdown and search.
+4. Filter by "Unresolved" status, locate an issue record in the grid, view its details via the Eye icon, and check the associated conversation via the Chat icon.
+5. Filter by "Resolved" status, select an issue, and verify the issue resolution workflow by clicking the Resolve (thumbs up) icon and confirming the prompt.</t>
+  </si>
+  <si>
+    <t>TC_RG_22_Driver_Report_Issues</t>
+  </si>
+  <si>
+    <t>TC_SA_22_Driver_Report_Issues</t>
+  </si>
+  <si>
+    <t>1. Navigate to Report Issue &gt; Driver Report Issue.
+2. Filter driver reported issues across all date ranges (Today, Yesterday, This Week, This Month, Last Month, This Year, and Last Year), clearing filters after each search.
+3. Filter reported issues by a specific driver using the "Created By" dropdown and search.
+4. Filter by "Unresolved" status, locate an issue record in the grid, view its details via the Eye icon, and check the associated conversation via the Chat icon.
+5. Filter by "Resolved" status, select an issue, and verify the issue resolution workflow by clicking the Resolve (thumbs up) icon and confirming the prompt.</t>
+  </si>
+  <si>
+    <t>TC_RG_23_add_store</t>
+  </si>
+  <si>
+    <t>TC_SA_23_add_store</t>
+  </si>
+  <si>
+    <t>1. Navigate to Delivery Services &gt; Food Delivery &gt; Stores and click "Add Store".
+2. Enter store details (Store Name, Delivery Radius: 25 km, ETA: 30 min, Minimum Amount, Packaging Charges, Description, Banner Image, Driver Notification: Both, Allow Pickup: Checked, Status: Active, and Address).
+3. Set commission and promotional details (Storewise Commission: 25%, Offer Type: Amount, Offer Amount, and Minimum Order Amount).
+4. Enter Contact Person details (Full Name, Email, Phone Number, Profile Image) and Bank Account details (Bank Name, Location, Account Number, Account Holder Name, Payment Email, BIC Code).
+5. Configure Everyday Store Timings (10:00 AM to 10:00 PM) and submit the form to create the store.
+6. Navigate to Stores &gt; Pending Documents Stores List and filter by the created Store Name.
+7. Click the Document icon, upload required Address Proof with an expiry date, submit, and approve the store document.
+8. Navigate back to Stores &gt; Store List, filter by the Store Name, and open the Document and Eye (View) icons to verify updated details.</t>
+  </si>
+  <si>
+    <t>TC_RG_24_store_oprerations</t>
+  </si>
+  <si>
+    <t>TC_SA_24_store_oprerations</t>
+  </si>
+  <si>
+    <t>1. Navigate to Delivery Services &gt; Food Delivery &gt; Store List and filter by the specific Store Name.
+2. Open Products for the store and click "Add Products".
+3. Enter product details (Category: Grill Chicken, Product Name, Amount: 500, Description, Product Image, Status: Active, Discount Amount: 50) and save the product.
+4. Filter and verify the newly added product, then return to the Store List.
+5. Navigate to Store Wallet and test wallet transactions: add 1000 to the wallet balance, then deduct 200 from the wallet balance.
+6. Return to the Store List, open Store Drivers, and click "Add Private Driver".
+7. Enter private driver details (Name, Email, Phone Number, Profile Image, Gender: Male) and Vehicle details (Vehicle Type: Scooter, Model Year, Company, Plate Number, Model Name, Vehicle Image, Color: White).
+8. Submit to create the driver, then filter for the created driver and click the Eye (View) icon to verify driver details.</t>
+  </si>
+  <si>
+    <t>TC_RG_25_store_status_management</t>
+  </si>
+  <si>
+    <t>TC_SA_25_store_status_management</t>
+  </si>
+  <si>
+    <t>1. Navigate to Delivery Services &gt; Food Delivery &gt; Stores and click "Add Store".
+2. Enter store details (Store Name, Delivery Radius: 25 km, ETA: 30 min, Minimum Order Amount, Packaging Charges, Description, Banner Image, Driver Notification: Both, Allow Pickup: Checked, Status: Active, Address).
+3. Set commission and promotional details (Storewise Commission: 25%, Offer Type: Amount, Offer Amount, Minimum Order Amount).
+4. Enter Contact Person details (Full Name, Email, Phone Number, Profile Image) and Bank Account details (Bank Name, Location, Account Number, Account Holder Name, Payment Email, BIC Code).
+5. Configure Everyday Store Timings (10:00 AM to 10:00 PM) and submit to create the store.
+6. Navigate to Stores &gt; Pending Documents Stores List, filter by the created Store Name, upload Address Proof with an expiry date, and approve the document.
+7. Navigate to Stores &gt; Store List, filter by the Store Name, click the Block icon, and confirm blocking the store.
+8. Navigate to Stores &gt; Blocked Stores List, filter for the store, and click the Unblock icon.
+9. Navigate to Stores &gt; Rejected Stores List, filter for the store, and click the Approve icon.
+10. Return to Stores &gt; Store List, filter by Store Name, open Documents, click the Unapprove/Reject icon, enter the rejection reason ("document insufficient"), and confirm store rejection.</t>
+  </si>
+  <si>
+    <t>TC_RG_26_delivery_service_complete_test</t>
+  </si>
+  <si>
+    <t>TC_SA_26_delivery_service_complete_test</t>
+  </si>
+  <si>
+    <t>1. Navigate to Delivery Services and click "Add Service Category".
+2. Enter category details (Category Name, Slug, Image, Status: Active, Category Flow: Food Delivery, and Multi-language Names in Tamil, Arabic, and Hindi) and submit.
+3. Configure Delivery Settings:
+   - Go to Settings &gt; Requirement Document and add a new mandatory document with display order.
+   - Go to Settings &gt; Service Settings and configure search radius, tax type/amount, platform fee type/amount, cancellation charge percentage, and driver accept timeout.
+4. Add and verify a new Store under Delivery Services:
+   - Enter store information (Name, Radius, ETA, Minimum Order Amount, Packaging Charges, Address, Status: Active).
+   - Set commission rate, offer details, contact person info, bank account details, and store operating hours.
+   - Navigate to Pending Documents Stores List, upload Address Proof, approve the document, and confirm store activation in Store List.
+5. Create a new Product Category (e.g., "curd") with multi-language names and image, then map it to the newly created store under Products.
+6. Navigate back to Delivery Services, filter for the created service category, click Edit, set status to Deactivate, and save changes.</t>
+  </si>
+  <si>
+    <t>TC_RG_27_add_provider</t>
+  </si>
+  <si>
+    <t>TC_SA_27_add_provider</t>
+  </si>
+  <si>
+    <t>1. Navigate to Delivery Services &gt; Plumbers and select "Add Providers".
+2. Enter plumber details (Full Name, Profile Image, Email, Phone Number, Landmark, Delivery Radius: 25 km, Minimum Order: 10, Address) and operating time slots.
+3. Enter Bank Account details (Bank Name, Location, Account Number, Account Holder Name, Payment Email, BIC Code) and save the provider.
+4. Navigate to Pending Document Providers, filter for the created Plumber, upload Address Proof with an expiry date, and approve the document.
+5. Navigate to Provider List, filter for the approved Plumber, and view/verify document details via the Eye icon.
+6. Open the Plumber Wallet and perform wallet transactions: add 1000 to the wallet balance, then deduct 200 from the wallet balance.
+7. Return to Provider Documents, select the document, click Reject, and submit the rejection reason ("document insufficient").
+8. Block the provider from the Provider List by specifying a blocking reason ("customer complaints").
+9. Navigate to Blocked Providers, filter for the Plumber, click Unblock, and confirm the provider returns to the active Provider List.</t>
+  </si>
+  <si>
+    <t>TC_RG_28_provider_service_full_lifecycle_test</t>
+  </si>
+  <si>
+    <t>TC_SA_28_provider_service_full_lifecycle_test</t>
+  </si>
+  <si>
+    <t>1. Navigate to Provider Services and click "Add New Services".
+2. Enter service details (Service Name: Painter, multi-language names in Tamil, Arabic, and Hindi, Slug, Image, Status: Active, and target City/Area) and submit to create the service.
+3. Configure Provider Service Settings:
+   - Go to Requirement Document and add a new mandatory document with expiry enabled.
+   - Go to Promocode and add a new discount promo code (assigning user, code name, discount type, amount: 100, expiry date, order/usage limits, and description).
+4. Navigate to Providers &gt; Add Providers and create a Painter profile:
+   - Enter contact details (Full Name, Profile Image, Email, Phone Number, Landmark, Delivery Radius: 25 km, Minimum Order: 10, Address) and daily operating time slots.
+   - Enter Bank Account details (Bank Name, Location, Account Number, Account Holder Name, Payment Email, BIC Code) and save.
+5. Go to Pending Document Providers, filter for the Painter, upload Address Proof with an expiry date, and approve the document.
+6. Create a new Provider Category (e.g., "residentialPainter") with multi-language names and image.
+7. Navigate to Provider List, filter for the Painter, open Package Management, and add a new service package (linking the created Category, Package Name, Amount: 1000, Max Booking Qty: 4, Status: Active, and Description).
+8. Return to Provider Services, filter for the created service ("Painter"), edit the service details, set the status to Deactivate, and save changes.
+9. Refresh the Provider Services view from the Dashboard to verify that the deactivated service is properly listed.</t>
+  </si>
+  <si>
+    <t>TC_RG_29_test_data_cleanup</t>
+  </si>
+  <si>
+    <t>TC_SA_29_test_data_cleanup</t>
+  </si>
+  <si>
+    <t>No Manual Test Cases Since this is a data cleanup sheet after test execution</t>
   </si>
 </sst>
 </file>
@@ -4602,74 +4966,89 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{452F96D9-3311-4A18-82B5-F5729925CB8A}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" customWidth="1"/>
-    <col min="2" max="2" width="21.5546875" customWidth="1"/>
-    <col min="3" max="3" width="28.77734375" customWidth="1"/>
-    <col min="4" max="4" width="26.6640625" customWidth="1"/>
-    <col min="5" max="5" width="53.21875" customWidth="1"/>
-    <col min="6" max="6" width="36.88671875" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" customWidth="1"/>
-    <col min="8" max="8" width="15.21875" customWidth="1"/>
+    <col min="2" max="3" width="21.5546875" customWidth="1"/>
+    <col min="4" max="4" width="28.77734375" customWidth="1"/>
+    <col min="5" max="5" width="26.6640625" customWidth="1"/>
+    <col min="6" max="6" width="36.6640625" customWidth="1"/>
+    <col min="7" max="7" width="53.21875" customWidth="1"/>
+    <col min="8" max="8" width="36.88671875" customWidth="1"/>
+    <col min="9" max="9" width="16.33203125" customWidth="1"/>
+    <col min="10" max="10" width="15.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>184</v>
+      <c r="C1" s="4" t="s">
+        <v>148</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>151</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>150</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="2"/>
+      <c r="C3" s="1"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4678,70 +5057,85 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9FEA58B-ACBB-4068-8C66-F4A14C3E8CAE}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="2" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26.77734375" customWidth="1"/>
+    <col min="5" max="5" width="34.109375" customWidth="1"/>
+    <col min="6" max="6" width="36.44140625" customWidth="1"/>
+    <col min="7" max="7" width="69.33203125" customWidth="1"/>
+    <col min="8" max="8" width="31.77734375" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="360" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="360" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>98</v>
+        <v>86</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>189</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>191</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4750,70 +5144,84 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A04AC2C5-FB17-478C-B9F4-6CCC13A451B0}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="2" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26.77734375" customWidth="1"/>
+    <col min="5" max="6" width="34.109375" customWidth="1"/>
+    <col min="7" max="7" width="69.33203125" customWidth="1"/>
+    <col min="8" max="8" width="31.77734375" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>101</v>
+        <v>91</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>192</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>194</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4822,70 +5230,85 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F55FCD48-3B50-4EDD-B265-9AB60F809D78}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="2" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26.77734375" customWidth="1"/>
+    <col min="5" max="5" width="34.109375" customWidth="1"/>
+    <col min="6" max="6" width="36.88671875" customWidth="1"/>
+    <col min="7" max="7" width="69.33203125" customWidth="1"/>
+    <col min="8" max="8" width="31.77734375" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>107</v>
+        <v>93</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>195</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>173</v>
+        <v>96</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>197</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4894,70 +5317,85 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{705BF950-38CF-4525-A333-E60DE1739EA0}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="2" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26.77734375" customWidth="1"/>
+    <col min="5" max="5" width="34.109375" customWidth="1"/>
+    <col min="6" max="6" width="42.109375" customWidth="1"/>
+    <col min="7" max="7" width="69.33203125" customWidth="1"/>
+    <col min="8" max="8" width="31.77734375" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>122</v>
+        <v>102</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>198</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>200</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4966,70 +5404,84 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4B640C4-00BD-478A-A57E-A90215D007C2}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="2" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26.77734375" customWidth="1"/>
+    <col min="5" max="6" width="34.109375" customWidth="1"/>
+    <col min="7" max="7" width="69.33203125" customWidth="1"/>
+    <col min="8" max="8" width="31.77734375" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>129</v>
+        <v>107</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>201</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>183</v>
+        <v>109</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>203</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5038,70 +5490,84 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05D8E6DC-EF3B-4D1D-A5D5-95A75B0B28AA}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="2" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26.77734375" customWidth="1"/>
+    <col min="5" max="6" width="34.109375" customWidth="1"/>
+    <col min="7" max="7" width="69.33203125" customWidth="1"/>
+    <col min="8" max="8" width="31.77734375" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>133</v>
+        <v>110</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>204</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>206</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5110,73 +5576,88 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB4E6D23-5EFE-4C84-AF6B-0AD768B8F6CC}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="20.6640625" customWidth="1"/>
+    <col min="2" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26.77734375" customWidth="1"/>
+    <col min="5" max="5" width="34.109375" customWidth="1"/>
+    <col min="6" max="6" width="39.44140625" customWidth="1"/>
+    <col min="7" max="7" width="69.33203125" customWidth="1"/>
+    <col min="8" max="8" width="31.77734375" customWidth="1"/>
+    <col min="9" max="9" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>140</v>
+        <v>115</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>207</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5185,70 +5666,85 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39F69F54-6E80-4C66-8F82-CEFA135D089A}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="2" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26.77734375" customWidth="1"/>
+    <col min="5" max="5" width="34.109375" customWidth="1"/>
+    <col min="6" max="6" width="36.6640625" customWidth="1"/>
+    <col min="7" max="7" width="69.33203125" customWidth="1"/>
+    <col min="8" max="8" width="31.77734375" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>61</v>
+        <v>52</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>210</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5257,70 +5753,84 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FB72DFB-F4E3-4531-A41F-FCF21B5BBF59}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="2" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26.77734375" customWidth="1"/>
+    <col min="5" max="6" width="34.109375" customWidth="1"/>
+    <col min="7" max="7" width="69.33203125" customWidth="1"/>
+    <col min="8" max="8" width="31.77734375" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>89</v>
+        <v>130</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>215</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>182</v>
+        <v>78</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5329,70 +5839,85 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBB09688-59B4-47C6-9CAD-FED2B503D101}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="2" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26.77734375" customWidth="1"/>
+    <col min="5" max="5" width="34.109375" customWidth="1"/>
+    <col min="6" max="6" width="37.77734375" customWidth="1"/>
+    <col min="7" max="7" width="69.33203125" customWidth="1"/>
+    <col min="8" max="8" width="31.77734375" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="345.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>89</v>
+        <v>79</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>216</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5401,77 +5926,92 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4396F6CA-D57B-49F5-A8ED-CEBB93A6ED43}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" customWidth="1"/>
-    <col min="2" max="2" width="21.5546875" customWidth="1"/>
-    <col min="3" max="3" width="28.77734375" customWidth="1"/>
-    <col min="4" max="4" width="31.6640625" customWidth="1"/>
-    <col min="5" max="5" width="53.21875" customWidth="1"/>
-    <col min="6" max="6" width="29" customWidth="1"/>
-    <col min="7" max="7" width="38.6640625" customWidth="1"/>
-    <col min="8" max="8" width="15.21875" customWidth="1"/>
+    <col min="2" max="3" width="21.5546875" customWidth="1"/>
+    <col min="4" max="4" width="28.77734375" customWidth="1"/>
+    <col min="5" max="5" width="31.6640625" customWidth="1"/>
+    <col min="6" max="6" width="39.33203125" customWidth="1"/>
+    <col min="7" max="7" width="53.21875" customWidth="1"/>
+    <col min="8" max="8" width="29" customWidth="1"/>
+    <col min="9" max="9" width="38.6640625" customWidth="1"/>
+    <col min="10" max="10" width="15.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>39</v>
+        <v>155</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>43</v>
+        <v>156</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>179</v>
+        <v>37</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>32</v>
+        <v>157</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="2"/>
+      <c r="C3" s="1"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5480,70 +6020,84 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23692DF2-D92E-4735-942F-857C385D78E2}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="2" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26.77734375" customWidth="1"/>
+    <col min="5" max="6" width="34.109375" customWidth="1"/>
+    <col min="7" max="7" width="69.33203125" customWidth="1"/>
+    <col min="8" max="8" width="31.77734375" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="403.2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>95</v>
+        <v>82</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>219</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5552,71 +6106,85 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59F1688F-2A0A-4B72-B3D2-D238F1ED2ADC}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="20.6640625" customWidth="1"/>
+    <col min="2" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26.77734375" customWidth="1"/>
+    <col min="5" max="6" width="34.109375" customWidth="1"/>
+    <col min="7" max="7" width="69.33203125" customWidth="1"/>
+    <col min="8" max="8" width="31.77734375" customWidth="1"/>
+    <col min="9" max="9" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>144</v>
+        <v>120</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>222</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G2" s="8"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I2" s="8"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5625,71 +6193,85 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9F16F73-60F9-4B7A-AD34-4E583B7CB7A7}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="20.6640625" customWidth="1"/>
+    <col min="2" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26.77734375" customWidth="1"/>
+    <col min="5" max="6" width="34.109375" customWidth="1"/>
+    <col min="7" max="7" width="69.33203125" customWidth="1"/>
+    <col min="8" max="8" width="31.77734375" customWidth="1"/>
+    <col min="9" max="9" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G2" s="8"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I2" s="8"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5698,71 +6280,85 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{065D1DC2-3D69-4BD0-B526-3FD12D803726}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="20.6640625" customWidth="1"/>
+    <col min="2" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26.77734375" customWidth="1"/>
+    <col min="5" max="6" width="34.109375" customWidth="1"/>
+    <col min="7" max="7" width="69.33203125" customWidth="1"/>
+    <col min="8" max="8" width="31.77734375" customWidth="1"/>
+    <col min="9" max="9" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>150</v>
+        <v>126</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>228</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>180</v>
+        <v>127</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G2" s="8"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>230</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I2" s="8"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5771,70 +6367,85 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9950CA5-B845-4E23-9843-8D459D399E99}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="2" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26.77734375" customWidth="1"/>
+    <col min="5" max="5" width="34.109375" customWidth="1"/>
+    <col min="6" max="6" width="35.77734375" customWidth="1"/>
+    <col min="7" max="7" width="69.33203125" customWidth="1"/>
+    <col min="8" max="8" width="31.77734375" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>231</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>174</v>
+        <v>18</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>233</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5843,70 +6454,86 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DE0E168-E98A-49FE-8885-7B5F3F3678F3}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="3" max="3" width="24.77734375" customWidth="1"/>
+    <col min="4" max="4" width="26.77734375" customWidth="1"/>
+    <col min="5" max="5" width="34.109375" customWidth="1"/>
+    <col min="6" max="6" width="38.109375" customWidth="1"/>
+    <col min="7" max="7" width="69.33203125" customWidth="1"/>
+    <col min="8" max="8" width="31.77734375" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>234</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>236</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5915,70 +6542,84 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9584B63-AFDB-41EC-A160-356B47922D15}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="2" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26.77734375" customWidth="1"/>
+    <col min="5" max="6" width="34.109375" customWidth="1"/>
+    <col min="7" max="7" width="69.33203125" customWidth="1"/>
+    <col min="8" max="8" width="31.77734375" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>237</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>175</v>
+        <v>22</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>239</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5987,77 +6628,92 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8A1C6E6-1358-42F0-B7B3-06420689DEE4}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="44.33203125" customWidth="1"/>
-    <col min="8" max="8" width="27.109375" customWidth="1"/>
+    <col min="3" max="3" width="27.5546875" customWidth="1"/>
+    <col min="4" max="4" width="26.77734375" customWidth="1"/>
+    <col min="5" max="6" width="34.109375" customWidth="1"/>
+    <col min="7" max="7" width="69.33203125" customWidth="1"/>
+    <col min="8" max="8" width="31.77734375" customWidth="1"/>
+    <col min="9" max="9" width="44.33203125" customWidth="1"/>
+    <col min="10" max="10" width="27.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="I1" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>240</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>176</v>
+        <v>41</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>242</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6066,70 +6722,84 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF16C04E-51BB-4902-91C6-410B8EB3791F}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="2" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26.77734375" customWidth="1"/>
+    <col min="5" max="6" width="34.109375" customWidth="1"/>
+    <col min="7" max="7" width="69.33203125" customWidth="1"/>
+    <col min="8" max="8" width="31.77734375" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>243</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>177</v>
+        <v>24</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>245</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6138,70 +6808,85 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E742ED82-3510-47F4-AA85-6344770C749C}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="2" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26.77734375" customWidth="1"/>
+    <col min="5" max="5" width="34.109375" customWidth="1"/>
+    <col min="6" max="6" width="36.88671875" customWidth="1"/>
+    <col min="7" max="7" width="69.33203125" customWidth="1"/>
+    <col min="8" max="8" width="31.77734375" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>46</v>
+        <v>28</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>246</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>178</v>
+        <v>40</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>248</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6210,74 +6895,89 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" customWidth="1"/>
-    <col min="2" max="2" width="21.5546875" customWidth="1"/>
-    <col min="3" max="3" width="28.77734375" customWidth="1"/>
-    <col min="4" max="4" width="31.6640625" customWidth="1"/>
-    <col min="5" max="5" width="53.21875" customWidth="1"/>
-    <col min="6" max="6" width="29" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" customWidth="1"/>
-    <col min="8" max="8" width="15.21875" customWidth="1"/>
+    <col min="2" max="3" width="21.5546875" customWidth="1"/>
+    <col min="4" max="4" width="27.33203125" customWidth="1"/>
+    <col min="5" max="5" width="31.6640625" customWidth="1"/>
+    <col min="6" max="6" width="39.109375" customWidth="1"/>
+    <col min="7" max="7" width="53.21875" customWidth="1"/>
+    <col min="8" max="8" width="29" customWidth="1"/>
+    <col min="9" max="9" width="16.33203125" customWidth="1"/>
+    <col min="10" max="10" width="15.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>40</v>
+      <c r="C2" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>18</v>
+        <v>158</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>181</v>
+        <v>15</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="2"/>
+      <c r="C3" s="1"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6286,70 +6986,84 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2F621F-9A1F-4BCF-BC43-4FD25385804C}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="2" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26.77734375" customWidth="1"/>
+    <col min="5" max="6" width="34.109375" customWidth="1"/>
+    <col min="7" max="7" width="69.33203125" customWidth="1"/>
+    <col min="8" max="8" width="31.77734375" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>249</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>109</v>
+        <v>50</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="8"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
@@ -6360,65 +7074,78 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB63C6AC-3593-403C-90C0-44D30EC92C43}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
-    <col min="2" max="2" width="19.88671875" customWidth="1"/>
-    <col min="3" max="3" width="25.44140625" customWidth="1"/>
-    <col min="4" max="4" width="34.77734375" customWidth="1"/>
-    <col min="5" max="5" width="64" customWidth="1"/>
-    <col min="6" max="6" width="32.6640625" customWidth="1"/>
-    <col min="7" max="7" width="44.21875" customWidth="1"/>
+    <col min="2" max="3" width="19.88671875" customWidth="1"/>
+    <col min="4" max="4" width="25.44140625" customWidth="1"/>
+    <col min="5" max="5" width="34.77734375" customWidth="1"/>
+    <col min="6" max="6" width="38.77734375" customWidth="1"/>
+    <col min="7" max="7" width="64" customWidth="1"/>
+    <col min="8" max="8" width="32.6640625" customWidth="1"/>
+    <col min="9" max="9" width="44.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="F1" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>19</v>
+      <c r="C2" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>29</v>
+        <v>165</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -6428,73 +7155,88 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{603F1167-C5E0-4A83-A433-4756502E0A3E}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="30.88671875" customWidth="1"/>
-    <col min="4" max="4" width="35.5546875" customWidth="1"/>
-    <col min="5" max="5" width="71.44140625" customWidth="1"/>
-    <col min="6" max="6" width="29.6640625" customWidth="1"/>
-    <col min="7" max="7" width="59.21875" customWidth="1"/>
+    <col min="2" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="30.88671875" customWidth="1"/>
+    <col min="5" max="5" width="35.5546875" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" customWidth="1"/>
+    <col min="7" max="7" width="71.44140625" customWidth="1"/>
+    <col min="8" max="8" width="29.6640625" customWidth="1"/>
+    <col min="9" max="9" width="59.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>114</v>
+        <v>166</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>167</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>168</v>
+        <v>13</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>33</v>
+        <v>169</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="2"/>
+      <c r="C3" s="1"/>
       <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6503,73 +7245,88 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E919CD9C-25F0-4379-9D1E-02428B737EB3}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="35.5546875" customWidth="1"/>
-    <col min="5" max="5" width="71.44140625" customWidth="1"/>
-    <col min="6" max="6" width="29.5546875" customWidth="1"/>
-    <col min="7" max="7" width="47.33203125" customWidth="1"/>
+    <col min="2" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="35.5546875" customWidth="1"/>
+    <col min="6" max="6" width="40.77734375" customWidth="1"/>
+    <col min="7" max="7" width="71.44140625" customWidth="1"/>
+    <col min="8" max="8" width="29.5546875" customWidth="1"/>
+    <col min="9" max="9" width="47.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>114</v>
+        <v>170</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>169</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>34</v>
+        <v>173</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6578,73 +7335,104 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF62477-5019-4694-8947-A26FED9A3AD4}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="29.5546875" customWidth="1"/>
-    <col min="4" max="4" width="35.5546875" customWidth="1"/>
-    <col min="5" max="5" width="71.44140625" customWidth="1"/>
-    <col min="6" max="6" width="29.6640625" customWidth="1"/>
-    <col min="7" max="7" width="40.44140625" customWidth="1"/>
+    <col min="2" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="29.5546875" customWidth="1"/>
+    <col min="5" max="6" width="35.5546875" customWidth="1"/>
+    <col min="7" max="7" width="71.44140625" customWidth="1"/>
+    <col min="8" max="8" width="29.6640625" customWidth="1"/>
+    <col min="9" max="9" width="40.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>114</v>
+        <v>174</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>35</v>
+        <v>188</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G3" s="8"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="F4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="F5" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="F6" t="s">
+        <v>180</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6653,73 +7441,88 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C5E7D15-8F85-42A0-A3E4-72E2C74068F3}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="69.33203125" customWidth="1"/>
-    <col min="6" max="6" width="38" customWidth="1"/>
-    <col min="7" max="7" width="61.5546875" customWidth="1"/>
+    <col min="2" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26.77734375" customWidth="1"/>
+    <col min="5" max="5" width="34.109375" customWidth="1"/>
+    <col min="6" max="6" width="36.5546875" customWidth="1"/>
+    <col min="7" max="7" width="69.33203125" customWidth="1"/>
+    <col min="8" max="8" width="38" customWidth="1"/>
+    <col min="9" max="9" width="61.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>114</v>
+        <v>181</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6729,62 +7532,75 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17220503-D468-40D2-B5A5-294329C90611}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
-    <col min="2" max="2" width="19.88671875" customWidth="1"/>
-    <col min="3" max="3" width="25.44140625" customWidth="1"/>
-    <col min="4" max="4" width="34.77734375" customWidth="1"/>
-    <col min="5" max="5" width="64" customWidth="1"/>
-    <col min="6" max="6" width="32.6640625" customWidth="1"/>
-    <col min="7" max="7" width="17.5546875" customWidth="1"/>
+    <col min="2" max="3" width="19.88671875" customWidth="1"/>
+    <col min="4" max="4" width="25.44140625" customWidth="1"/>
+    <col min="5" max="5" width="34.77734375" customWidth="1"/>
+    <col min="6" max="6" width="36.44140625" customWidth="1"/>
+    <col min="7" max="7" width="64" customWidth="1"/>
+    <col min="8" max="8" width="32.6640625" customWidth="1"/>
+    <col min="9" max="9" width="17.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="F1" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>73</v>
+        <v>186</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>69</v>
+        <v>185</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>172</v>
+        <v>59</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>70</v>
+        <v>187</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Framework_For_WE1_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ADF90FE-3740-4F57-BF2C-6189E4F6ABDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF28C08-BE47-44FA-B959-3BB1306F735B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="26" activeTab="29" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="11" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Framework_For_WE1_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF28C08-BE47-44FA-B959-3BB1306F735B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F318867E-90FD-49B3-8190-67208FF35A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="11" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="26" activeTab="29" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Framework_For_WE1_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F318867E-90FD-49B3-8190-67208FF35A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E5E5018-9F39-4BAE-9CFD-DD35C4AB9210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="26" activeTab="29" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="11" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Framework_For_WE1_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E5E5018-9F39-4BAE-9CFD-DD35C4AB9210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91419805-60DD-49F2-A44E-4741FA5F2869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="11" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>

--- a/we1_superAdmin_regression.xlsx
+++ b/we1_superAdmin_regression.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91419805-60DD-49F2-A44E-4741FA5F2869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuperAdminLogin" sheetId="6" r:id="rId1"/>
